--- a/data/minimarket.xlsx
+++ b/data/minimarket.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SEMESTER 6\PRAK. SIGTER\PROJECT AKHIR\STUDENT SURVIVAL MAP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E88308DC-0387-4015-B5E5-AA2DFC22F13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0314C2DF-4890-48B9-AD17-25CCEE1E3B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F35F33EF-EB1F-4670-92AD-4BBD8F6B088B}"/>
   </bookViews>
@@ -75,1011 +75,27 @@
     <t>Minimarket/Supermarket</t>
   </si>
   <si>
-    <t>-7.733752545117078</t>
-  </si>
-  <si>
-    <t>110.39419756395505</t>
-  </si>
-  <si>
-    <t>Jl. Kaliurang Km 8.3 Prujukan Rt 2/3 Sinduharjo, Tambakan, Sinduharjo, Sleman, Sleman Regency, Special Region of Yogyakarta 55581</t>
-  </si>
-  <si>
     <t>Senin-Minggu</t>
   </si>
   <si>
-    <t>07.00-22.00</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.3/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/HvGAw3yRT4Z41LoZ7</t>
-  </si>
-  <si>
-    <t>M001.jpg</t>
-  </si>
-  <si>
     <t>Tidak</t>
   </si>
   <si>
-    <t>-7.749447245716337</t>
-  </si>
-  <si>
-    <t>110.38578306135572</t>
-  </si>
-  <si>
-    <t>Jl. Kaliurang, Kentungan, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>3.8/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/hrcCoQa6NbGUDMs58</t>
-  </si>
-  <si>
-    <t>M002.jpg</t>
-  </si>
-  <si>
-    <t>-7.756250064506058</t>
-  </si>
-  <si>
-    <t>110.37932712120767</t>
-  </si>
-  <si>
-    <t>Jl. Kaliurang, Km 5, 2, Catur Tunggal, Kec. Depok, Jl. Kaliurang No.27, Karang Wuni, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55284</t>
-  </si>
-  <si>
-    <t>07.00-22.01</t>
-  </si>
-  <si>
-    <t>3.9/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/yuGPo2Cdzm1cwWWFA</t>
-  </si>
-  <si>
-    <t>M003.jpg</t>
-  </si>
-  <si>
-    <t>-7.752217570012537</t>
-  </si>
-  <si>
-    <t>110.38218871514682</t>
-  </si>
-  <si>
-    <t>Jalan Pandega Marta No. 1 Sarimulyo Manggung, Manggung, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
     <t>Buka 24 Jam</t>
   </si>
   <si>
-    <t>3.4/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/y7eFw3yPzy8XiyVH8</t>
-  </si>
-  <si>
-    <t>M004.jpg</t>
-  </si>
-  <si>
     <t>Ya</t>
   </si>
   <si>
-    <t>-7.765916891413229</t>
-  </si>
-  <si>
-    <t>110.39147146767357</t>
-  </si>
-  <si>
-    <t>Jl. Affandi No.31a, Karang Gayam, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>3.1/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/FcK4Bx17jAYCpJhX8</t>
-  </si>
-  <si>
-    <t>M005.jpg</t>
-  </si>
-  <si>
-    <t>-7.758056400724876</t>
-  </si>
-  <si>
-    <t>110.39494223275801</t>
-  </si>
-  <si>
-    <t>Jl. Affandi No.23, Soropadan, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/gk9yBhy1XfxyNVp5A</t>
-  </si>
-  <si>
-    <t>M006.jpg</t>
-  </si>
-  <si>
-    <t>-7.752947002982559</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 110.39672719765858</t>
-  </si>
-  <si>
-    <t>Jl. Anggajaya 1 No.282, Sanggrahan, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>07.00-22.02</t>
-  </si>
-  <si>
-    <t>3.2/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/U18wT9wYGWXs2n1dA</t>
-  </si>
-  <si>
-    <t>M007.jpg</t>
-  </si>
-  <si>
-    <t>-7.749895190158755</t>
-  </si>
-  <si>
-    <t>110.39808053648082</t>
-  </si>
-  <si>
-    <t>Jl. Sukoharjo No.133 A, Sanggrahan, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4.1/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/ACN1JDZCWuDx7x3c9</t>
-  </si>
-  <si>
-    <t>M008.jpg</t>
-  </si>
-  <si>
-    <t>-7.7425767277541</t>
-  </si>
-  <si>
-    <t>110.39742175575905</t>
-  </si>
-  <si>
-    <t>Jl. Rajawali Raya No.32, Sanggrahan, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4.3/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/vtbQovKZLG9tKWRM9</t>
-  </si>
-  <si>
-    <t>M009.jpg</t>
-  </si>
-  <si>
-    <t>-7.749210435076886</t>
-  </si>
-  <si>
-    <t>110.40617648604177</t>
-  </si>
-  <si>
-    <t>Jl. Cemp. No.60, Dero, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4.5/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/Nj7awyKrLigPrPDt5</t>
-  </si>
-  <si>
-    <t>M010.jpg</t>
-  </si>
-  <si>
-    <t>-7.748732158171262</t>
-  </si>
-  <si>
-    <t>110.41114301296018</t>
-  </si>
-  <si>
-    <t>Jl. Nusa Indah No.249, Dero, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/UWnDTdNhGfGvs4cf6</t>
-  </si>
-  <si>
-    <t>M011.jpg</t>
-  </si>
-  <si>
-    <t>-7.752859025575523</t>
-  </si>
-  <si>
-    <t>110.40985387164312</t>
-  </si>
-  <si>
-    <t>Jl. Nusa Indah II No.50, Dero, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>2.7/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/wtP4be5hRqgrhRSLA</t>
-  </si>
-  <si>
-    <t>M012.jpg</t>
-  </si>
-  <si>
-    <t>-7.765337640697154</t>
-  </si>
-  <si>
-    <t>110.39597081132904</t>
-  </si>
-  <si>
-    <t>JL. Empu Tantular, No. 106, Pringwulung, Condongcatur, Depok, Jl. Tantular No.103, Kaliwaru, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>3.5/5/0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/BFdQ2TDQ9pBMcoAX8</t>
-  </si>
-  <si>
-    <t>M013.jpg</t>
-  </si>
-  <si>
-    <t>-7.769195812965372</t>
-  </si>
-  <si>
-    <t>110.3954706508378</t>
-  </si>
-  <si>
-    <t>Jl. Tantular Selatan, Pringwulung, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4.2/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/x2AwyBvdkzFEaSBq6</t>
-  </si>
-  <si>
-    <t>M014.jpg</t>
-  </si>
-  <si>
-    <t>-7.766357839864531</t>
-  </si>
-  <si>
-    <t>110.40251671938006</t>
-  </si>
-  <si>
-    <t>Jl. Wahid Hasyim No.5, Dabag, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/RnsoQmriB1m6i3AZ8</t>
-  </si>
-  <si>
-    <t>M015.jpg</t>
-  </si>
-  <si>
-    <t>-7.769020449248469</t>
-  </si>
-  <si>
-    <t>110.4051622426191</t>
-  </si>
-  <si>
-    <t>Jl. Perumnas No.8, Dabag, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/7pUGd4KNk2rEpYPh9</t>
-  </si>
-  <si>
-    <t>M016.jpg</t>
-  </si>
-  <si>
-    <t>-7.764893740448012</t>
-  </si>
-  <si>
-    <t>110.40570764856093</t>
-  </si>
-  <si>
-    <t>Indomaret, Jl. Perumnas, Ngropoh, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>3.6/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/i2NX2in6kMciJJ2f8</t>
-  </si>
-  <si>
-    <t>M017.jpg</t>
-  </si>
-  <si>
-    <t>Jl. Pintu Selatan UPN, Ngropoh, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/yiqGLnZVyKNjwWkj6?g_st=ac</t>
-  </si>
-  <si>
-    <t>M018.png</t>
-  </si>
-  <si>
-    <t>Ruko Pulohdadi, Jl. Seturan Raya Blok A2, Kledokan, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/YaX6UcnU3gT1rtmEA</t>
-  </si>
-  <si>
-    <t>M019.jpg</t>
-  </si>
-  <si>
-    <t>-7.769901074159813</t>
-  </si>
-  <si>
-    <t>110.4098548994134</t>
-  </si>
-  <si>
-    <t>Jl. Seturan Raya, RT.4/RW.2, Kledokan, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/rf4pXZ5op64fGaEM8</t>
-  </si>
-  <si>
-    <t>M020.jpg</t>
-  </si>
-  <si>
-    <t>-7.744073071243356</t>
-  </si>
-  <si>
-    <t>110.41459663470026</t>
-  </si>
-  <si>
     <t>Jalan Jetis, Ngemplak, Jetis, Wedomartani, Sleman, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55584</t>
   </si>
   <si>
-    <t>https://maps.app.goo.gl/fufaosvrsao483j99</t>
-  </si>
-  <si>
-    <t>M021.jpg</t>
-  </si>
-  <si>
-    <t>-7.769789454884158</t>
-  </si>
-  <si>
-    <t>110.402001372579</t>
-  </si>
-  <si>
-    <t>Jl. Wahid Hasyim No.130Dabag, Dabag, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/x4QJfLUQkhHWqZ137</t>
-  </si>
-  <si>
-    <t>M022.jpg</t>
-  </si>
-  <si>
-    <t>-7.781287170789081</t>
-  </si>
-  <si>
-    <t>110.41401363389748</t>
-  </si>
-  <si>
-    <t>Jl. Babarsari No.11, Janti, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/E5VGMWFMkCHfZriL7</t>
-  </si>
-  <si>
-    <t>M023.jpg</t>
-  </si>
-  <si>
-    <t>-7.76074441972423</t>
-  </si>
-  <si>
-    <t>110.42005087958772</t>
-  </si>
-  <si>
-    <t>Jl. P. Puger 1 No.2, Pugeran, Maguwoharjo, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>2.5/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/6ptXJdnoMD4LfxAm6</t>
-  </si>
-  <si>
-    <t>M024.jpg</t>
-  </si>
-  <si>
-    <t>-7.771760619476064</t>
-  </si>
-  <si>
-    <t>110.40402001483787</t>
-  </si>
-  <si>
-    <t>Jl. Perumnas, Nologaten, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/kQbgHLjC9CHXDVUd8</t>
-  </si>
-  <si>
-    <t>M025.jpg</t>
-  </si>
-  <si>
-    <t>-7.767021127082602</t>
-  </si>
-  <si>
-    <t>110.39044549226743</t>
-  </si>
-  <si>
-    <t>Jl. Affandi, Karang Gayam, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/D3hU9pNhRSwwefzd8</t>
-  </si>
-  <si>
-    <t>M026.jpg</t>
-  </si>
-  <si>
-    <t>-7.756085604225498</t>
-  </si>
-  <si>
-    <t>110.3943908636679</t>
-  </si>
-  <si>
-    <t>Jl. Anggajaya III No.66, Gejayan, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>4.4/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/SaS1WCo3QxG3jwW48</t>
-  </si>
-  <si>
-    <t>M027.jpg</t>
-  </si>
-  <si>
-    <t>-7.7757624268869865</t>
-  </si>
-  <si>
-    <t>110.3946526972518</t>
-  </si>
-  <si>
-    <t>Jl. Petung No.7, Papringan, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/qQN4SrSZBWcQTHjU8</t>
-  </si>
-  <si>
-    <t>M028.jpg</t>
-  </si>
-  <si>
-    <t>-7.77254523832928</t>
-  </si>
-  <si>
-    <t>110.41586671232616</t>
-  </si>
-  <si>
-    <t>Jl. Babarsari, Tambak Bayan, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/jZqh5aGaYjRwjM1Q9</t>
-  </si>
-  <si>
-    <t>M029.jpg</t>
-  </si>
-  <si>
-    <t>-7.7750608431802695</t>
-  </si>
-  <si>
-    <t>110.41612060615564</t>
-  </si>
-  <si>
-    <t>Jl. Babarsari No.23DTambak Bayan, Tambak Bayan, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/FKLhFzTtUv9Svu8X8</t>
-  </si>
-  <si>
-    <t>M030.jpg</t>
-  </si>
-  <si>
-    <t>-7.780008155389338</t>
-  </si>
-  <si>
-    <t>110.41434334934921</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/SXgbsSj6UDL5eM7v7</t>
-  </si>
-  <si>
-    <t>M031.jpg</t>
-  </si>
-  <si>
-    <t>-7.778918074660311</t>
-  </si>
-  <si>
-    <t>110.40850379127096</t>
-  </si>
-  <si>
-    <t>Jl. Kapas No.7, Ngentak, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4.0/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/v5r9juBWxgPk1Bog6</t>
-  </si>
-  <si>
-    <t>M032.jpg</t>
-  </si>
-  <si>
-    <t>-7.782104456519171</t>
-  </si>
-  <si>
-    <t>110.41045031063037</t>
-  </si>
-  <si>
-    <t>Jl. Raya Janti No.3, Gowok, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/wWMHH899sSHvLsLJ7</t>
-  </si>
-  <si>
-    <t>M033.jpg</t>
-  </si>
-  <si>
-    <t>-7.730661259789763</t>
-  </si>
-  <si>
-    <t>110.39141445284271</t>
-  </si>
-  <si>
-    <t>Jl. Damai Dk. Prujakan, RT.01/RW.32, Tambakan, Sinduharjo, Kec. Ngaglik, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55581</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/Hkk5NCU4DLaffHSk8</t>
-  </si>
-  <si>
-    <t>M034.jpg</t>
-  </si>
-  <si>
-    <t>-7.733212770145344</t>
-  </si>
-  <si>
-    <t>110.39450435764837</t>
-  </si>
-  <si>
-    <t>Jl. Kaliurang 8,1 No. 72, RT.04/RW.33, Tambakan, Sinduharjo, Kec. Ngaglik, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55581</t>
-  </si>
-  <si>
-    <t>3.7/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/ZP2CpU3Z8afNahNt5</t>
-  </si>
-  <si>
-    <t>M035.jpg</t>
-  </si>
-  <si>
-    <t>-7.752603744250776</t>
-  </si>
-  <si>
-    <t>110.38128643153526</t>
-  </si>
-  <si>
-    <t>Jl. Kaliurang Km 5.6 Rt 01 Rw 01, Dk Manggung Kel, Manggung, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>08.00-23.00</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/hFHpxtCSXm4rSsPWA</t>
-  </si>
-  <si>
-    <t>M036.jpg</t>
-  </si>
-  <si>
-    <t>-7.739846624846841</t>
-  </si>
-  <si>
-    <t>110.40240078104064</t>
-  </si>
-  <si>
-    <t>Jl. Raya Manukan Kel No.Rt. 05, RW.Iv, Manukan, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/LLdHixFNGbzeXS5M9</t>
-  </si>
-  <si>
-    <t>M037.jpg</t>
-  </si>
-  <si>
-    <t>-7.741377499571684</t>
-  </si>
-  <si>
-    <t>110.41098384994527</t>
-  </si>
-  <si>
-    <t>Jl. Candi Gebang, Jetis, Wedomartani, Kec. Ngemplak, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55282</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/gWeNBEXEgqUYBySc8</t>
-  </si>
-  <si>
-    <t>M038.jpg</t>
-  </si>
-  <si>
-    <t>-7.750902817325119</t>
-  </si>
-  <si>
-    <t>110.3984525693445</t>
-  </si>
-  <si>
-    <t>Jl. Anggajaya 2 Kel No.75B, RT.04/RW.09, Sanggrahan, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>3.0/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/VfSbdzbDWi5UdNs68</t>
-  </si>
-  <si>
-    <t>M039.jpg</t>
-  </si>
-  <si>
-    <t>-7.756502140675588</t>
-  </si>
-  <si>
-    <t>110.40329998540003</t>
-  </si>
-  <si>
-    <t>Jl. Ring Road Utara No.160, Perumnas Condong Catur, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/2HTUZCfFgRj1mc689</t>
-  </si>
-  <si>
-    <t>M040.jpg</t>
-  </si>
-  <si>
-    <t>-7.758410435461992</t>
-  </si>
-  <si>
-    <t>110.40632643116737</t>
-  </si>
-  <si>
-    <t>Jl. Ring Road Utara No.Kel, Perumnas Condong Catur, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/biQStQVcheFZL4fN8</t>
-  </si>
-  <si>
-    <t>M041.jpg</t>
-  </si>
-  <si>
-    <t>-7.760641876439936</t>
-  </si>
-  <si>
-    <t>110.41567434281566</t>
-  </si>
-  <si>
-    <t>Jalan Ringroad Utara, Mancasan Kidul, Ngropoh, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>07.00-23.00</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/EpAysQ3WXUkqcna2A</t>
-  </si>
-  <si>
-    <t>M042.jpg</t>
-  </si>
-  <si>
-    <t>-7.7729243349685735</t>
-  </si>
-  <si>
-    <t>110.41312950657385</t>
-  </si>
-  <si>
-    <t>Jl. Babarsari Ct 19, Kel, Tambak Bayan, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>10.00-21.00</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/wJ3bHdk31Wbs57Jf7</t>
-  </si>
-  <si>
-    <t>M043.jpg</t>
-  </si>
-  <si>
-    <t>-7.76691020590576</t>
-  </si>
-  <si>
-    <t>110.40986108656197</t>
-  </si>
-  <si>
-    <t>Jl. Seturan Raya No.Kel Blok C No.5, Kledokan, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>2.3/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/pLVtxDoDFYRnXBfS7</t>
-  </si>
-  <si>
-    <t>M044.jpg</t>
-  </si>
-  <si>
-    <t>-7.763377003772743</t>
-  </si>
-  <si>
-    <t>110.40540371062711</t>
-  </si>
-  <si>
-    <t>Jl. Perumnas No.106, Dabag, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/69ffCYJN4SpQF2DW8</t>
-  </si>
-  <si>
-    <t>M045.jpg</t>
-  </si>
-  <si>
-    <t>-7.765364433687017</t>
-  </si>
-  <si>
-    <t>110.40243212676862</t>
-  </si>
-  <si>
-    <t>Jl. Wahid Hasyim No.Kel, RW.No: 6, Dabag, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/brniKuRnRZYaVX8F6</t>
-  </si>
-  <si>
-    <t>M046.jpg</t>
-  </si>
-  <si>
-    <t>-7.761536782621959</t>
-  </si>
-  <si>
-    <t>110.39559748366851</t>
-  </si>
-  <si>
-    <t>Gg. Jemb. Merah Kel No.103 A, RT.04/RW.06, Soropadan, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>09.00-22.00</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/bJxupU96DGrmDFjY7</t>
-  </si>
-  <si>
-    <t>M047.jpg</t>
-  </si>
-  <si>
-    <t>-7.770126662899377</t>
-  </si>
-  <si>
-    <t>110.38942776021663</t>
-  </si>
-  <si>
-    <t>Jl. Affandi Kel No.21 A, Santren, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>06.00-22.00</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/mDaN88tVqkM2FXoNA</t>
-  </si>
-  <si>
-    <t>M048.jpg</t>
-  </si>
-  <si>
-    <t>-7.776009658807369</t>
-  </si>
-  <si>
-    <t>110.3854961371992</t>
-  </si>
-  <si>
-    <t>Jl. Colombo 13/30, Desa Kel No.Rt. 04, RT.04/RW.02, Samirono, Caturtunggal, Depok, Sleman Regency, Special Region of Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/nvtwnSp9Uzx7WN8fA</t>
-  </si>
-  <si>
-    <t>M049.jpg</t>
-  </si>
-  <si>
-    <t>-7.774319145981829</t>
-  </si>
-  <si>
-    <t>110.39359100168197</t>
-  </si>
-  <si>
-    <t>Jl. Pringgodani Kel No.8, RT.19/RW.14, Mrican, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>2.2/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/XkByBoZZxTmunCKW6</t>
-  </si>
-  <si>
-    <t>M050.jpg</t>
-  </si>
-  <si>
-    <t>-7.770417559044908</t>
-  </si>
-  <si>
-    <t>110.40143654905349</t>
-  </si>
-  <si>
-    <t>Jl. Nologaten No.187, Dabag, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/apZbFsSCBr6EYLRT9</t>
-  </si>
-  <si>
-    <t>M051.jpg</t>
-  </si>
-  <si>
-    <t>-7.771095549600947</t>
-  </si>
-  <si>
-    <t>110.40178587703575</t>
-  </si>
-  <si>
-    <t>Dkh.Dabag, Jl. Wahid Hasyim Kel No.11, RT.008/RW.027, Dabag, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/VrgpLuxUPrsUphA38</t>
-  </si>
-  <si>
-    <t>M052.jpg</t>
-  </si>
-  <si>
-    <t>-7.77159183805787</t>
-  </si>
-  <si>
-    <t>110.40423466690144</t>
-  </si>
-  <si>
-    <t>Jl. Perumnas No. 85, Komplek Graha Strategic Blok A3 / A4 Kel, Dabag, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>09.00-21.00</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/XafqcjhRZgeAV1c77</t>
-  </si>
-  <si>
-    <t>M053.jpg</t>
-  </si>
-  <si>
-    <t>-7.763065828579438</t>
-  </si>
-  <si>
-    <t>110.40756256677764</t>
-  </si>
-  <si>
-    <t>Jl. Pintu Selatan UPN No.3, Ngropoh, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/sXSR64xef5eu8CCL8</t>
-  </si>
-  <si>
-    <t>M054.jpg</t>
-  </si>
-  <si>
-    <t>-7.760820680118197</t>
-  </si>
-  <si>
-    <t>110.40799963210634</t>
-  </si>
-  <si>
-    <t>Universitas Pembangunan Nasional "Veteran, Ngropoh, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
     <t>Senin-Sabtu</t>
   </si>
   <si>
-    <t>08.00-20.00</t>
-  </si>
-  <si>
-    <t>5.0/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/K8a86JiuLDtJy7Z98</t>
-  </si>
-  <si>
-    <t>M055.jpg</t>
-  </si>
-  <si>
-    <t>Jl. Pintu Selatan UPN Jl. Seturan Raya, Ngropoh, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/kU2uvJp8YCZwLjSG6</t>
-  </si>
-  <si>
-    <t>M056.jpg</t>
-  </si>
-  <si>
-    <t>-7.770692904079514</t>
-  </si>
-  <si>
-    <t>110.40972750368472</t>
-  </si>
-  <si>
-    <t>Depok Sports Center, Jl. Seturan Raya Kav.IV, Kledokan, Caturtunggal, Depok, Sleman Regency, Special Region of Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>10.00-22.00</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/2qZxGGcCcJtkY1g39</t>
-  </si>
-  <si>
-    <t>M057.jpg</t>
-  </si>
-  <si>
-    <t>-7.758533872322579</t>
-  </si>
-  <si>
-    <t>110.41282053517918</t>
-  </si>
-  <si>
-    <t>Jl. Cendrawasih No.90b, Ngringin, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>06.00-21.00</t>
-  </si>
-  <si>
-    <t>4.6/5.0</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/Whhj3uPkLXoK1M1Y7</t>
-  </si>
-  <si>
-    <t>M058.jpg</t>
-  </si>
-  <si>
-    <t>-7.7496373777161125</t>
-  </si>
-  <si>
-    <t>110.41077505786859</t>
-  </si>
-  <si>
-    <t>Jl. Candi Gebang, Dero, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>07.30-21.30</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/FLzj6sN18SWF7E4C6</t>
-  </si>
-  <si>
-    <t>M059.jpg</t>
-  </si>
-  <si>
-    <t>-7.782078923814419</t>
-  </si>
-  <si>
-    <t>110.41443305384664</t>
-  </si>
-  <si>
-    <t>Jl. Raya Solo - Yogyakarta Jl. Babarsari No.KM. 7, Janti, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>08.30-21.30</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/8eNFKmsacyiLPxVA9</t>
-  </si>
-  <si>
-    <t>M060.jpg</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -1089,9 +105,6 @@
     <t>M001</t>
   </si>
   <si>
-    <t>Indomaret Jl Kaliurang KM 8.3</t>
-  </si>
-  <si>
     <t>M002</t>
   </si>
   <si>
@@ -1167,9 +180,6 @@
     <t>M014</t>
   </si>
   <si>
-    <t>Indomaret Tantular No. 409 (FY5C)</t>
-  </si>
-  <si>
     <t>M015</t>
   </si>
   <si>
@@ -1290,9 +300,6 @@
     <t>M035</t>
   </si>
   <si>
-    <t>Alfamart Kaliurang KM 8.1</t>
-  </si>
-  <si>
     <t>M036</t>
   </si>
   <si>
@@ -1434,22 +441,1015 @@
     <t>Manna Kampus (Mirota Kampus) Babarsari</t>
   </si>
   <si>
-    <t>-7.7638932991633425</t>
-  </si>
-  <si>
-    <t>110.40900868735301</t>
-  </si>
-  <si>
-    <t>-7.764463124084063</t>
-  </si>
-  <si>
-    <t>110.41105130801496</t>
-  </si>
-  <si>
-    <t>-7.76318000437515</t>
-  </si>
-  <si>
-    <t>110.40996607313167</t>
+    <t>Indomaret Jl Kaliurang KM 8,3</t>
+  </si>
+  <si>
+    <t>-7,733752545117078</t>
+  </si>
+  <si>
+    <t>110,39419756395505</t>
+  </si>
+  <si>
+    <t>Jl, Kaliurang Km 8,3 Prujukan Rt 2/3 Sinduharjo, Tambakan, Sinduharjo, Sleman, Sleman Regency, Special Region of Yogyakarta 55581</t>
+  </si>
+  <si>
+    <t>07,00-22,00</t>
+  </si>
+  <si>
+    <t>3,3/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/HvGAw3yRT4Z41LoZ7</t>
+  </si>
+  <si>
+    <t>M001,jpg</t>
+  </si>
+  <si>
+    <t>-7,749447245716337</t>
+  </si>
+  <si>
+    <t>110,38578306135572</t>
+  </si>
+  <si>
+    <t>Jl, Kaliurang, Kentungan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>3,8/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/hrcCoQa6NbGUDMs58</t>
+  </si>
+  <si>
+    <t>M002,jpg</t>
+  </si>
+  <si>
+    <t>-7,756250064506058</t>
+  </si>
+  <si>
+    <t>110,37932712120767</t>
+  </si>
+  <si>
+    <t>Jl, Kaliurang, Km 5, 2, Catur Tunggal, Kec, Depok, Jl, Kaliurang No,27, Karang Wuni, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55284</t>
+  </si>
+  <si>
+    <t>07,00-22,01</t>
+  </si>
+  <si>
+    <t>3,9/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/yuGPo2Cdzm1cwWWFA</t>
+  </si>
+  <si>
+    <t>M003,jpg</t>
+  </si>
+  <si>
+    <t>-7,752217570012537</t>
+  </si>
+  <si>
+    <t>110,38218871514682</t>
+  </si>
+  <si>
+    <t>Jalan Pandega Marta No, 1 Sarimulyo Manggung, Manggung, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>3,4/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/y7eFw3yPzy8XiyVH8</t>
+  </si>
+  <si>
+    <t>M004,jpg</t>
+  </si>
+  <si>
+    <t>-7,765916891413229</t>
+  </si>
+  <si>
+    <t>110,39147146767357</t>
+  </si>
+  <si>
+    <t>Jl, Affandi No,31a, Karang Gayam, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>3,1/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/FcK4Bx17jAYCpJhX8</t>
+  </si>
+  <si>
+    <t>M005,jpg</t>
+  </si>
+  <si>
+    <t>-7,758056400724876</t>
+  </si>
+  <si>
+    <t>110,39494223275801</t>
+  </si>
+  <si>
+    <t>Jl, Affandi No,23, Soropadan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/gk9yBhy1XfxyNVp5A</t>
+  </si>
+  <si>
+    <t>M006,jpg</t>
+  </si>
+  <si>
+    <t>-7,752947002982559</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 110,39672719765858</t>
+  </si>
+  <si>
+    <t>Jl, Anggajaya 1 No,282, Sanggrahan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>07,00-22,02</t>
+  </si>
+  <si>
+    <t>3,2/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/U18wT9wYGWXs2n1dA</t>
+  </si>
+  <si>
+    <t>M007,jpg</t>
+  </si>
+  <si>
+    <t>-7,749895190158755</t>
+  </si>
+  <si>
+    <t>110,39808053648082</t>
+  </si>
+  <si>
+    <t>Jl, Sukoharjo No,133 A, Sanggrahan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>4,1/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/ACN1JDZCWuDx7x3c9</t>
+  </si>
+  <si>
+    <t>M008,jpg</t>
+  </si>
+  <si>
+    <t>-7,7425767277541</t>
+  </si>
+  <si>
+    <t>110,39742175575905</t>
+  </si>
+  <si>
+    <t>Jl, Rajawali Raya No,32, Sanggrahan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>4,3/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/vtbQovKZLG9tKWRM9</t>
+  </si>
+  <si>
+    <t>M009,jpg</t>
+  </si>
+  <si>
+    <t>-7,749210435076886</t>
+  </si>
+  <si>
+    <t>110,40617648604177</t>
+  </si>
+  <si>
+    <t>Jl, Cemp, No,60, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>4,5/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/Nj7awyKrLigPrPDt5</t>
+  </si>
+  <si>
+    <t>M010,jpg</t>
+  </si>
+  <si>
+    <t>-7,748732158171262</t>
+  </si>
+  <si>
+    <t>110,41114301296018</t>
+  </si>
+  <si>
+    <t>Jl, Nusa Indah No,249, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/UWnDTdNhGfGvs4cf6</t>
+  </si>
+  <si>
+    <t>M011,jpg</t>
+  </si>
+  <si>
+    <t>-7,752859025575523</t>
+  </si>
+  <si>
+    <t>110,40985387164312</t>
+  </si>
+  <si>
+    <t>Jl, Nusa Indah II No,50, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>2,7/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/wtP4be5hRqgrhRSLA</t>
+  </si>
+  <si>
+    <t>M012,jpg</t>
+  </si>
+  <si>
+    <t>-7,765337640697154</t>
+  </si>
+  <si>
+    <t>110,39597081132904</t>
+  </si>
+  <si>
+    <t>JL, Empu Tantular, No, 106, Pringwulung, Condongcatur, Depok, Jl, Tantular No,103, Kaliwaru, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>3,5/5/0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/BFdQ2TDQ9pBMcoAX8</t>
+  </si>
+  <si>
+    <t>M013,jpg</t>
+  </si>
+  <si>
+    <t>Indomaret Tantular No, 409 (FY5C)</t>
+  </si>
+  <si>
+    <t>-7,769195812965372</t>
+  </si>
+  <si>
+    <t>110,3954706508378</t>
+  </si>
+  <si>
+    <t>Jl, Tantular Selatan, Pringwulung, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>4,2/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/x2AwyBvdkzFEaSBq6</t>
+  </si>
+  <si>
+    <t>M014,jpg</t>
+  </si>
+  <si>
+    <t>-7,766357839864531</t>
+  </si>
+  <si>
+    <t>110,40251671938006</t>
+  </si>
+  <si>
+    <t>Jl, Wahid Hasyim No,5, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/RnsoQmriB1m6i3AZ8</t>
+  </si>
+  <si>
+    <t>M015,jpg</t>
+  </si>
+  <si>
+    <t>-7,769020449248469</t>
+  </si>
+  <si>
+    <t>110,4051622426191</t>
+  </si>
+  <si>
+    <t>Jl, Perumnas No,8, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/7pUGd4KNk2rEpYPh9</t>
+  </si>
+  <si>
+    <t>M016,jpg</t>
+  </si>
+  <si>
+    <t>-7,764893740448012</t>
+  </si>
+  <si>
+    <t>110,40570764856093</t>
+  </si>
+  <si>
+    <t>Indomaret, Jl, Perumnas, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>3,6/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/i2NX2in6kMciJJ2f8</t>
+  </si>
+  <si>
+    <t>M017,jpg</t>
+  </si>
+  <si>
+    <t>-7,7638932991633425</t>
+  </si>
+  <si>
+    <t>110,40900868735301</t>
+  </si>
+  <si>
+    <t>Jl, Pintu Selatan UPN, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/yiqGLnZVyKNjwWkj6?g_st=ac</t>
+  </si>
+  <si>
+    <t>M018,png</t>
+  </si>
+  <si>
+    <t>-7,764463124084063</t>
+  </si>
+  <si>
+    <t>110,41105130801496</t>
+  </si>
+  <si>
+    <t>Ruko Pulohdadi, Jl, Seturan Raya Blok A2, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/YaX6UcnU3gT1rtmEA</t>
+  </si>
+  <si>
+    <t>M019,jpg</t>
+  </si>
+  <si>
+    <t>-7,769901074159813</t>
+  </si>
+  <si>
+    <t>110,4098548994134</t>
+  </si>
+  <si>
+    <t>Jl, Seturan Raya, RT,4/RW,2, Kledokan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/rf4pXZ5op64fGaEM8</t>
+  </si>
+  <si>
+    <t>M020,jpg</t>
+  </si>
+  <si>
+    <t>-7,744073071243356</t>
+  </si>
+  <si>
+    <t>110,41459663470026</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/fufaosvrsao483j99</t>
+  </si>
+  <si>
+    <t>M021,jpg</t>
+  </si>
+  <si>
+    <t>-7,769789454884158</t>
+  </si>
+  <si>
+    <t>110,402001372579</t>
+  </si>
+  <si>
+    <t>Jl, Wahid Hasyim No,130Dabag, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/x4QJfLUQkhHWqZ137</t>
+  </si>
+  <si>
+    <t>M022,jpg</t>
+  </si>
+  <si>
+    <t>-7,781287170789081</t>
+  </si>
+  <si>
+    <t>110,41401363389748</t>
+  </si>
+  <si>
+    <t>Jl, Babarsari No,11, Janti, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/E5VGMWFMkCHfZriL7</t>
+  </si>
+  <si>
+    <t>M023,jpg</t>
+  </si>
+  <si>
+    <t>-7,76074441972423</t>
+  </si>
+  <si>
+    <t>110,42005087958772</t>
+  </si>
+  <si>
+    <t>Jl, P, Puger 1 No,2, Pugeran, Maguwoharjo, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>2,5/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/6ptXJdnoMD4LfxAm6</t>
+  </si>
+  <si>
+    <t>M024,jpg</t>
+  </si>
+  <si>
+    <t>-7,771760619476064</t>
+  </si>
+  <si>
+    <t>110,40402001483787</t>
+  </si>
+  <si>
+    <t>Jl, Perumnas, Nologaten, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/kQbgHLjC9CHXDVUd8</t>
+  </si>
+  <si>
+    <t>M025,jpg</t>
+  </si>
+  <si>
+    <t>-7,767021127082602</t>
+  </si>
+  <si>
+    <t>110,39044549226743</t>
+  </si>
+  <si>
+    <t>Jl, Affandi, Karang Gayam, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/D3hU9pNhRSwwefzd8</t>
+  </si>
+  <si>
+    <t>M026,jpg</t>
+  </si>
+  <si>
+    <t>-7,756085604225498</t>
+  </si>
+  <si>
+    <t>110,3943908636679</t>
+  </si>
+  <si>
+    <t>Jl, Anggajaya III No,66, Gejayan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>4,4/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/SaS1WCo3QxG3jwW48</t>
+  </si>
+  <si>
+    <t>M027,jpg</t>
+  </si>
+  <si>
+    <t>-7,7757624268869865</t>
+  </si>
+  <si>
+    <t>110,3946526972518</t>
+  </si>
+  <si>
+    <t>Jl, Petung No,7, Papringan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/qQN4SrSZBWcQTHjU8</t>
+  </si>
+  <si>
+    <t>M028,jpg</t>
+  </si>
+  <si>
+    <t>-7,77254523832928</t>
+  </si>
+  <si>
+    <t>110,41586671232616</t>
+  </si>
+  <si>
+    <t>Jl, Babarsari, Tambak Bayan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/jZqh5aGaYjRwjM1Q9</t>
+  </si>
+  <si>
+    <t>M029,jpg</t>
+  </si>
+  <si>
+    <t>-7,7750608431802695</t>
+  </si>
+  <si>
+    <t>110,41612060615564</t>
+  </si>
+  <si>
+    <t>Jl, Babarsari No,23DTambak Bayan, Tambak Bayan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/FKLhFzTtUv9Svu8X8</t>
+  </si>
+  <si>
+    <t>M030,jpg</t>
+  </si>
+  <si>
+    <t>-7,780008155389338</t>
+  </si>
+  <si>
+    <t>110,41434334934921</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/SXgbsSj6UDL5eM7v7</t>
+  </si>
+  <si>
+    <t>M031,jpg</t>
+  </si>
+  <si>
+    <t>-7,778918074660311</t>
+  </si>
+  <si>
+    <t>110,40850379127096</t>
+  </si>
+  <si>
+    <t>Jl, Kapas No,7, Ngentak, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>4,0/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/v5r9juBWxgPk1Bog6</t>
+  </si>
+  <si>
+    <t>M032,jpg</t>
+  </si>
+  <si>
+    <t>-7,782104456519171</t>
+  </si>
+  <si>
+    <t>110,41045031063037</t>
+  </si>
+  <si>
+    <t>Jl, Raya Janti No,3, Gowok, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/wWMHH899sSHvLsLJ7</t>
+  </si>
+  <si>
+    <t>M033,jpg</t>
+  </si>
+  <si>
+    <t>-7,730661259789763</t>
+  </si>
+  <si>
+    <t>110,39141445284271</t>
+  </si>
+  <si>
+    <t>Jl, Damai Dk, Prujakan, RT,01/RW,32, Tambakan, Sinduharjo, Kec, Ngaglik, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55581</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/Hkk5NCU4DLaffHSk8</t>
+  </si>
+  <si>
+    <t>M034,jpg</t>
+  </si>
+  <si>
+    <t>Alfamart Kaliurang KM 8,1</t>
+  </si>
+  <si>
+    <t>-7,733212770145344</t>
+  </si>
+  <si>
+    <t>110,39450435764837</t>
+  </si>
+  <si>
+    <t>Jl, Kaliurang 8,1 No, 72, RT,04/RW,33, Tambakan, Sinduharjo, Kec, Ngaglik, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55581</t>
+  </si>
+  <si>
+    <t>3,7/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/ZP2CpU3Z8afNahNt5</t>
+  </si>
+  <si>
+    <t>M035,jpg</t>
+  </si>
+  <si>
+    <t>-7,752603744250776</t>
+  </si>
+  <si>
+    <t>110,38128643153526</t>
+  </si>
+  <si>
+    <t>Jl, Kaliurang Km 5,6 Rt 01 Rw 01, Dk Manggung Kel, Manggung, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>08,00-23,00</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/hFHpxtCSXm4rSsPWA</t>
+  </si>
+  <si>
+    <t>M036,jpg</t>
+  </si>
+  <si>
+    <t>-7,739846624846841</t>
+  </si>
+  <si>
+    <t>110,40240078104064</t>
+  </si>
+  <si>
+    <t>Jl, Raya Manukan Kel No,Rt, 05, RW,Iv, Manukan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/LLdHixFNGbzeXS5M9</t>
+  </si>
+  <si>
+    <t>M037,jpg</t>
+  </si>
+  <si>
+    <t>-7,741377499571684</t>
+  </si>
+  <si>
+    <t>110,41098384994527</t>
+  </si>
+  <si>
+    <t>Jl, Candi Gebang, Jetis, Wedomartani, Kec, Ngemplak, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55282</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/gWeNBEXEgqUYBySc8</t>
+  </si>
+  <si>
+    <t>M038,jpg</t>
+  </si>
+  <si>
+    <t>-7,750902817325119</t>
+  </si>
+  <si>
+    <t>110,3984525693445</t>
+  </si>
+  <si>
+    <t>Jl, Anggajaya 2 Kel No,75B, RT,04/RW,09, Sanggrahan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>3,0/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/VfSbdzbDWi5UdNs68</t>
+  </si>
+  <si>
+    <t>M039,jpg</t>
+  </si>
+  <si>
+    <t>-7,756502140675588</t>
+  </si>
+  <si>
+    <t>110,40329998540003</t>
+  </si>
+  <si>
+    <t>Jl, Ring Road Utara No,160, Perumnas Condong Catur, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/2HTUZCfFgRj1mc689</t>
+  </si>
+  <si>
+    <t>M040,jpg</t>
+  </si>
+  <si>
+    <t>-7,758410435461992</t>
+  </si>
+  <si>
+    <t>110,40632643116737</t>
+  </si>
+  <si>
+    <t>Jl, Ring Road Utara No,Kel, Perumnas Condong Catur, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/biQStQVcheFZL4fN8</t>
+  </si>
+  <si>
+    <t>M041,jpg</t>
+  </si>
+  <si>
+    <t>-7,760641876439936</t>
+  </si>
+  <si>
+    <t>110,41567434281566</t>
+  </si>
+  <si>
+    <t>Jalan Ringroad Utara, Mancasan Kidul, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>07,00-23,00</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/EpAysQ3WXUkqcna2A</t>
+  </si>
+  <si>
+    <t>M042,jpg</t>
+  </si>
+  <si>
+    <t>-7,7729243349685735</t>
+  </si>
+  <si>
+    <t>110,41312950657385</t>
+  </si>
+  <si>
+    <t>Jl, Babarsari Ct 19, Kel, Tambak Bayan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>10,00-21,00</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/wJ3bHdk31Wbs57Jf7</t>
+  </si>
+  <si>
+    <t>M043,jpg</t>
+  </si>
+  <si>
+    <t>-7,76691020590576</t>
+  </si>
+  <si>
+    <t>110,40986108656197</t>
+  </si>
+  <si>
+    <t>Jl, Seturan Raya No,Kel Blok C No,5, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>2,3/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/pLVtxDoDFYRnXBfS7</t>
+  </si>
+  <si>
+    <t>M044,jpg</t>
+  </si>
+  <si>
+    <t>-7,763377003772743</t>
+  </si>
+  <si>
+    <t>110,40540371062711</t>
+  </si>
+  <si>
+    <t>Jl, Perumnas No,106, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/69ffCYJN4SpQF2DW8</t>
+  </si>
+  <si>
+    <t>M045,jpg</t>
+  </si>
+  <si>
+    <t>-7,765364433687017</t>
+  </si>
+  <si>
+    <t>110,40243212676862</t>
+  </si>
+  <si>
+    <t>Jl, Wahid Hasyim No,Kel, RW,No: 6, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/brniKuRnRZYaVX8F6</t>
+  </si>
+  <si>
+    <t>M046,jpg</t>
+  </si>
+  <si>
+    <t>-7,761536782621959</t>
+  </si>
+  <si>
+    <t>110,39559748366851</t>
+  </si>
+  <si>
+    <t>Gg, Jemb, Merah Kel No,103 A, RT,04/RW,06, Soropadan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>09,00-22,00</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/bJxupU96DGrmDFjY7</t>
+  </si>
+  <si>
+    <t>M047,jpg</t>
+  </si>
+  <si>
+    <t>-7,770126662899377</t>
+  </si>
+  <si>
+    <t>110,38942776021663</t>
+  </si>
+  <si>
+    <t>Jl, Affandi Kel No,21 A, Santren, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>06,00-22,00</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/mDaN88tVqkM2FXoNA</t>
+  </si>
+  <si>
+    <t>M048,jpg</t>
+  </si>
+  <si>
+    <t>-7,776009658807369</t>
+  </si>
+  <si>
+    <t>110,3854961371992</t>
+  </si>
+  <si>
+    <t>Jl, Colombo 13/30, Desa Kel No,Rt, 04, RT,04/RW,02, Samirono, Caturtunggal, Depok, Sleman Regency, Special Region of Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/nvtwnSp9Uzx7WN8fA</t>
+  </si>
+  <si>
+    <t>M049,jpg</t>
+  </si>
+  <si>
+    <t>-7,774319145981829</t>
+  </si>
+  <si>
+    <t>110,39359100168197</t>
+  </si>
+  <si>
+    <t>Jl, Pringgodani Kel No,8, RT,19/RW,14, Mrican, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>2,2/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/XkByBoZZxTmunCKW6</t>
+  </si>
+  <si>
+    <t>M050,jpg</t>
+  </si>
+  <si>
+    <t>-7,770417559044908</t>
+  </si>
+  <si>
+    <t>110,40143654905349</t>
+  </si>
+  <si>
+    <t>Jl, Nologaten No,187, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/apZbFsSCBr6EYLRT9</t>
+  </si>
+  <si>
+    <t>M051,jpg</t>
+  </si>
+  <si>
+    <t>-7,771095549600947</t>
+  </si>
+  <si>
+    <t>110,40178587703575</t>
+  </si>
+  <si>
+    <t>Dkh,Dabag, Jl, Wahid Hasyim Kel No,11, RT,008/RW,027, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/VrgpLuxUPrsUphA38</t>
+  </si>
+  <si>
+    <t>M052,jpg</t>
+  </si>
+  <si>
+    <t>-7,77159183805787</t>
+  </si>
+  <si>
+    <t>110,40423466690144</t>
+  </si>
+  <si>
+    <t>Jl, Perumnas No, 85, Komplek Graha Strategic Blok A3 / A4 Kel, Dabag, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>09,00-21,00</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/XafqcjhRZgeAV1c77</t>
+  </si>
+  <si>
+    <t>M053,jpg</t>
+  </si>
+  <si>
+    <t>-7,763065828579438</t>
+  </si>
+  <si>
+    <t>110,40756256677764</t>
+  </si>
+  <si>
+    <t>Jl, Pintu Selatan UPN No,3, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/sXSR64xef5eu8CCL8</t>
+  </si>
+  <si>
+    <t>M054,jpg</t>
+  </si>
+  <si>
+    <t>-7,760820680118197</t>
+  </si>
+  <si>
+    <t>110,40799963210634</t>
+  </si>
+  <si>
+    <t>Universitas Pembangunan Nasional "Veteran, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>08,00-20,00</t>
+  </si>
+  <si>
+    <t>5,0/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/K8a86JiuLDtJy7Z98</t>
+  </si>
+  <si>
+    <t>M055,jpg</t>
+  </si>
+  <si>
+    <t>-7,76318000437515</t>
+  </si>
+  <si>
+    <t>110,40996607313167</t>
+  </si>
+  <si>
+    <t>Jl, Pintu Selatan UPN Jl, Seturan Raya, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/kU2uvJp8YCZwLjSG6</t>
+  </si>
+  <si>
+    <t>M056,jpg</t>
+  </si>
+  <si>
+    <t>-7,770692904079514</t>
+  </si>
+  <si>
+    <t>110,40972750368472</t>
+  </si>
+  <si>
+    <t>Depok Sports Center, Jl, Seturan Raya Kav,IV, Kledokan, Caturtunggal, Depok, Sleman Regency, Special Region of Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>10,00-22,00</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/2qZxGGcCcJtkY1g39</t>
+  </si>
+  <si>
+    <t>M057,jpg</t>
+  </si>
+  <si>
+    <t>-7,758533872322579</t>
+  </si>
+  <si>
+    <t>110,41282053517918</t>
+  </si>
+  <si>
+    <t>Jl, Cendrawasih No,90b, Ngringin, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>06,00-21,00</t>
+  </si>
+  <si>
+    <t>4,6/5,0</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/Whhj3uPkLXoK1M1Y7</t>
+  </si>
+  <si>
+    <t>M058,jpg</t>
+  </si>
+  <si>
+    <t>-7,7496373777161125</t>
+  </si>
+  <si>
+    <t>110,41077505786859</t>
+  </si>
+  <si>
+    <t>Jl, Candi Gebang, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>07,30-21,30</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/FLzj6sN18SWF7E4C6</t>
+  </si>
+  <si>
+    <t>M059,jpg</t>
+  </si>
+  <si>
+    <t>-7,782078923814419</t>
+  </si>
+  <si>
+    <t>110,41443305384664</t>
+  </si>
+  <si>
+    <t>Jl, Raya Solo - Yogyakarta Jl, Babarsari No,KM, 7, Janti, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>08,30-21,30</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/8eNFKmsacyiLPxVA9</t>
+  </si>
+  <si>
+    <t>M060,jpg</t>
   </si>
 </sst>
 </file>
@@ -1477,45 +1477,38 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1577,10 +1570,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1589,21 +1582,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1940,10 +1933,10 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>349</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1984,2706 +1977,2717 @@
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>350</v>
+        <v>22</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>351</v>
+        <v>135</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>14</v>
+        <v>137</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="N2" s="11" t="s">
         <v>15</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>352</v>
+        <v>23</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>353</v>
+        <v>24</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>25</v>
+        <v>145</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>26</v>
+        <v>146</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>27</v>
+        <v>147</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>354</v>
+        <v>25</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>355</v>
+        <v>26</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>29</v>
+        <v>149</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>33</v>
+        <v>153</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>34</v>
+        <v>154</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>356</v>
+        <v>27</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>357</v>
+        <v>28</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>38</v>
+        <v>158</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I5" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>42</v>
+        <v>161</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>358</v>
+        <v>29</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>359</v>
+        <v>30</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>44</v>
+        <v>162</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>45</v>
+        <v>163</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>46</v>
+        <v>164</v>
       </c>
       <c r="G6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I6" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>47</v>
+        <v>165</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>48</v>
+        <v>166</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>49</v>
+        <v>167</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>360</v>
+        <v>31</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>361</v>
+        <v>32</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>50</v>
+        <v>168</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>52</v>
+        <v>170</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>53</v>
+        <v>171</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>362</v>
+        <v>33</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>363</v>
+        <v>34</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>55</v>
+        <v>173</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>57</v>
+        <v>175</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>59</v>
+        <v>177</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>60</v>
+        <v>178</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>61</v>
+        <v>179</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>364</v>
+        <v>35</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>365</v>
+        <v>36</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>62</v>
+        <v>180</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>64</v>
+        <v>182</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>66</v>
+        <v>184</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>67</v>
+        <v>185</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>366</v>
+        <v>37</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>367</v>
+        <v>38</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>68</v>
+        <v>186</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>69</v>
+        <v>187</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>70</v>
+        <v>188</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>368</v>
+        <v>39</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>369</v>
+        <v>40</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>74</v>
+        <v>192</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>75</v>
+        <v>193</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>76</v>
+        <v>194</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>370</v>
+        <v>41</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>371</v>
+        <v>42</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>33</v>
+        <v>153</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>372</v>
+        <v>43</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>373</v>
+        <v>44</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>85</v>
+        <v>203</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>86</v>
+        <v>204</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>87</v>
+        <v>205</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>88</v>
+        <v>206</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>89</v>
+        <v>207</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>90</v>
+        <v>208</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>374</v>
+        <v>45</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>375</v>
+        <v>46</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>91</v>
+        <v>209</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>92</v>
+        <v>210</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>93</v>
+        <v>211</v>
       </c>
       <c r="G14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I14" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>94</v>
+        <v>212</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>96</v>
+        <v>214</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>376</v>
+        <v>47</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>377</v>
+        <v>215</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>97</v>
+        <v>216</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>98</v>
+        <v>217</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>99</v>
+        <v>218</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>100</v>
+        <v>219</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>101</v>
+        <v>220</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>102</v>
+        <v>221</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>378</v>
+        <v>48</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>379</v>
+        <v>49</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>103</v>
+        <v>222</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>104</v>
+        <v>223</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>105</v>
+        <v>224</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>94</v>
+        <v>212</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>106</v>
+        <v>225</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>107</v>
+        <v>226</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>380</v>
+        <v>50</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>381</v>
+        <v>51</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>108</v>
+        <v>227</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>109</v>
+        <v>228</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>110</v>
+        <v>229</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>111</v>
+        <v>230</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>112</v>
+        <v>231</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>382</v>
+        <v>52</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>383</v>
+        <v>53</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>113</v>
+        <v>232</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>114</v>
+        <v>233</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>115</v>
+        <v>234</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>116</v>
+        <v>235</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>117</v>
+        <v>236</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>118</v>
+        <v>237</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>384</v>
+        <v>54</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>385</v>
+        <v>55</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>466</v>
+        <v>238</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>467</v>
+        <v>239</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>119</v>
+        <v>240</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>120</v>
+        <v>241</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>121</v>
+        <v>242</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>386</v>
+        <v>56</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>387</v>
+        <v>57</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>468</v>
+        <v>243</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>469</v>
+        <v>244</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>122</v>
+        <v>245</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>33</v>
+        <v>153</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>123</v>
+        <v>246</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>124</v>
+        <v>247</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>388</v>
+        <v>58</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>389</v>
+        <v>59</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>125</v>
+        <v>248</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>126</v>
+        <v>249</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>127</v>
+        <v>250</v>
       </c>
       <c r="G21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H21" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I21" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>94</v>
+        <v>212</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>128</v>
+        <v>251</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>129</v>
+        <v>252</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>390</v>
+        <v>60</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>391</v>
+        <v>61</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>130</v>
+        <v>253</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>131</v>
+        <v>254</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>100</v>
+        <v>219</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>133</v>
+        <v>255</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>392</v>
+        <v>62</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>393</v>
+        <v>63</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>135</v>
+        <v>257</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>136</v>
+        <v>258</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>137</v>
+        <v>259</v>
       </c>
       <c r="G23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H23" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I23" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>33</v>
+        <v>153</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>138</v>
+        <v>260</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>139</v>
+        <v>261</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>394</v>
+        <v>64</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>395</v>
+        <v>65</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K24" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="E24" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="L24" s="10" t="s">
-        <v>143</v>
+        <v>265</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>144</v>
+        <v>266</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>396</v>
+        <v>66</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>397</v>
+        <v>67</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>145</v>
+        <v>267</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>146</v>
+        <v>268</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>147</v>
+        <v>269</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>148</v>
+        <v>270</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>149</v>
+        <v>271</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>150</v>
+        <v>272</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>398</v>
+        <v>68</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>399</v>
+        <v>69</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>151</v>
+        <v>273</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>152</v>
+        <v>274</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>153</v>
+        <v>275</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>154</v>
+        <v>276</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>155</v>
+        <v>277</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>401</v>
+        <v>71</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>156</v>
+        <v>278</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>157</v>
+        <v>279</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>158</v>
+        <v>280</v>
       </c>
       <c r="G27" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H27" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I27" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>47</v>
+        <v>165</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>159</v>
+        <v>281</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>160</v>
+        <v>282</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>402</v>
+        <v>72</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>403</v>
+        <v>73</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>161</v>
+        <v>283</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>162</v>
+        <v>284</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>163</v>
+        <v>285</v>
       </c>
       <c r="G28" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I28" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>164</v>
+        <v>286</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>165</v>
+        <v>287</v>
       </c>
       <c r="M28" s="7" t="s">
-        <v>166</v>
+        <v>288</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>404</v>
+        <v>74</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>405</v>
+        <v>75</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>167</v>
+        <v>289</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>168</v>
+        <v>290</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>169</v>
+        <v>291</v>
       </c>
       <c r="G29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H29" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I29" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>170</v>
+        <v>292</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>171</v>
+        <v>293</v>
       </c>
       <c r="N29" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>406</v>
+        <v>76</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>407</v>
+        <v>77</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>172</v>
+        <v>294</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>173</v>
+        <v>295</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>174</v>
+        <v>296</v>
       </c>
       <c r="G30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H30" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I30" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>26</v>
+        <v>146</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>175</v>
+        <v>297</v>
       </c>
       <c r="M30" s="7" t="s">
-        <v>176</v>
+        <v>298</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>408</v>
+        <v>78</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>409</v>
+        <v>79</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>177</v>
+        <v>299</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>178</v>
+        <v>300</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>179</v>
+        <v>301</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>180</v>
+        <v>302</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>181</v>
+        <v>303</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>395</v>
+        <v>65</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>182</v>
+        <v>304</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>183</v>
+        <v>305</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>142</v>
+        <v>264</v>
       </c>
       <c r="G32" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I32" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>184</v>
+        <v>306</v>
       </c>
       <c r="M32" s="7" t="s">
-        <v>185</v>
+        <v>307</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>186</v>
+        <v>308</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>187</v>
+        <v>309</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>188</v>
+        <v>310</v>
       </c>
       <c r="G33" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H33" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I33" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>189</v>
+        <v>311</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>190</v>
+        <v>312</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>191</v>
+        <v>313</v>
       </c>
       <c r="N33" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>413</v>
+        <v>83</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>414</v>
+        <v>84</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>192</v>
+        <v>314</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>193</v>
+        <v>315</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>194</v>
+        <v>316</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>100</v>
+        <v>219</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>195</v>
+        <v>317</v>
       </c>
       <c r="M34" s="7" t="s">
-        <v>196</v>
+        <v>318</v>
       </c>
       <c r="N34" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>415</v>
+        <v>85</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>416</v>
+        <v>86</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>197</v>
+        <v>319</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>198</v>
+        <v>320</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>199</v>
+        <v>321</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>189</v>
+        <v>311</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>200</v>
+        <v>322</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>201</v>
+        <v>323</v>
       </c>
       <c r="N35" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>417</v>
+        <v>87</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>418</v>
+        <v>324</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>202</v>
+        <v>325</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>203</v>
+        <v>326</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>204</v>
+        <v>327</v>
       </c>
       <c r="G36" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H36" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I36" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>205</v>
+        <v>328</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>206</v>
+        <v>329</v>
       </c>
       <c r="M36" s="7" t="s">
-        <v>207</v>
+        <v>330</v>
       </c>
       <c r="N36" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>419</v>
+        <v>88</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>420</v>
+        <v>89</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>208</v>
+        <v>331</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>209</v>
+        <v>332</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>210</v>
+        <v>333</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>211</v>
+        <v>334</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>212</v>
+        <v>335</v>
       </c>
       <c r="M37" s="7" t="s">
-        <v>213</v>
+        <v>336</v>
       </c>
       <c r="N37" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>421</v>
+        <v>90</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>422</v>
+        <v>91</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>214</v>
+        <v>337</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>215</v>
+        <v>338</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>216</v>
+        <v>339</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>94</v>
+        <v>212</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>217</v>
+        <v>340</v>
       </c>
       <c r="M38" s="7" t="s">
-        <v>218</v>
+        <v>341</v>
       </c>
       <c r="N38" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>423</v>
+        <v>92</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>424</v>
+        <v>93</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>219</v>
+        <v>342</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>220</v>
+        <v>343</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>221</v>
+        <v>344</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>33</v>
+        <v>153</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>222</v>
+        <v>345</v>
       </c>
       <c r="M39" s="7" t="s">
-        <v>223</v>
+        <v>346</v>
       </c>
       <c r="N39" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>425</v>
+        <v>94</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>426</v>
+        <v>95</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>224</v>
+        <v>347</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>225</v>
+        <v>348</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>226</v>
+        <v>349</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>227</v>
+        <v>350</v>
       </c>
       <c r="L40" s="10" t="s">
-        <v>228</v>
+        <v>351</v>
       </c>
       <c r="M40" s="7" t="s">
-        <v>229</v>
+        <v>352</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>427</v>
+        <v>96</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>420</v>
+        <v>89</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>230</v>
+        <v>353</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>231</v>
+        <v>354</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>232</v>
+        <v>355</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="L41" s="10" t="s">
-        <v>233</v>
+        <v>356</v>
       </c>
       <c r="M41" s="7" t="s">
-        <v>234</v>
+        <v>357</v>
       </c>
       <c r="N41" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>428</v>
+        <v>97</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>429</v>
+        <v>98</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>235</v>
+        <v>358</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>236</v>
+        <v>359</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>237</v>
+        <v>360</v>
       </c>
       <c r="G42" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I42" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>47</v>
+        <v>165</v>
       </c>
       <c r="L42" s="10" t="s">
-        <v>238</v>
+        <v>361</v>
       </c>
       <c r="M42" s="7" t="s">
-        <v>239</v>
+        <v>362</v>
       </c>
       <c r="N42" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>430</v>
+        <v>99</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>431</v>
+        <v>100</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>240</v>
+        <v>363</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>241</v>
+        <v>364</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>242</v>
+        <v>365</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>243</v>
+        <v>366</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>205</v>
+        <v>328</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>244</v>
+        <v>367</v>
       </c>
       <c r="M43" s="7" t="s">
-        <v>245</v>
+        <v>368</v>
       </c>
       <c r="N43" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>432</v>
+        <v>101</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>433</v>
+        <v>102</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>246</v>
+        <v>369</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>247</v>
+        <v>370</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>248</v>
+        <v>371</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>249</v>
+        <v>372</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>148</v>
+        <v>270</v>
       </c>
       <c r="L44" s="10" t="s">
-        <v>250</v>
+        <v>373</v>
       </c>
       <c r="M44" s="7" t="s">
-        <v>251</v>
+        <v>374</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>434</v>
+        <v>103</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>420</v>
+        <v>89</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>252</v>
+        <v>375</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>253</v>
+        <v>376</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>254</v>
+        <v>377</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>255</v>
+        <v>378</v>
       </c>
       <c r="L45" s="10" t="s">
-        <v>256</v>
+        <v>379</v>
       </c>
       <c r="M45" s="7" t="s">
-        <v>257</v>
+        <v>380</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>435</v>
+        <v>104</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>436</v>
+        <v>105</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>258</v>
+        <v>381</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>259</v>
+        <v>382</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>260</v>
+        <v>383</v>
       </c>
       <c r="G46" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H46" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I46" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>148</v>
+        <v>270</v>
       </c>
       <c r="L46" s="10" t="s">
-        <v>261</v>
+        <v>384</v>
       </c>
       <c r="M46" s="7" t="s">
-        <v>262</v>
+        <v>385</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>437</v>
+        <v>106</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>438</v>
+        <v>107</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>263</v>
+        <v>386</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>264</v>
+        <v>387</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>265</v>
+        <v>388</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>116</v>
+        <v>235</v>
       </c>
       <c r="L47" s="10" t="s">
-        <v>266</v>
+        <v>389</v>
       </c>
       <c r="M47" s="7" t="s">
-        <v>267</v>
+        <v>390</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>439</v>
+        <v>108</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>440</v>
+        <v>109</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>268</v>
+        <v>391</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>269</v>
+        <v>392</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>270</v>
+        <v>393</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>271</v>
+        <v>394</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>116</v>
+        <v>235</v>
       </c>
       <c r="L48" s="10" t="s">
-        <v>272</v>
+        <v>395</v>
       </c>
       <c r="M48" s="7" t="s">
-        <v>273</v>
+        <v>396</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>441</v>
+        <v>110</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>442</v>
+        <v>111</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>274</v>
+        <v>397</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>275</v>
+        <v>398</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>276</v>
+        <v>399</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>277</v>
+        <v>400</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="L49" s="10" t="s">
-        <v>278</v>
+        <v>401</v>
       </c>
       <c r="M49" s="7" t="s">
-        <v>279</v>
+        <v>402</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>443</v>
+        <v>112</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>420</v>
+        <v>89</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>280</v>
+        <v>403</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>281</v>
+        <v>404</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>282</v>
+        <v>405</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="L50" s="10" t="s">
-        <v>283</v>
+        <v>406</v>
       </c>
       <c r="M50" s="7" t="s">
-        <v>284</v>
+        <v>407</v>
       </c>
       <c r="N50" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>444</v>
+        <v>113</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>445</v>
+        <v>114</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>285</v>
+        <v>408</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>286</v>
+        <v>409</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>287</v>
+        <v>410</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>288</v>
+        <v>411</v>
       </c>
       <c r="L51" s="10" t="s">
-        <v>289</v>
+        <v>412</v>
       </c>
       <c r="M51" s="7" t="s">
-        <v>290</v>
+        <v>413</v>
       </c>
       <c r="N51" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>446</v>
+        <v>115</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>447</v>
+        <v>116</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>291</v>
+        <v>414</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>292</v>
+        <v>415</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>293</v>
+        <v>416</v>
       </c>
       <c r="G52" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H52" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I52" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>47</v>
+        <v>165</v>
       </c>
       <c r="L52" s="16" t="s">
-        <v>294</v>
+        <v>417</v>
       </c>
       <c r="M52" s="7" t="s">
-        <v>295</v>
+        <v>418</v>
       </c>
       <c r="N52" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>448</v>
+        <v>117</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>449</v>
+        <v>118</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>296</v>
+        <v>419</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>297</v>
+        <v>420</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>298</v>
+        <v>421</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>227</v>
+        <v>350</v>
       </c>
       <c r="L53" s="16" t="s">
-        <v>299</v>
+        <v>422</v>
       </c>
       <c r="M53" s="7" t="s">
-        <v>300</v>
+        <v>423</v>
       </c>
       <c r="N53" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>450</v>
+        <v>119</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>451</v>
+        <v>120</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>301</v>
+        <v>424</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>302</v>
+        <v>425</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>303</v>
+        <v>426</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>304</v>
+        <v>427</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>148</v>
+        <v>270</v>
       </c>
       <c r="L54" s="16" t="s">
-        <v>305</v>
+        <v>428</v>
       </c>
       <c r="M54" s="7" t="s">
-        <v>306</v>
+        <v>429</v>
       </c>
       <c r="N54" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>452</v>
+        <v>121</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>453</v>
+        <v>122</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>307</v>
+        <v>430</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>308</v>
+        <v>431</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>309</v>
+        <v>432</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>189</v>
+        <v>311</v>
       </c>
       <c r="L55" s="16" t="s">
-        <v>310</v>
+        <v>433</v>
       </c>
       <c r="M55" s="7" t="s">
-        <v>311</v>
+        <v>434</v>
       </c>
       <c r="N55" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>454</v>
+        <v>123</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>455</v>
+        <v>124</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>312</v>
+        <v>435</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>313</v>
+        <v>436</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>314</v>
+        <v>437</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>315</v>
+        <v>19</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>316</v>
+        <v>438</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>317</v>
+        <v>439</v>
       </c>
       <c r="L56" s="16" t="s">
-        <v>318</v>
+        <v>440</v>
       </c>
       <c r="M56" s="7" t="s">
-        <v>319</v>
+        <v>441</v>
       </c>
       <c r="N56" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>456</v>
+        <v>125</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>457</v>
+        <v>126</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>470</v>
+        <v>442</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>471</v>
+        <v>443</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>320</v>
+        <v>444</v>
       </c>
       <c r="G57" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H57" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I57" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>227</v>
+        <v>350</v>
       </c>
       <c r="L57" s="16" t="s">
-        <v>321</v>
+        <v>445</v>
       </c>
       <c r="M57" s="7" t="s">
-        <v>322</v>
+        <v>446</v>
       </c>
       <c r="N57" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>458</v>
+        <v>127</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>459</v>
+        <v>128</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>323</v>
+        <v>447</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>324</v>
+        <v>448</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>325</v>
+        <v>449</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>326</v>
+        <v>450</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>164</v>
+        <v>286</v>
       </c>
       <c r="L58" s="16" t="s">
-        <v>327</v>
+        <v>451</v>
       </c>
       <c r="M58" s="7" t="s">
-        <v>328</v>
+        <v>452</v>
       </c>
       <c r="N58" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>460</v>
+        <v>129</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>461</v>
+        <v>130</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>329</v>
+        <v>453</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>330</v>
+        <v>454</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>331</v>
+        <v>455</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>332</v>
+        <v>456</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>333</v>
+        <v>457</v>
       </c>
       <c r="L59" s="16" t="s">
-        <v>334</v>
+        <v>458</v>
       </c>
       <c r="M59" s="7" t="s">
-        <v>335</v>
+        <v>459</v>
       </c>
       <c r="N59" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="E60" s="15" t="s">
+        <v>461</v>
+      </c>
+      <c r="F60" s="11" t="s">
         <v>462</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="G60" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="C60" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D60" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="E60" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="F60" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H60" s="11" t="s">
-        <v>339</v>
-      </c>
       <c r="I60" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>100</v>
+        <v>219</v>
       </c>
       <c r="L60" s="16" t="s">
-        <v>340</v>
+        <v>464</v>
       </c>
       <c r="M60" s="7" t="s">
-        <v>341</v>
+        <v>465</v>
       </c>
       <c r="N60" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>464</v>
+        <v>133</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>465</v>
+        <v>134</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>342</v>
+        <v>466</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>343</v>
+        <v>467</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>344</v>
+        <v>468</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>345</v>
+        <v>469</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="L61" s="16" t="s">
-        <v>346</v>
+        <v>470</v>
       </c>
       <c r="M61" s="7" t="s">
-        <v>347</v>
+        <v>471</v>
       </c>
       <c r="N61" s="11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H61" xr:uid="{5AB1C413-B544-4BC1-A663-085AE1BB7139}">
+      <formula1>"07,00-22,00,07,00-22,01,Buka 24 Jam,07,00-22,02,08,00-23,00,-,07,00-23,00,10,00-21,00,09,00-22,00,06,00-22,00,09,00-21,00,08,00-20,00,10,00-22,00,06,00-21,00,07,30-21,30,08,30-21,30"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G61" xr:uid="{A68015C9-E5EB-43AF-AEA8-7116933EBDC6}">
+      <formula1>"Senin-Minggu,-,Senin-Sabtu"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N2:N61" xr:uid="{1DC8E56B-386A-49F3-8F03-FF7304DEF1DD}">
+      <formula1>"Tidak,Ya"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
-    <hyperlink ref="L2" r:id="rId1" xr:uid="{3594373A-D036-4FB5-ACAD-735E44A8ADAF}"/>
-    <hyperlink ref="L3" r:id="rId2" xr:uid="{BEC6BA59-4B6B-4320-A680-6E513F5AFB26}"/>
-    <hyperlink ref="L4" r:id="rId3" xr:uid="{C601715E-45BF-4717-A779-6F1D68200A7E}"/>
-    <hyperlink ref="L5" r:id="rId4" xr:uid="{588B88DA-76BC-4FDD-83DD-F23F375E9AE4}"/>
-    <hyperlink ref="L6" r:id="rId5" xr:uid="{DFA19CAB-F8A9-479F-8506-6322DD0957A4}"/>
-    <hyperlink ref="L7" r:id="rId6" xr:uid="{281EE68C-435C-4361-9322-AAA8A4C4F36E}"/>
-    <hyperlink ref="L8" r:id="rId7" xr:uid="{9D45584E-F738-4F09-A69A-01BB79D37AD2}"/>
-    <hyperlink ref="L9" r:id="rId8" xr:uid="{76B0B3DE-8716-4AFD-A9E9-0A93D0F03BFF}"/>
-    <hyperlink ref="L10" r:id="rId9" xr:uid="{266CDDF0-DAE6-4A00-B471-4B4B9EDA03D9}"/>
-    <hyperlink ref="L11" r:id="rId10" xr:uid="{BC91367E-9B4C-4863-A60D-715CEB6B8AA3}"/>
-    <hyperlink ref="L12" r:id="rId11" xr:uid="{DC212539-A4C1-438D-9EA4-E433E85F69B9}"/>
-    <hyperlink ref="L13" r:id="rId12" xr:uid="{40995F5E-0354-40A0-8EC5-4417DC4E4ADF}"/>
-    <hyperlink ref="L14" r:id="rId13" xr:uid="{3881CED8-410A-4566-A2D3-A22ABDCF0D26}"/>
-    <hyperlink ref="L15" r:id="rId14" xr:uid="{906FD4E0-95FB-4A3D-9C1B-8B9EAF3C1DB9}"/>
-    <hyperlink ref="L16" r:id="rId15" xr:uid="{37E404B9-543A-42C0-AE5B-70EA24DD4DB5}"/>
-    <hyperlink ref="L17" r:id="rId16" xr:uid="{8E8ADE65-F540-4489-9445-CB2E1825691B}"/>
-    <hyperlink ref="L18" r:id="rId17" xr:uid="{D531D004-544A-4BF7-92FC-A9D961608643}"/>
-    <hyperlink ref="L19" r:id="rId18" xr:uid="{17D30FE4-9974-4207-8777-5978249B32E2}"/>
-    <hyperlink ref="L20" r:id="rId19" xr:uid="{12D8853B-7729-470C-AB90-D207CE98EEA0}"/>
-    <hyperlink ref="L21" r:id="rId20" xr:uid="{00D2223C-31CF-43D1-856F-D49BDCEA131C}"/>
-    <hyperlink ref="L22" r:id="rId21" xr:uid="{CB96AD4A-9B90-4C5E-A68B-DDD676640F9E}"/>
-    <hyperlink ref="L23" r:id="rId22" xr:uid="{26105D90-DFF5-4CA6-9582-299263E31B35}"/>
-    <hyperlink ref="L24" r:id="rId23" xr:uid="{9AB0BAFE-0381-44D2-9EDC-247FD363F79C}"/>
-    <hyperlink ref="L25" r:id="rId24" xr:uid="{98AEAB84-FA3F-4910-86CF-70342316C3FF}"/>
-    <hyperlink ref="L26" r:id="rId25" xr:uid="{0957C3AC-4EA5-4849-B5CC-1D7B262623BB}"/>
-    <hyperlink ref="L27" r:id="rId26" xr:uid="{D0280BDE-DC2A-40E3-9CB7-A2D9CC06BBEB}"/>
-    <hyperlink ref="L28" r:id="rId27" xr:uid="{6A4F2510-888E-4960-9B6A-6BD5C38F76A4}"/>
-    <hyperlink ref="L29" r:id="rId28" xr:uid="{D13EA121-6BF2-4E02-916A-95E49ED24CCA}"/>
-    <hyperlink ref="L30" r:id="rId29" xr:uid="{D8A1C9AA-BD31-46BE-BC73-F665EBC68578}"/>
-    <hyperlink ref="L31" r:id="rId30" xr:uid="{4EB5D526-602F-4067-80DF-55449C4182EB}"/>
-    <hyperlink ref="L32" r:id="rId31" xr:uid="{A77DA222-C77B-4E65-A287-EF1BC7F6BC4E}"/>
-    <hyperlink ref="L33" r:id="rId32" xr:uid="{9A82D738-3188-4F12-927B-E76C3CC8DDDC}"/>
-    <hyperlink ref="L34" r:id="rId33" xr:uid="{B931127A-2A69-4C61-90E0-F3E9FF45E299}"/>
-    <hyperlink ref="L35" r:id="rId34" xr:uid="{3875832D-940A-4023-9258-204A3176979F}"/>
-    <hyperlink ref="L36" r:id="rId35" xr:uid="{A0848D60-2B6A-4CD1-A151-7DA89BC0302C}"/>
-    <hyperlink ref="L37" r:id="rId36" xr:uid="{9D67C847-9061-4817-86FE-2F30830FD740}"/>
-    <hyperlink ref="L38" r:id="rId37" xr:uid="{4D36B57D-0B77-4DB8-931E-DFB6C2F5BF1D}"/>
-    <hyperlink ref="L39" r:id="rId38" xr:uid="{800CAF86-127D-4E14-A542-79A7563B39CF}"/>
-    <hyperlink ref="L40" r:id="rId39" xr:uid="{EB0A2389-14BA-46E0-BBEB-6DE12BC96AF1}"/>
-    <hyperlink ref="L41" r:id="rId40" xr:uid="{5087DB48-A486-473F-9410-816F63206DC3}"/>
-    <hyperlink ref="L42" r:id="rId41" xr:uid="{A422A3DB-9626-42A4-BDC5-D0B72C9E4E96}"/>
-    <hyperlink ref="L43" r:id="rId42" xr:uid="{419160F8-9626-49F9-B97D-D584B7E9A31B}"/>
-    <hyperlink ref="L44" r:id="rId43" xr:uid="{83451493-B638-4D70-B844-6FABFC274F9B}"/>
-    <hyperlink ref="L45" r:id="rId44" xr:uid="{7C7A8136-2261-4BA4-A548-3200EA322F81}"/>
-    <hyperlink ref="L46" r:id="rId45" xr:uid="{0FCA1DFF-55AE-4172-A0B3-F23D8EE0D395}"/>
-    <hyperlink ref="L47" r:id="rId46" xr:uid="{8452CD0F-70AB-453A-9D98-7C1ECE7BDA50}"/>
-    <hyperlink ref="L48" r:id="rId47" xr:uid="{3E3EE573-009E-4A47-A274-DB0F739B3B79}"/>
-    <hyperlink ref="L49" r:id="rId48" xr:uid="{2CAAFA5A-A4C1-4852-BF88-14A39418FBBD}"/>
-    <hyperlink ref="L50" r:id="rId49" xr:uid="{303C32D1-AF48-475F-9C4C-20DFBD596C84}"/>
-    <hyperlink ref="L51" r:id="rId50" xr:uid="{AF88C707-B85C-4FBE-8C9B-8398926EEBC4}"/>
-    <hyperlink ref="L52" r:id="rId51" xr:uid="{5567A5B6-8C97-4CC7-B50D-BC96927EAD02}"/>
-    <hyperlink ref="L53" r:id="rId52" xr:uid="{A9D02F2E-3F4A-48F4-BABA-7A22A3E654BE}"/>
-    <hyperlink ref="L54" r:id="rId53" xr:uid="{41550DCC-F81D-456F-90CF-54382D602CA9}"/>
-    <hyperlink ref="L55" r:id="rId54" xr:uid="{CD55F6E1-08BE-4264-A4B5-2A7C25A98C9E}"/>
-    <hyperlink ref="L56" r:id="rId55" xr:uid="{837195C5-0FE4-4B93-B784-7D14AA909584}"/>
-    <hyperlink ref="L57" r:id="rId56" xr:uid="{C88F936C-B0C6-4E94-9E27-B4BE18742505}"/>
-    <hyperlink ref="L58" r:id="rId57" xr:uid="{8E56B441-70FA-4855-8BD8-A97B59BA1B3E}"/>
-    <hyperlink ref="L59" r:id="rId58" xr:uid="{79608F45-DEA9-4FF2-942D-286BA5D05C89}"/>
-    <hyperlink ref="L60" r:id="rId59" xr:uid="{72209A95-F34D-4644-BD6D-41058221E7A5}"/>
-    <hyperlink ref="L61" r:id="rId60" xr:uid="{694F4FB5-0990-4526-96D4-FA41AFB6969E}"/>
+    <hyperlink ref="L2" r:id="rId1" xr:uid="{DD5FB9C5-11B2-454E-B40E-F2B85FA35303}"/>
+    <hyperlink ref="L3" r:id="rId2" xr:uid="{CC121A12-2951-409E-9C93-FFDB4C6188DF}"/>
+    <hyperlink ref="L4" r:id="rId3" xr:uid="{211A7499-A7D9-4639-8354-67C76EBDD757}"/>
+    <hyperlink ref="L5" r:id="rId4" xr:uid="{CFBCD0EA-A915-4CE4-9F65-B18094235AD2}"/>
+    <hyperlink ref="L6" r:id="rId5" xr:uid="{5ACF1155-4913-4765-8884-697602D5DB0E}"/>
+    <hyperlink ref="L7" r:id="rId6" xr:uid="{6C3AD45D-3AA2-4271-B4A5-2DC7F1E6E3F4}"/>
+    <hyperlink ref="L8" r:id="rId7" xr:uid="{998098B4-FD06-467B-AC6C-BB3159D35F42}"/>
+    <hyperlink ref="L9" r:id="rId8" xr:uid="{B82850EC-7DC4-45CB-846F-295522D1E743}"/>
+    <hyperlink ref="L10" r:id="rId9" xr:uid="{1E9F6DC3-B91A-439F-80D0-7BADBE0C5994}"/>
+    <hyperlink ref="L11" r:id="rId10" xr:uid="{2627E8BD-9526-4C41-9CE5-EA19BC6811C8}"/>
+    <hyperlink ref="L12" r:id="rId11" xr:uid="{FA15459C-13A7-428C-94B8-9FBDEB1FF9B9}"/>
+    <hyperlink ref="L13" r:id="rId12" xr:uid="{419EF7C1-870D-4500-AEFE-9B1CD6498E7E}"/>
+    <hyperlink ref="L14" r:id="rId13" xr:uid="{A456E84A-5D0D-43F4-A13D-539209F30E18}"/>
+    <hyperlink ref="L15" r:id="rId14" xr:uid="{89FE0333-F5B1-4644-90FF-181B6AE1F0D6}"/>
+    <hyperlink ref="L16" r:id="rId15" xr:uid="{9319C978-D8D6-4396-8F23-77B89C1E1D19}"/>
+    <hyperlink ref="L17" r:id="rId16" xr:uid="{6920FD91-FBED-4E1F-9999-8C5A41B90F8C}"/>
+    <hyperlink ref="L18" r:id="rId17" xr:uid="{9AF770F0-C13F-4C3B-8F75-E4254D2E5678}"/>
+    <hyperlink ref="L19" r:id="rId18" xr:uid="{80013883-1ECC-43B2-94D7-5C67FE77247D}"/>
+    <hyperlink ref="L20" r:id="rId19" xr:uid="{30B6AF3D-57A8-43E5-AACA-ED5455EC8C9A}"/>
+    <hyperlink ref="L21" r:id="rId20" xr:uid="{370C481B-CA7D-475E-BD99-3F507787473D}"/>
+    <hyperlink ref="L22" r:id="rId21" xr:uid="{8C124D02-A0C3-4B35-93F0-708D655DB5D6}"/>
+    <hyperlink ref="L23" r:id="rId22" xr:uid="{D79FCAC6-ACF0-42DE-94A1-5B8D9A86CA0C}"/>
+    <hyperlink ref="L24" r:id="rId23" xr:uid="{08A34378-15AA-4143-B4C0-B095D814BF36}"/>
+    <hyperlink ref="L25" r:id="rId24" xr:uid="{13723B77-E945-4D7A-9516-7AA27F9E9F2B}"/>
+    <hyperlink ref="L26" r:id="rId25" xr:uid="{4C7DF777-A3CB-43CB-8EFE-93160B2477C8}"/>
+    <hyperlink ref="L27" r:id="rId26" xr:uid="{9DFC322B-C867-41EA-9F01-5595915D8CC5}"/>
+    <hyperlink ref="L28" r:id="rId27" xr:uid="{085920D6-B132-460D-B4D9-A2F5E92FB6F1}"/>
+    <hyperlink ref="L29" r:id="rId28" xr:uid="{5A4FCE80-14B3-4554-A6F2-F6695F54BA41}"/>
+    <hyperlink ref="L30" r:id="rId29" xr:uid="{FA77F17F-0E6B-4F84-AF94-5CAA9A23D88A}"/>
+    <hyperlink ref="L31" r:id="rId30" xr:uid="{4CADEA5B-E76F-4806-844A-7841A10B4D3F}"/>
+    <hyperlink ref="L32" r:id="rId31" xr:uid="{4E766F18-AAFE-4617-AB87-5F4B26174B5A}"/>
+    <hyperlink ref="L33" r:id="rId32" xr:uid="{5CB53484-EFBA-41AD-8B88-2CCA3A245B72}"/>
+    <hyperlink ref="L34" r:id="rId33" xr:uid="{9419F98F-31A4-43B9-BE20-7A300E0123B0}"/>
+    <hyperlink ref="L35" r:id="rId34" xr:uid="{8985CDFB-98DB-4116-A1A7-FD533D4FEBB1}"/>
+    <hyperlink ref="L36" r:id="rId35" xr:uid="{3048C4DF-4988-4656-9000-F6993EABB01A}"/>
+    <hyperlink ref="L37" r:id="rId36" xr:uid="{A8DC4BA7-E8CE-4D12-AC6C-F46769F253EB}"/>
+    <hyperlink ref="L38" r:id="rId37" xr:uid="{CC23D497-312C-4528-8A52-82352416CE49}"/>
+    <hyperlink ref="L39" r:id="rId38" xr:uid="{AB130CA2-0CD2-4494-9CE0-2C4AFECB7CCF}"/>
+    <hyperlink ref="L40" r:id="rId39" xr:uid="{E43A5C1A-74E6-45A9-BA77-F0971D5F8E3C}"/>
+    <hyperlink ref="L41" r:id="rId40" xr:uid="{C557DBC2-9163-4FD4-AFE0-6299FDD31829}"/>
+    <hyperlink ref="L42" r:id="rId41" xr:uid="{0E9BDAFE-597C-4254-A703-65EED2875169}"/>
+    <hyperlink ref="L43" r:id="rId42" xr:uid="{9046DCDC-6CD3-4482-8E8B-4148D3526825}"/>
+    <hyperlink ref="L44" r:id="rId43" xr:uid="{E803C6ED-0E58-4BD3-AE3A-F44616B29161}"/>
+    <hyperlink ref="L45" r:id="rId44" xr:uid="{6A1FF743-F18C-46FC-ADD2-B03466427D51}"/>
+    <hyperlink ref="L46" r:id="rId45" xr:uid="{C2DE1701-245F-44CF-AF47-B318B6F10A14}"/>
+    <hyperlink ref="L47" r:id="rId46" xr:uid="{1AED909D-979A-452E-8EE7-725D69567D78}"/>
+    <hyperlink ref="L48" r:id="rId47" xr:uid="{D8172872-2FE8-4464-9BB8-ABFE63A043B1}"/>
+    <hyperlink ref="L49" r:id="rId48" xr:uid="{D1D4D322-29A5-4FF4-A0D8-6142423CD780}"/>
+    <hyperlink ref="L50" r:id="rId49" xr:uid="{F8B50BB0-0F96-4851-8F23-4C73967B65ED}"/>
+    <hyperlink ref="L51" r:id="rId50" xr:uid="{B0545B0F-5C4D-4E9A-B5D3-C333B1F109E9}"/>
+    <hyperlink ref="L52" r:id="rId51" xr:uid="{73DA4084-5712-4EC9-953A-8C384C53807E}"/>
+    <hyperlink ref="L53" r:id="rId52" xr:uid="{E384C138-8B8B-402B-BCDF-6B4BCEF72D90}"/>
+    <hyperlink ref="L54" r:id="rId53" xr:uid="{478D2098-28BE-4F29-8D37-EE03579E0897}"/>
+    <hyperlink ref="L55" r:id="rId54" xr:uid="{65146706-6DBB-49D3-B626-63AC0FCFBB3C}"/>
+    <hyperlink ref="L56" r:id="rId55" xr:uid="{E6EADD49-008F-458F-BAA6-79BD8BD85977}"/>
+    <hyperlink ref="L57" r:id="rId56" xr:uid="{30914AE0-A72C-48EA-B606-90D7DEE3B770}"/>
+    <hyperlink ref="L58" r:id="rId57" xr:uid="{401E3435-E881-46A1-80AA-A537657B0E56}"/>
+    <hyperlink ref="L59" r:id="rId58" xr:uid="{5D5DD823-BEAD-4002-8FC4-1382A6ECCBED}"/>
+    <hyperlink ref="L60" r:id="rId59" xr:uid="{8716DD53-5EC7-46AB-A027-44830796C7CA}"/>
+    <hyperlink ref="L61" r:id="rId60" xr:uid="{A614186C-C6BA-4C7C-A88A-71A1FA704D78}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/minimarket.xlsx
+++ b/data/minimarket.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SEMESTER 6\PRAK. SIGTER\PROJECT AKHIR\STUDENT SURVIVAL MAP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0314C2DF-4890-48B9-AD17-25CCEE1E3B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9D3A8D-95B7-4871-BF06-0B681682523B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F35F33EF-EB1F-4670-92AD-4BBD8F6B088B}"/>
   </bookViews>
@@ -462,9 +462,6 @@
     <t>https://maps,app,goo,gl/HvGAw3yRT4Z41LoZ7</t>
   </si>
   <si>
-    <t>M001,jpg</t>
-  </si>
-  <si>
     <t>-7,749447245716337</t>
   </si>
   <si>
@@ -480,9 +477,6 @@
     <t>https://maps,app,goo,gl/hrcCoQa6NbGUDMs58</t>
   </si>
   <si>
-    <t>M002,jpg</t>
-  </si>
-  <si>
     <t>-7,756250064506058</t>
   </si>
   <si>
@@ -501,9 +495,6 @@
     <t>https://maps,app,goo,gl/yuGPo2Cdzm1cwWWFA</t>
   </si>
   <si>
-    <t>M003,jpg</t>
-  </si>
-  <si>
     <t>-7,752217570012537</t>
   </si>
   <si>
@@ -519,9 +510,6 @@
     <t>https://maps,app,goo,gl/y7eFw3yPzy8XiyVH8</t>
   </si>
   <si>
-    <t>M004,jpg</t>
-  </si>
-  <si>
     <t>-7,765916891413229</t>
   </si>
   <si>
@@ -537,9 +525,6 @@
     <t>https://maps,app,goo,gl/FcK4Bx17jAYCpJhX8</t>
   </si>
   <si>
-    <t>M005,jpg</t>
-  </si>
-  <si>
     <t>-7,758056400724876</t>
   </si>
   <si>
@@ -552,9 +537,6 @@
     <t>https://maps,app,goo,gl/gk9yBhy1XfxyNVp5A</t>
   </si>
   <si>
-    <t>M006,jpg</t>
-  </si>
-  <si>
     <t>-7,752947002982559</t>
   </si>
   <si>
@@ -573,9 +555,6 @@
     <t>https://maps,app,goo,gl/U18wT9wYGWXs2n1dA</t>
   </si>
   <si>
-    <t>M007,jpg</t>
-  </si>
-  <si>
     <t>-7,749895190158755</t>
   </si>
   <si>
@@ -591,9 +570,6 @@
     <t>https://maps,app,goo,gl/ACN1JDZCWuDx7x3c9</t>
   </si>
   <si>
-    <t>M008,jpg</t>
-  </si>
-  <si>
     <t>-7,7425767277541</t>
   </si>
   <si>
@@ -609,9 +585,6 @@
     <t>https://maps,app,goo,gl/vtbQovKZLG9tKWRM9</t>
   </si>
   <si>
-    <t>M009,jpg</t>
-  </si>
-  <si>
     <t>-7,749210435076886</t>
   </si>
   <si>
@@ -627,9 +600,6 @@
     <t>https://maps,app,goo,gl/Nj7awyKrLigPrPDt5</t>
   </si>
   <si>
-    <t>M010,jpg</t>
-  </si>
-  <si>
     <t>-7,748732158171262</t>
   </si>
   <si>
@@ -642,9 +612,6 @@
     <t>https://maps,app,goo,gl/UWnDTdNhGfGvs4cf6</t>
   </si>
   <si>
-    <t>M011,jpg</t>
-  </si>
-  <si>
     <t>-7,752859025575523</t>
   </si>
   <si>
@@ -660,9 +627,6 @@
     <t>https://maps,app,goo,gl/wtP4be5hRqgrhRSLA</t>
   </si>
   <si>
-    <t>M012,jpg</t>
-  </si>
-  <si>
     <t>-7,765337640697154</t>
   </si>
   <si>
@@ -678,9 +642,6 @@
     <t>https://maps,app,goo,gl/BFdQ2TDQ9pBMcoAX8</t>
   </si>
   <si>
-    <t>M013,jpg</t>
-  </si>
-  <si>
     <t>Indomaret Tantular No, 409 (FY5C)</t>
   </si>
   <si>
@@ -699,9 +660,6 @@
     <t>https://maps,app,goo,gl/x2AwyBvdkzFEaSBq6</t>
   </si>
   <si>
-    <t>M014,jpg</t>
-  </si>
-  <si>
     <t>-7,766357839864531</t>
   </si>
   <si>
@@ -714,9 +672,6 @@
     <t>https://maps,app,goo,gl/RnsoQmriB1m6i3AZ8</t>
   </si>
   <si>
-    <t>M015,jpg</t>
-  </si>
-  <si>
     <t>-7,769020449248469</t>
   </si>
   <si>
@@ -729,9 +684,6 @@
     <t>https://maps,app,goo,gl/7pUGd4KNk2rEpYPh9</t>
   </si>
   <si>
-    <t>M016,jpg</t>
-  </si>
-  <si>
     <t>-7,764893740448012</t>
   </si>
   <si>
@@ -747,9 +699,6 @@
     <t>https://maps,app,goo,gl/i2NX2in6kMciJJ2f8</t>
   </si>
   <si>
-    <t>M017,jpg</t>
-  </si>
-  <si>
     <t>-7,7638932991633425</t>
   </si>
   <si>
@@ -762,9 +711,6 @@
     <t>https://maps,app,goo,gl/yiqGLnZVyKNjwWkj6?g_st=ac</t>
   </si>
   <si>
-    <t>M018,png</t>
-  </si>
-  <si>
     <t>-7,764463124084063</t>
   </si>
   <si>
@@ -777,9 +723,6 @@
     <t>https://maps,app,goo,gl/YaX6UcnU3gT1rtmEA</t>
   </si>
   <si>
-    <t>M019,jpg</t>
-  </si>
-  <si>
     <t>-7,769901074159813</t>
   </si>
   <si>
@@ -792,9 +735,6 @@
     <t>https://maps,app,goo,gl/rf4pXZ5op64fGaEM8</t>
   </si>
   <si>
-    <t>M020,jpg</t>
-  </si>
-  <si>
     <t>-7,744073071243356</t>
   </si>
   <si>
@@ -804,9 +744,6 @@
     <t>https://maps,app,goo,gl/fufaosvrsao483j99</t>
   </si>
   <si>
-    <t>M021,jpg</t>
-  </si>
-  <si>
     <t>-7,769789454884158</t>
   </si>
   <si>
@@ -819,9 +756,6 @@
     <t>https://maps,app,goo,gl/x4QJfLUQkhHWqZ137</t>
   </si>
   <si>
-    <t>M022,jpg</t>
-  </si>
-  <si>
     <t>-7,781287170789081</t>
   </si>
   <si>
@@ -834,9 +768,6 @@
     <t>https://maps,app,goo,gl/E5VGMWFMkCHfZriL7</t>
   </si>
   <si>
-    <t>M023,jpg</t>
-  </si>
-  <si>
     <t>-7,76074441972423</t>
   </si>
   <si>
@@ -852,9 +783,6 @@
     <t>https://maps,app,goo,gl/6ptXJdnoMD4LfxAm6</t>
   </si>
   <si>
-    <t>M024,jpg</t>
-  </si>
-  <si>
     <t>-7,771760619476064</t>
   </si>
   <si>
@@ -867,9 +795,6 @@
     <t>https://maps,app,goo,gl/kQbgHLjC9CHXDVUd8</t>
   </si>
   <si>
-    <t>M025,jpg</t>
-  </si>
-  <si>
     <t>-7,767021127082602</t>
   </si>
   <si>
@@ -882,9 +807,6 @@
     <t>https://maps,app,goo,gl/D3hU9pNhRSwwefzd8</t>
   </si>
   <si>
-    <t>M026,jpg</t>
-  </si>
-  <si>
     <t>-7,756085604225498</t>
   </si>
   <si>
@@ -900,9 +822,6 @@
     <t>https://maps,app,goo,gl/SaS1WCo3QxG3jwW48</t>
   </si>
   <si>
-    <t>M027,jpg</t>
-  </si>
-  <si>
     <t>-7,7757624268869865</t>
   </si>
   <si>
@@ -915,9 +834,6 @@
     <t>https://maps,app,goo,gl/qQN4SrSZBWcQTHjU8</t>
   </si>
   <si>
-    <t>M028,jpg</t>
-  </si>
-  <si>
     <t>-7,77254523832928</t>
   </si>
   <si>
@@ -930,9 +846,6 @@
     <t>https://maps,app,goo,gl/jZqh5aGaYjRwjM1Q9</t>
   </si>
   <si>
-    <t>M029,jpg</t>
-  </si>
-  <si>
     <t>-7,7750608431802695</t>
   </si>
   <si>
@@ -945,9 +858,6 @@
     <t>https://maps,app,goo,gl/FKLhFzTtUv9Svu8X8</t>
   </si>
   <si>
-    <t>M030,jpg</t>
-  </si>
-  <si>
     <t>-7,780008155389338</t>
   </si>
   <si>
@@ -957,9 +867,6 @@
     <t>https://maps,app,goo,gl/SXgbsSj6UDL5eM7v7</t>
   </si>
   <si>
-    <t>M031,jpg</t>
-  </si>
-  <si>
     <t>-7,778918074660311</t>
   </si>
   <si>
@@ -975,9 +882,6 @@
     <t>https://maps,app,goo,gl/v5r9juBWxgPk1Bog6</t>
   </si>
   <si>
-    <t>M032,jpg</t>
-  </si>
-  <si>
     <t>-7,782104456519171</t>
   </si>
   <si>
@@ -990,9 +894,6 @@
     <t>https://maps,app,goo,gl/wWMHH899sSHvLsLJ7</t>
   </si>
   <si>
-    <t>M033,jpg</t>
-  </si>
-  <si>
     <t>-7,730661259789763</t>
   </si>
   <si>
@@ -1005,9 +906,6 @@
     <t>https://maps,app,goo,gl/Hkk5NCU4DLaffHSk8</t>
   </si>
   <si>
-    <t>M034,jpg</t>
-  </si>
-  <si>
     <t>Alfamart Kaliurang KM 8,1</t>
   </si>
   <si>
@@ -1026,9 +924,6 @@
     <t>https://maps,app,goo,gl/ZP2CpU3Z8afNahNt5</t>
   </si>
   <si>
-    <t>M035,jpg</t>
-  </si>
-  <si>
     <t>-7,752603744250776</t>
   </si>
   <si>
@@ -1044,9 +939,6 @@
     <t>https://maps,app,goo,gl/hFHpxtCSXm4rSsPWA</t>
   </si>
   <si>
-    <t>M036,jpg</t>
-  </si>
-  <si>
     <t>-7,739846624846841</t>
   </si>
   <si>
@@ -1059,9 +951,6 @@
     <t>https://maps,app,goo,gl/LLdHixFNGbzeXS5M9</t>
   </si>
   <si>
-    <t>M037,jpg</t>
-  </si>
-  <si>
     <t>-7,741377499571684</t>
   </si>
   <si>
@@ -1074,9 +963,6 @@
     <t>https://maps,app,goo,gl/gWeNBEXEgqUYBySc8</t>
   </si>
   <si>
-    <t>M038,jpg</t>
-  </si>
-  <si>
     <t>-7,750902817325119</t>
   </si>
   <si>
@@ -1092,9 +978,6 @@
     <t>https://maps,app,goo,gl/VfSbdzbDWi5UdNs68</t>
   </si>
   <si>
-    <t>M039,jpg</t>
-  </si>
-  <si>
     <t>-7,756502140675588</t>
   </si>
   <si>
@@ -1107,9 +990,6 @@
     <t>https://maps,app,goo,gl/2HTUZCfFgRj1mc689</t>
   </si>
   <si>
-    <t>M040,jpg</t>
-  </si>
-  <si>
     <t>-7,758410435461992</t>
   </si>
   <si>
@@ -1122,9 +1002,6 @@
     <t>https://maps,app,goo,gl/biQStQVcheFZL4fN8</t>
   </si>
   <si>
-    <t>M041,jpg</t>
-  </si>
-  <si>
     <t>-7,760641876439936</t>
   </si>
   <si>
@@ -1140,9 +1017,6 @@
     <t>https://maps,app,goo,gl/EpAysQ3WXUkqcna2A</t>
   </si>
   <si>
-    <t>M042,jpg</t>
-  </si>
-  <si>
     <t>-7,7729243349685735</t>
   </si>
   <si>
@@ -1158,9 +1032,6 @@
     <t>https://maps,app,goo,gl/wJ3bHdk31Wbs57Jf7</t>
   </si>
   <si>
-    <t>M043,jpg</t>
-  </si>
-  <si>
     <t>-7,76691020590576</t>
   </si>
   <si>
@@ -1176,9 +1047,6 @@
     <t>https://maps,app,goo,gl/pLVtxDoDFYRnXBfS7</t>
   </si>
   <si>
-    <t>M044,jpg</t>
-  </si>
-  <si>
     <t>-7,763377003772743</t>
   </si>
   <si>
@@ -1191,9 +1059,6 @@
     <t>https://maps,app,goo,gl/69ffCYJN4SpQF2DW8</t>
   </si>
   <si>
-    <t>M045,jpg</t>
-  </si>
-  <si>
     <t>-7,765364433687017</t>
   </si>
   <si>
@@ -1206,9 +1071,6 @@
     <t>https://maps,app,goo,gl/brniKuRnRZYaVX8F6</t>
   </si>
   <si>
-    <t>M046,jpg</t>
-  </si>
-  <si>
     <t>-7,761536782621959</t>
   </si>
   <si>
@@ -1224,9 +1086,6 @@
     <t>https://maps,app,goo,gl/bJxupU96DGrmDFjY7</t>
   </si>
   <si>
-    <t>M047,jpg</t>
-  </si>
-  <si>
     <t>-7,770126662899377</t>
   </si>
   <si>
@@ -1242,9 +1101,6 @@
     <t>https://maps,app,goo,gl/mDaN88tVqkM2FXoNA</t>
   </si>
   <si>
-    <t>M048,jpg</t>
-  </si>
-  <si>
     <t>-7,776009658807369</t>
   </si>
   <si>
@@ -1257,9 +1113,6 @@
     <t>https://maps,app,goo,gl/nvtwnSp9Uzx7WN8fA</t>
   </si>
   <si>
-    <t>M049,jpg</t>
-  </si>
-  <si>
     <t>-7,774319145981829</t>
   </si>
   <si>
@@ -1275,9 +1128,6 @@
     <t>https://maps,app,goo,gl/XkByBoZZxTmunCKW6</t>
   </si>
   <si>
-    <t>M050,jpg</t>
-  </si>
-  <si>
     <t>-7,770417559044908</t>
   </si>
   <si>
@@ -1290,9 +1140,6 @@
     <t>https://maps,app,goo,gl/apZbFsSCBr6EYLRT9</t>
   </si>
   <si>
-    <t>M051,jpg</t>
-  </si>
-  <si>
     <t>-7,771095549600947</t>
   </si>
   <si>
@@ -1305,9 +1152,6 @@
     <t>https://maps,app,goo,gl/VrgpLuxUPrsUphA38</t>
   </si>
   <si>
-    <t>M052,jpg</t>
-  </si>
-  <si>
     <t>-7,77159183805787</t>
   </si>
   <si>
@@ -1323,9 +1167,6 @@
     <t>https://maps,app,goo,gl/XafqcjhRZgeAV1c77</t>
   </si>
   <si>
-    <t>M053,jpg</t>
-  </si>
-  <si>
     <t>-7,763065828579438</t>
   </si>
   <si>
@@ -1338,9 +1179,6 @@
     <t>https://maps,app,goo,gl/sXSR64xef5eu8CCL8</t>
   </si>
   <si>
-    <t>M054,jpg</t>
-  </si>
-  <si>
     <t>-7,760820680118197</t>
   </si>
   <si>
@@ -1359,9 +1197,6 @@
     <t>https://maps,app,goo,gl/K8a86JiuLDtJy7Z98</t>
   </si>
   <si>
-    <t>M055,jpg</t>
-  </si>
-  <si>
     <t>-7,76318000437515</t>
   </si>
   <si>
@@ -1374,9 +1209,6 @@
     <t>https://maps,app,goo,gl/kU2uvJp8YCZwLjSG6</t>
   </si>
   <si>
-    <t>M056,jpg</t>
-  </si>
-  <si>
     <t>-7,770692904079514</t>
   </si>
   <si>
@@ -1392,9 +1224,6 @@
     <t>https://maps,app,goo,gl/2qZxGGcCcJtkY1g39</t>
   </si>
   <si>
-    <t>M057,jpg</t>
-  </si>
-  <si>
     <t>-7,758533872322579</t>
   </si>
   <si>
@@ -1413,9 +1242,6 @@
     <t>https://maps,app,goo,gl/Whhj3uPkLXoK1M1Y7</t>
   </si>
   <si>
-    <t>M058,jpg</t>
-  </si>
-  <si>
     <t>-7,7496373777161125</t>
   </si>
   <si>
@@ -1431,9 +1257,6 @@
     <t>https://maps,app,goo,gl/FLzj6sN18SWF7E4C6</t>
   </si>
   <si>
-    <t>M059,jpg</t>
-  </si>
-  <si>
     <t>-7,782078923814419</t>
   </si>
   <si>
@@ -1449,7 +1272,184 @@
     <t>https://maps,app,goo,gl/8eNFKmsacyiLPxVA9</t>
   </si>
   <si>
-    <t>M060,jpg</t>
+    <t>images\M001,jpg</t>
+  </si>
+  <si>
+    <t>images\M002,jpg</t>
+  </si>
+  <si>
+    <t>images\M003,jpg</t>
+  </si>
+  <si>
+    <t>images\M004,jpg</t>
+  </si>
+  <si>
+    <t>images\M005,jpg</t>
+  </si>
+  <si>
+    <t>images\M006,jpg</t>
+  </si>
+  <si>
+    <t>images\M007,jpg</t>
+  </si>
+  <si>
+    <t>images\M008,jpg</t>
+  </si>
+  <si>
+    <t>images\M009,jpg</t>
+  </si>
+  <si>
+    <t>images\M010,jpg</t>
+  </si>
+  <si>
+    <t>images\M011,jpg</t>
+  </si>
+  <si>
+    <t>images\M012,jpg</t>
+  </si>
+  <si>
+    <t>images\M013,jpg</t>
+  </si>
+  <si>
+    <t>images\M014,jpg</t>
+  </si>
+  <si>
+    <t>images\M015,jpg</t>
+  </si>
+  <si>
+    <t>images\M016,jpg</t>
+  </si>
+  <si>
+    <t>images\M017,jpg</t>
+  </si>
+  <si>
+    <t>images\M018,png</t>
+  </si>
+  <si>
+    <t>images\M019,jpg</t>
+  </si>
+  <si>
+    <t>images\M020,jpg</t>
+  </si>
+  <si>
+    <t>images\M021,jpg</t>
+  </si>
+  <si>
+    <t>images\M022,jpg</t>
+  </si>
+  <si>
+    <t>images\M023,jpg</t>
+  </si>
+  <si>
+    <t>images\M024,jpg</t>
+  </si>
+  <si>
+    <t>images\M025,jpg</t>
+  </si>
+  <si>
+    <t>images\M026,jpg</t>
+  </si>
+  <si>
+    <t>images\M027,jpg</t>
+  </si>
+  <si>
+    <t>images\M028,jpg</t>
+  </si>
+  <si>
+    <t>images\M029,jpg</t>
+  </si>
+  <si>
+    <t>images\M030,jpg</t>
+  </si>
+  <si>
+    <t>images\M031,jpg</t>
+  </si>
+  <si>
+    <t>images\M032,jpg</t>
+  </si>
+  <si>
+    <t>images\M033,jpg</t>
+  </si>
+  <si>
+    <t>images\M034,jpg</t>
+  </si>
+  <si>
+    <t>images\M035,jpg</t>
+  </si>
+  <si>
+    <t>images\M036,jpg</t>
+  </si>
+  <si>
+    <t>images\M037,jpg</t>
+  </si>
+  <si>
+    <t>images\M038,jpg</t>
+  </si>
+  <si>
+    <t>images\M039,jpg</t>
+  </si>
+  <si>
+    <t>images\M040,jpg</t>
+  </si>
+  <si>
+    <t>images\M041,jpg</t>
+  </si>
+  <si>
+    <t>images\M042,jpg</t>
+  </si>
+  <si>
+    <t>images\M043,jpg</t>
+  </si>
+  <si>
+    <t>images\M044,jpg</t>
+  </si>
+  <si>
+    <t>images\M045,jpg</t>
+  </si>
+  <si>
+    <t>images\M046,jpg</t>
+  </si>
+  <si>
+    <t>images\M047,jpg</t>
+  </si>
+  <si>
+    <t>images\M048,jpg</t>
+  </si>
+  <si>
+    <t>images\M049,jpg</t>
+  </si>
+  <si>
+    <t>images\M050,jpg</t>
+  </si>
+  <si>
+    <t>images\M051,jpg</t>
+  </si>
+  <si>
+    <t>images\M052,jpg</t>
+  </si>
+  <si>
+    <t>images\M053,jpg</t>
+  </si>
+  <si>
+    <t>images\M054,jpg</t>
+  </si>
+  <si>
+    <t>images\M055,jpg</t>
+  </si>
+  <si>
+    <t>images\M056,jpg</t>
+  </si>
+  <si>
+    <t>images\M057,jpg</t>
+  </si>
+  <si>
+    <t>images\M058,jpg</t>
+  </si>
+  <si>
+    <t>images\M059,jpg</t>
+  </si>
+  <si>
+    <t>images\M060,jpg</t>
   </si>
 </sst>
 </file>
@@ -1477,38 +1477,45 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F1F1F"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2013,7 +2020,7 @@
         <v>141</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>142</v>
+        <v>412</v>
       </c>
       <c r="N2" s="11" t="s">
         <v>15</v>
@@ -2030,13 +2037,13 @@
         <v>12</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>13</v>
@@ -2051,13 +2058,13 @@
         <v>14</v>
       </c>
       <c r="K3" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="L3" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="L3" s="10" t="s">
-        <v>147</v>
-      </c>
       <c r="M3" s="7" t="s">
-        <v>148</v>
+        <v>413</v>
       </c>
       <c r="N3" s="11" t="s">
         <v>15</v>
@@ -2074,34 +2081,34 @@
         <v>12</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="G4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="I4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="7" t="s">
+      <c r="L4" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="M4" s="7" t="s">
-        <v>155</v>
+        <v>414</v>
       </c>
       <c r="N4" s="11" t="s">
         <v>15</v>
@@ -2118,13 +2125,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>13</v>
@@ -2139,13 +2146,13 @@
         <v>14</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>161</v>
+        <v>415</v>
       </c>
       <c r="N5" s="11" t="s">
         <v>17</v>
@@ -2162,13 +2169,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>13</v>
@@ -2183,13 +2190,13 @@
         <v>14</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>167</v>
+        <v>416</v>
       </c>
       <c r="N6" s="11" t="s">
         <v>17</v>
@@ -2206,19 +2213,19 @@
         <v>12</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>14</v>
@@ -2227,13 +2234,13 @@
         <v>14</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>172</v>
+        <v>417</v>
       </c>
       <c r="N7" s="11" t="s">
         <v>15</v>
@@ -2250,19 +2257,19 @@
         <v>12</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>14</v>
@@ -2271,13 +2278,13 @@
         <v>14</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>179</v>
+        <v>418</v>
       </c>
       <c r="N8" s="11" t="s">
         <v>15</v>
@@ -2294,34 +2301,34 @@
         <v>12</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>183</v>
-      </c>
       <c r="L9" s="10" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>185</v>
+        <v>419</v>
       </c>
       <c r="N9" s="11" t="s">
         <v>15</v>
@@ -2338,19 +2345,19 @@
         <v>12</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>14</v>
@@ -2359,13 +2366,13 @@
         <v>14</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>191</v>
+        <v>420</v>
       </c>
       <c r="N10" s="11" t="s">
         <v>15</v>
@@ -2382,19 +2389,19 @@
         <v>12</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>14</v>
@@ -2403,13 +2410,13 @@
         <v>14</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>197</v>
+        <v>421</v>
       </c>
       <c r="N11" s="11" t="s">
         <v>15</v>
@@ -2426,19 +2433,19 @@
         <v>12</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>14</v>
@@ -2447,13 +2454,13 @@
         <v>14</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>202</v>
+        <v>422</v>
       </c>
       <c r="N12" s="11" t="s">
         <v>15</v>
@@ -2470,19 +2477,19 @@
         <v>12</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>14</v>
@@ -2491,13 +2498,13 @@
         <v>14</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>208</v>
+        <v>423</v>
       </c>
       <c r="N13" s="11" t="s">
         <v>15</v>
@@ -2514,13 +2521,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>13</v>
@@ -2535,13 +2542,13 @@
         <v>14</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>214</v>
+        <v>424</v>
       </c>
       <c r="N14" s="11" t="s">
         <v>17</v>
@@ -2552,25 +2559,25 @@
         <v>47</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I15" s="9" t="s">
         <v>14</v>
@@ -2579,13 +2586,13 @@
         <v>14</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>221</v>
+        <v>425</v>
       </c>
       <c r="N15" s="11" t="s">
         <v>15</v>
@@ -2602,19 +2609,19 @@
         <v>12</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>14</v>
@@ -2623,13 +2630,13 @@
         <v>14</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>226</v>
+        <v>426</v>
       </c>
       <c r="N16" s="11" t="s">
         <v>15</v>
@@ -2646,19 +2653,19 @@
         <v>12</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>14</v>
@@ -2667,13 +2674,13 @@
         <v>14</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>231</v>
+        <v>427</v>
       </c>
       <c r="N17" s="11" t="s">
         <v>15</v>
@@ -2690,19 +2697,19 @@
         <v>12</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I18" s="9" t="s">
         <v>14</v>
@@ -2711,13 +2718,13 @@
         <v>14</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>237</v>
+        <v>428</v>
       </c>
       <c r="N18" s="11" t="s">
         <v>15</v>
@@ -2734,13 +2741,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>13</v>
@@ -2758,10 +2765,10 @@
         <v>14</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>242</v>
+        <v>429</v>
       </c>
       <c r="N19" s="11" t="s">
         <v>15</v>
@@ -2778,13 +2785,13 @@
         <v>12</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>13</v>
@@ -2799,13 +2806,13 @@
         <v>14</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>247</v>
+        <v>430</v>
       </c>
       <c r="N20" s="11" t="s">
         <v>15</v>
@@ -2822,13 +2829,13 @@
         <v>12</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>13</v>
@@ -2843,13 +2850,13 @@
         <v>14</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>252</v>
+        <v>431</v>
       </c>
       <c r="N21" s="11" t="s">
         <v>17</v>
@@ -2866,10 +2873,10 @@
         <v>12</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>18</v>
@@ -2887,13 +2894,13 @@
         <v>14</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>256</v>
+        <v>432</v>
       </c>
       <c r="N22" s="11" t="s">
         <v>15</v>
@@ -2910,13 +2917,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>13</v>
@@ -2931,13 +2938,13 @@
         <v>14</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>261</v>
+        <v>433</v>
       </c>
       <c r="N23" s="11" t="s">
         <v>17</v>
@@ -2954,13 +2961,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>13</v>
@@ -2978,10 +2985,10 @@
         <v>140</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>266</v>
+        <v>434</v>
       </c>
       <c r="N24" s="11" t="s">
         <v>17</v>
@@ -2998,13 +3005,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>13</v>
@@ -3019,13 +3026,13 @@
         <v>14</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>272</v>
+        <v>435</v>
       </c>
       <c r="N25" s="11" t="s">
         <v>15</v>
@@ -3042,13 +3049,13 @@
         <v>12</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>13</v>
@@ -3063,13 +3070,13 @@
         <v>14</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>277</v>
+        <v>436</v>
       </c>
       <c r="N26" s="11" t="s">
         <v>15</v>
@@ -3086,13 +3093,13 @@
         <v>12</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>278</v>
+        <v>253</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>13</v>
@@ -3107,13 +3114,13 @@
         <v>14</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>282</v>
+        <v>437</v>
       </c>
       <c r="N27" s="11" t="s">
         <v>17</v>
@@ -3130,13 +3137,13 @@
         <v>12</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>284</v>
+        <v>258</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>13</v>
@@ -3151,13 +3158,13 @@
         <v>14</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="M28" s="7" t="s">
-        <v>288</v>
+        <v>438</v>
       </c>
       <c r="N28" s="11" t="s">
         <v>17</v>
@@ -3174,13 +3181,13 @@
         <v>12</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>13</v>
@@ -3195,13 +3202,13 @@
         <v>14</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>292</v>
+        <v>265</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>293</v>
+        <v>439</v>
       </c>
       <c r="N29" s="11" t="s">
         <v>17</v>
@@ -3218,13 +3225,13 @@
         <v>12</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>13</v>
@@ -3239,13 +3246,13 @@
         <v>14</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="M30" s="7" t="s">
-        <v>298</v>
+        <v>440</v>
       </c>
       <c r="N30" s="11" t="s">
         <v>17</v>
@@ -3262,13 +3269,13 @@
         <v>12</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>299</v>
+        <v>270</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>301</v>
+        <v>272</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>13</v>
@@ -3286,10 +3293,10 @@
         <v>14</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>302</v>
+        <v>273</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>303</v>
+        <v>441</v>
       </c>
       <c r="N31" s="11" t="s">
         <v>15</v>
@@ -3306,13 +3313,13 @@
         <v>12</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>13</v>
@@ -3330,10 +3337,10 @@
         <v>140</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="M32" s="7" t="s">
-        <v>307</v>
+        <v>442</v>
       </c>
       <c r="N32" s="11" t="s">
         <v>17</v>
@@ -3350,13 +3357,13 @@
         <v>12</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>309</v>
+        <v>278</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>310</v>
+        <v>279</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>13</v>
@@ -3371,13 +3378,13 @@
         <v>14</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>311</v>
+        <v>280</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>312</v>
+        <v>281</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>313</v>
+        <v>443</v>
       </c>
       <c r="N33" s="11" t="s">
         <v>17</v>
@@ -3394,13 +3401,13 @@
         <v>12</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>316</v>
+        <v>284</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>13</v>
@@ -3415,13 +3422,13 @@
         <v>14</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>317</v>
+        <v>285</v>
       </c>
       <c r="M34" s="7" t="s">
-        <v>318</v>
+        <v>444</v>
       </c>
       <c r="N34" s="11" t="s">
         <v>15</v>
@@ -3438,13 +3445,13 @@
         <v>12</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>321</v>
+        <v>288</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>13</v>
@@ -3459,13 +3466,13 @@
         <v>14</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>311</v>
+        <v>280</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>323</v>
+        <v>445</v>
       </c>
       <c r="N35" s="11" t="s">
         <v>15</v>
@@ -3476,19 +3483,19 @@
         <v>87</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>324</v>
+        <v>290</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>326</v>
+        <v>292</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>327</v>
+        <v>293</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>13</v>
@@ -3503,13 +3510,13 @@
         <v>14</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>328</v>
+        <v>294</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>329</v>
+        <v>295</v>
       </c>
       <c r="M36" s="7" t="s">
-        <v>330</v>
+        <v>446</v>
       </c>
       <c r="N36" s="11" t="s">
         <v>17</v>
@@ -3526,19 +3533,19 @@
         <v>12</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>332</v>
+        <v>297</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>333</v>
+        <v>298</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>334</v>
+        <v>299</v>
       </c>
       <c r="I37" s="9" t="s">
         <v>14</v>
@@ -3547,13 +3554,13 @@
         <v>14</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>335</v>
+        <v>300</v>
       </c>
       <c r="M37" s="7" t="s">
-        <v>336</v>
+        <v>447</v>
       </c>
       <c r="N37" s="11" t="s">
         <v>15</v>
@@ -3570,13 +3577,13 @@
         <v>12</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>337</v>
+        <v>301</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>338</v>
+        <v>302</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>339</v>
+        <v>303</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>13</v>
@@ -3591,13 +3598,13 @@
         <v>14</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>340</v>
+        <v>304</v>
       </c>
       <c r="M38" s="7" t="s">
-        <v>341</v>
+        <v>448</v>
       </c>
       <c r="N38" s="11" t="s">
         <v>15</v>
@@ -3614,13 +3621,13 @@
         <v>12</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>342</v>
+        <v>305</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>343</v>
+        <v>306</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>344</v>
+        <v>307</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>14</v>
@@ -3635,13 +3642,13 @@
         <v>14</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>345</v>
+        <v>308</v>
       </c>
       <c r="M39" s="7" t="s">
-        <v>346</v>
+        <v>449</v>
       </c>
       <c r="N39" s="11" t="s">
         <v>15</v>
@@ -3658,13 +3665,13 @@
         <v>12</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>347</v>
+        <v>309</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>348</v>
+        <v>310</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>349</v>
+        <v>311</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>13</v>
@@ -3679,13 +3686,13 @@
         <v>14</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>350</v>
+        <v>312</v>
       </c>
       <c r="L40" s="10" t="s">
-        <v>351</v>
+        <v>313</v>
       </c>
       <c r="M40" s="7" t="s">
-        <v>352</v>
+        <v>450</v>
       </c>
       <c r="N40" s="11" t="s">
         <v>15</v>
@@ -3702,13 +3709,13 @@
         <v>12</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>353</v>
+        <v>314</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>354</v>
+        <v>315</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>355</v>
+        <v>316</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>14</v>
@@ -3723,13 +3730,13 @@
         <v>14</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="L41" s="10" t="s">
-        <v>356</v>
+        <v>317</v>
       </c>
       <c r="M41" s="7" t="s">
-        <v>357</v>
+        <v>451</v>
       </c>
       <c r="N41" s="11" t="s">
         <v>15</v>
@@ -3746,13 +3753,13 @@
         <v>12</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>359</v>
+        <v>319</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>13</v>
@@ -3767,13 +3774,13 @@
         <v>14</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L42" s="10" t="s">
-        <v>361</v>
+        <v>321</v>
       </c>
       <c r="M42" s="7" t="s">
-        <v>362</v>
+        <v>452</v>
       </c>
       <c r="N42" s="11" t="s">
         <v>17</v>
@@ -3790,19 +3797,19 @@
         <v>12</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>363</v>
+        <v>322</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>364</v>
+        <v>323</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>365</v>
+        <v>324</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>13</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>366</v>
+        <v>325</v>
       </c>
       <c r="I43" s="9" t="s">
         <v>14</v>
@@ -3811,13 +3818,13 @@
         <v>14</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>328</v>
+        <v>294</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>367</v>
+        <v>326</v>
       </c>
       <c r="M43" s="7" t="s">
-        <v>368</v>
+        <v>453</v>
       </c>
       <c r="N43" s="11" t="s">
         <v>15</v>
@@ -3834,19 +3841,19 @@
         <v>12</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>369</v>
+        <v>327</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>370</v>
+        <v>328</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>371</v>
+        <v>329</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>13</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>372</v>
+        <v>330</v>
       </c>
       <c r="I44" s="9" t="s">
         <v>14</v>
@@ -3855,13 +3862,13 @@
         <v>14</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="L44" s="10" t="s">
-        <v>373</v>
+        <v>331</v>
       </c>
       <c r="M44" s="7" t="s">
-        <v>374</v>
+        <v>454</v>
       </c>
       <c r="N44" s="11" t="s">
         <v>15</v>
@@ -3878,13 +3885,13 @@
         <v>12</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>375</v>
+        <v>332</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>376</v>
+        <v>333</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>377</v>
+        <v>334</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>13</v>
@@ -3899,13 +3906,13 @@
         <v>14</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>378</v>
+        <v>335</v>
       </c>
       <c r="L45" s="10" t="s">
-        <v>379</v>
+        <v>336</v>
       </c>
       <c r="M45" s="7" t="s">
-        <v>380</v>
+        <v>455</v>
       </c>
       <c r="N45" s="11" t="s">
         <v>15</v>
@@ -3922,13 +3929,13 @@
         <v>12</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>381</v>
+        <v>337</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>382</v>
+        <v>338</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>383</v>
+        <v>339</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>13</v>
@@ -3943,13 +3950,13 @@
         <v>14</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="L46" s="10" t="s">
-        <v>384</v>
+        <v>340</v>
       </c>
       <c r="M46" s="7" t="s">
-        <v>385</v>
+        <v>456</v>
       </c>
       <c r="N46" s="11" t="s">
         <v>17</v>
@@ -3966,13 +3973,13 @@
         <v>12</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>386</v>
+        <v>341</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>387</v>
+        <v>342</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>13</v>
@@ -3987,13 +3994,13 @@
         <v>14</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="L47" s="10" t="s">
-        <v>389</v>
+        <v>344</v>
       </c>
       <c r="M47" s="7" t="s">
-        <v>390</v>
+        <v>457</v>
       </c>
       <c r="N47" s="11" t="s">
         <v>15</v>
@@ -4010,19 +4017,19 @@
         <v>12</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>391</v>
+        <v>345</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>392</v>
+        <v>346</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>393</v>
+        <v>347</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>13</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>394</v>
+        <v>348</v>
       </c>
       <c r="I48" s="9" t="s">
         <v>14</v>
@@ -4031,13 +4038,13 @@
         <v>14</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="L48" s="10" t="s">
-        <v>395</v>
+        <v>349</v>
       </c>
       <c r="M48" s="7" t="s">
-        <v>396</v>
+        <v>458</v>
       </c>
       <c r="N48" s="11" t="s">
         <v>15</v>
@@ -4054,19 +4061,19 @@
         <v>12</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>397</v>
+        <v>350</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>398</v>
+        <v>351</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>399</v>
+        <v>352</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>13</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>400</v>
+        <v>353</v>
       </c>
       <c r="I49" s="9" t="s">
         <v>14</v>
@@ -4078,10 +4085,10 @@
         <v>140</v>
       </c>
       <c r="L49" s="10" t="s">
-        <v>401</v>
+        <v>354</v>
       </c>
       <c r="M49" s="7" t="s">
-        <v>402</v>
+        <v>459</v>
       </c>
       <c r="N49" s="11" t="s">
         <v>15</v>
@@ -4098,13 +4105,13 @@
         <v>12</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>403</v>
+        <v>355</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>404</v>
+        <v>356</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>405</v>
+        <v>357</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>13</v>
@@ -4119,13 +4126,13 @@
         <v>14</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="L50" s="10" t="s">
-        <v>406</v>
+        <v>358</v>
       </c>
       <c r="M50" s="7" t="s">
-        <v>407</v>
+        <v>460</v>
       </c>
       <c r="N50" s="11" t="s">
         <v>15</v>
@@ -4142,13 +4149,13 @@
         <v>12</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>408</v>
+        <v>359</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>409</v>
+        <v>360</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>410</v>
+        <v>361</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>13</v>
@@ -4163,13 +4170,13 @@
         <v>14</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>411</v>
+        <v>362</v>
       </c>
       <c r="L51" s="10" t="s">
-        <v>412</v>
+        <v>363</v>
       </c>
       <c r="M51" s="7" t="s">
-        <v>413</v>
+        <v>461</v>
       </c>
       <c r="N51" s="11" t="s">
         <v>15</v>
@@ -4186,13 +4193,13 @@
         <v>12</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>414</v>
+        <v>364</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>415</v>
+        <v>365</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>416</v>
+        <v>366</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>13</v>
@@ -4207,13 +4214,13 @@
         <v>14</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L52" s="16" t="s">
-        <v>417</v>
+        <v>367</v>
       </c>
       <c r="M52" s="7" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="N52" s="11" t="s">
         <v>17</v>
@@ -4230,13 +4237,13 @@
         <v>12</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>419</v>
+        <v>368</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>421</v>
+        <v>370</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>13</v>
@@ -4251,13 +4258,13 @@
         <v>14</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>350</v>
+        <v>312</v>
       </c>
       <c r="L53" s="16" t="s">
-        <v>422</v>
+        <v>371</v>
       </c>
       <c r="M53" s="7" t="s">
-        <v>423</v>
+        <v>463</v>
       </c>
       <c r="N53" s="11" t="s">
         <v>15</v>
@@ -4274,19 +4281,19 @@
         <v>12</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>424</v>
+        <v>372</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>425</v>
+        <v>373</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>426</v>
+        <v>374</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>13</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>427</v>
+        <v>375</v>
       </c>
       <c r="I54" s="9" t="s">
         <v>14</v>
@@ -4295,13 +4302,13 @@
         <v>14</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="L54" s="16" t="s">
-        <v>428</v>
+        <v>376</v>
       </c>
       <c r="M54" s="7" t="s">
-        <v>429</v>
+        <v>464</v>
       </c>
       <c r="N54" s="11" t="s">
         <v>15</v>
@@ -4318,13 +4325,13 @@
         <v>12</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>430</v>
+        <v>377</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>431</v>
+        <v>378</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>432</v>
+        <v>379</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>14</v>
@@ -4339,13 +4346,13 @@
         <v>14</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>311</v>
+        <v>280</v>
       </c>
       <c r="L55" s="16" t="s">
-        <v>433</v>
+        <v>380</v>
       </c>
       <c r="M55" s="7" t="s">
-        <v>434</v>
+        <v>465</v>
       </c>
       <c r="N55" s="11" t="s">
         <v>15</v>
@@ -4362,19 +4369,19 @@
         <v>12</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>435</v>
+        <v>381</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>436</v>
+        <v>382</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>437</v>
+        <v>383</v>
       </c>
       <c r="G56" s="11" t="s">
         <v>19</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>438</v>
+        <v>384</v>
       </c>
       <c r="I56" s="9" t="s">
         <v>14</v>
@@ -4383,13 +4390,13 @@
         <v>14</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>439</v>
+        <v>385</v>
       </c>
       <c r="L56" s="16" t="s">
-        <v>440</v>
+        <v>386</v>
       </c>
       <c r="M56" s="7" t="s">
-        <v>441</v>
+        <v>466</v>
       </c>
       <c r="N56" s="11" t="s">
         <v>15</v>
@@ -4406,13 +4413,13 @@
         <v>12</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>442</v>
+        <v>387</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>443</v>
+        <v>388</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>444</v>
+        <v>389</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>13</v>
@@ -4427,13 +4434,13 @@
         <v>14</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>350</v>
+        <v>312</v>
       </c>
       <c r="L57" s="16" t="s">
-        <v>445</v>
+        <v>390</v>
       </c>
       <c r="M57" s="7" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="N57" s="11" t="s">
         <v>17</v>
@@ -4450,19 +4457,19 @@
         <v>12</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>447</v>
+        <v>391</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>448</v>
+        <v>392</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>449</v>
+        <v>393</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>450</v>
+        <v>394</v>
       </c>
       <c r="I58" s="9" t="s">
         <v>14</v>
@@ -4471,13 +4478,13 @@
         <v>14</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="L58" s="16" t="s">
-        <v>451</v>
+        <v>395</v>
       </c>
       <c r="M58" s="7" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="N58" s="11" t="s">
         <v>15</v>
@@ -4494,19 +4501,19 @@
         <v>12</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>453</v>
+        <v>396</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>454</v>
+        <v>397</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>455</v>
+        <v>398</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>456</v>
+        <v>399</v>
       </c>
       <c r="I59" s="9" t="s">
         <v>14</v>
@@ -4515,13 +4522,13 @@
         <v>14</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>457</v>
+        <v>400</v>
       </c>
       <c r="L59" s="16" t="s">
-        <v>458</v>
+        <v>401</v>
       </c>
       <c r="M59" s="7" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="N59" s="11" t="s">
         <v>15</v>
@@ -4538,19 +4545,19 @@
         <v>12</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>460</v>
+        <v>402</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>461</v>
+        <v>403</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>462</v>
+        <v>404</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>463</v>
+        <v>405</v>
       </c>
       <c r="I60" s="9" t="s">
         <v>14</v>
@@ -4559,13 +4566,13 @@
         <v>14</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="L60" s="16" t="s">
-        <v>464</v>
+        <v>406</v>
       </c>
       <c r="M60" s="7" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="N60" s="11" t="s">
         <v>15</v>
@@ -4582,19 +4589,19 @@
         <v>12</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>466</v>
+        <v>407</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>467</v>
+        <v>408</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>468</v>
+        <v>409</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>469</v>
+        <v>410</v>
       </c>
       <c r="I61" s="9" t="s">
         <v>14</v>
@@ -4603,10 +4610,10 @@
         <v>14</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="L61" s="16" t="s">
-        <v>470</v>
+        <v>411</v>
       </c>
       <c r="M61" s="7" t="s">
         <v>471</v>
@@ -4617,77 +4624,77 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H61" xr:uid="{5AB1C413-B544-4BC1-A663-085AE1BB7139}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H61" xr:uid="{C19C8D62-4DAD-429F-BB08-B31EAFF01892}">
       <formula1>"07,00-22,00,07,00-22,01,Buka 24 Jam,07,00-22,02,08,00-23,00,-,07,00-23,00,10,00-21,00,09,00-22,00,06,00-22,00,09,00-21,00,08,00-20,00,10,00-22,00,06,00-21,00,07,30-21,30,08,30-21,30"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G61" xr:uid="{A68015C9-E5EB-43AF-AEA8-7116933EBDC6}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G61" xr:uid="{82A80630-5183-4792-B832-9BA2FED1891B}">
       <formula1>"Senin-Minggu,-,Senin-Sabtu"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N2:N61" xr:uid="{1DC8E56B-386A-49F3-8F03-FF7304DEF1DD}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N2:N61" xr:uid="{A5D164C1-C8EB-4435-814E-75FFF6DABE7F}">
       <formula1>"Tidak,Ya"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="L2" r:id="rId1" xr:uid="{DD5FB9C5-11B2-454E-B40E-F2B85FA35303}"/>
-    <hyperlink ref="L3" r:id="rId2" xr:uid="{CC121A12-2951-409E-9C93-FFDB4C6188DF}"/>
-    <hyperlink ref="L4" r:id="rId3" xr:uid="{211A7499-A7D9-4639-8354-67C76EBDD757}"/>
-    <hyperlink ref="L5" r:id="rId4" xr:uid="{CFBCD0EA-A915-4CE4-9F65-B18094235AD2}"/>
-    <hyperlink ref="L6" r:id="rId5" xr:uid="{5ACF1155-4913-4765-8884-697602D5DB0E}"/>
-    <hyperlink ref="L7" r:id="rId6" xr:uid="{6C3AD45D-3AA2-4271-B4A5-2DC7F1E6E3F4}"/>
-    <hyperlink ref="L8" r:id="rId7" xr:uid="{998098B4-FD06-467B-AC6C-BB3159D35F42}"/>
-    <hyperlink ref="L9" r:id="rId8" xr:uid="{B82850EC-7DC4-45CB-846F-295522D1E743}"/>
-    <hyperlink ref="L10" r:id="rId9" xr:uid="{1E9F6DC3-B91A-439F-80D0-7BADBE0C5994}"/>
-    <hyperlink ref="L11" r:id="rId10" xr:uid="{2627E8BD-9526-4C41-9CE5-EA19BC6811C8}"/>
-    <hyperlink ref="L12" r:id="rId11" xr:uid="{FA15459C-13A7-428C-94B8-9FBDEB1FF9B9}"/>
-    <hyperlink ref="L13" r:id="rId12" xr:uid="{419EF7C1-870D-4500-AEFE-9B1CD6498E7E}"/>
-    <hyperlink ref="L14" r:id="rId13" xr:uid="{A456E84A-5D0D-43F4-A13D-539209F30E18}"/>
-    <hyperlink ref="L15" r:id="rId14" xr:uid="{89FE0333-F5B1-4644-90FF-181B6AE1F0D6}"/>
-    <hyperlink ref="L16" r:id="rId15" xr:uid="{9319C978-D8D6-4396-8F23-77B89C1E1D19}"/>
-    <hyperlink ref="L17" r:id="rId16" xr:uid="{6920FD91-FBED-4E1F-9999-8C5A41B90F8C}"/>
-    <hyperlink ref="L18" r:id="rId17" xr:uid="{9AF770F0-C13F-4C3B-8F75-E4254D2E5678}"/>
-    <hyperlink ref="L19" r:id="rId18" xr:uid="{80013883-1ECC-43B2-94D7-5C67FE77247D}"/>
-    <hyperlink ref="L20" r:id="rId19" xr:uid="{30B6AF3D-57A8-43E5-AACA-ED5455EC8C9A}"/>
-    <hyperlink ref="L21" r:id="rId20" xr:uid="{370C481B-CA7D-475E-BD99-3F507787473D}"/>
-    <hyperlink ref="L22" r:id="rId21" xr:uid="{8C124D02-A0C3-4B35-93F0-708D655DB5D6}"/>
-    <hyperlink ref="L23" r:id="rId22" xr:uid="{D79FCAC6-ACF0-42DE-94A1-5B8D9A86CA0C}"/>
-    <hyperlink ref="L24" r:id="rId23" xr:uid="{08A34378-15AA-4143-B4C0-B095D814BF36}"/>
-    <hyperlink ref="L25" r:id="rId24" xr:uid="{13723B77-E945-4D7A-9516-7AA27F9E9F2B}"/>
-    <hyperlink ref="L26" r:id="rId25" xr:uid="{4C7DF777-A3CB-43CB-8EFE-93160B2477C8}"/>
-    <hyperlink ref="L27" r:id="rId26" xr:uid="{9DFC322B-C867-41EA-9F01-5595915D8CC5}"/>
-    <hyperlink ref="L28" r:id="rId27" xr:uid="{085920D6-B132-460D-B4D9-A2F5E92FB6F1}"/>
-    <hyperlink ref="L29" r:id="rId28" xr:uid="{5A4FCE80-14B3-4554-A6F2-F6695F54BA41}"/>
-    <hyperlink ref="L30" r:id="rId29" xr:uid="{FA77F17F-0E6B-4F84-AF94-5CAA9A23D88A}"/>
-    <hyperlink ref="L31" r:id="rId30" xr:uid="{4CADEA5B-E76F-4806-844A-7841A10B4D3F}"/>
-    <hyperlink ref="L32" r:id="rId31" xr:uid="{4E766F18-AAFE-4617-AB87-5F4B26174B5A}"/>
-    <hyperlink ref="L33" r:id="rId32" xr:uid="{5CB53484-EFBA-41AD-8B88-2CCA3A245B72}"/>
-    <hyperlink ref="L34" r:id="rId33" xr:uid="{9419F98F-31A4-43B9-BE20-7A300E0123B0}"/>
-    <hyperlink ref="L35" r:id="rId34" xr:uid="{8985CDFB-98DB-4116-A1A7-FD533D4FEBB1}"/>
-    <hyperlink ref="L36" r:id="rId35" xr:uid="{3048C4DF-4988-4656-9000-F6993EABB01A}"/>
-    <hyperlink ref="L37" r:id="rId36" xr:uid="{A8DC4BA7-E8CE-4D12-AC6C-F46769F253EB}"/>
-    <hyperlink ref="L38" r:id="rId37" xr:uid="{CC23D497-312C-4528-8A52-82352416CE49}"/>
-    <hyperlink ref="L39" r:id="rId38" xr:uid="{AB130CA2-0CD2-4494-9CE0-2C4AFECB7CCF}"/>
-    <hyperlink ref="L40" r:id="rId39" xr:uid="{E43A5C1A-74E6-45A9-BA77-F0971D5F8E3C}"/>
-    <hyperlink ref="L41" r:id="rId40" xr:uid="{C557DBC2-9163-4FD4-AFE0-6299FDD31829}"/>
-    <hyperlink ref="L42" r:id="rId41" xr:uid="{0E9BDAFE-597C-4254-A703-65EED2875169}"/>
-    <hyperlink ref="L43" r:id="rId42" xr:uid="{9046DCDC-6CD3-4482-8E8B-4148D3526825}"/>
-    <hyperlink ref="L44" r:id="rId43" xr:uid="{E803C6ED-0E58-4BD3-AE3A-F44616B29161}"/>
-    <hyperlink ref="L45" r:id="rId44" xr:uid="{6A1FF743-F18C-46FC-ADD2-B03466427D51}"/>
-    <hyperlink ref="L46" r:id="rId45" xr:uid="{C2DE1701-245F-44CF-AF47-B318B6F10A14}"/>
-    <hyperlink ref="L47" r:id="rId46" xr:uid="{1AED909D-979A-452E-8EE7-725D69567D78}"/>
-    <hyperlink ref="L48" r:id="rId47" xr:uid="{D8172872-2FE8-4464-9BB8-ABFE63A043B1}"/>
-    <hyperlink ref="L49" r:id="rId48" xr:uid="{D1D4D322-29A5-4FF4-A0D8-6142423CD780}"/>
-    <hyperlink ref="L50" r:id="rId49" xr:uid="{F8B50BB0-0F96-4851-8F23-4C73967B65ED}"/>
-    <hyperlink ref="L51" r:id="rId50" xr:uid="{B0545B0F-5C4D-4E9A-B5D3-C333B1F109E9}"/>
-    <hyperlink ref="L52" r:id="rId51" xr:uid="{73DA4084-5712-4EC9-953A-8C384C53807E}"/>
-    <hyperlink ref="L53" r:id="rId52" xr:uid="{E384C138-8B8B-402B-BCDF-6B4BCEF72D90}"/>
-    <hyperlink ref="L54" r:id="rId53" xr:uid="{478D2098-28BE-4F29-8D37-EE03579E0897}"/>
-    <hyperlink ref="L55" r:id="rId54" xr:uid="{65146706-6DBB-49D3-B626-63AC0FCFBB3C}"/>
-    <hyperlink ref="L56" r:id="rId55" xr:uid="{E6EADD49-008F-458F-BAA6-79BD8BD85977}"/>
-    <hyperlink ref="L57" r:id="rId56" xr:uid="{30914AE0-A72C-48EA-B606-90D7DEE3B770}"/>
-    <hyperlink ref="L58" r:id="rId57" xr:uid="{401E3435-E881-46A1-80AA-A537657B0E56}"/>
-    <hyperlink ref="L59" r:id="rId58" xr:uid="{5D5DD823-BEAD-4002-8FC4-1382A6ECCBED}"/>
-    <hyperlink ref="L60" r:id="rId59" xr:uid="{8716DD53-5EC7-46AB-A027-44830796C7CA}"/>
-    <hyperlink ref="L61" r:id="rId60" xr:uid="{A614186C-C6BA-4C7C-A88A-71A1FA704D78}"/>
+    <hyperlink ref="L2" r:id="rId1" xr:uid="{6D0044F8-64EB-4C26-80BD-855334CB67F6}"/>
+    <hyperlink ref="L3" r:id="rId2" xr:uid="{8D591168-9A54-4297-8172-98C3ED2631DC}"/>
+    <hyperlink ref="L4" r:id="rId3" xr:uid="{7F64F6A7-40FD-4621-9630-55F72163E88D}"/>
+    <hyperlink ref="L5" r:id="rId4" xr:uid="{D18415F4-7FD3-4384-8DF9-A68FD889A836}"/>
+    <hyperlink ref="L6" r:id="rId5" xr:uid="{D06B767D-4DA4-49A2-8018-F420718709A3}"/>
+    <hyperlink ref="L7" r:id="rId6" xr:uid="{BA7FE18D-54C2-417F-B887-7BECDA9C2467}"/>
+    <hyperlink ref="L8" r:id="rId7" xr:uid="{8B19968C-5A96-49F8-AB2A-89B0D9EFF11F}"/>
+    <hyperlink ref="L9" r:id="rId8" xr:uid="{5B9C64A4-4249-4639-8CBC-5B9D5009F19B}"/>
+    <hyperlink ref="L10" r:id="rId9" xr:uid="{71495D91-B812-4994-A91F-3B866E0F6FDD}"/>
+    <hyperlink ref="L11" r:id="rId10" xr:uid="{21B966C0-0E0C-424E-941E-8B63E98E8249}"/>
+    <hyperlink ref="L12" r:id="rId11" xr:uid="{AB17AD24-F322-4413-996E-8C98535CE044}"/>
+    <hyperlink ref="L13" r:id="rId12" xr:uid="{BB273E1A-747C-4D82-8319-A4BC08BA230D}"/>
+    <hyperlink ref="L14" r:id="rId13" xr:uid="{5101A74E-36D2-447C-AE09-6040186B340C}"/>
+    <hyperlink ref="L15" r:id="rId14" xr:uid="{606FF1CA-3263-419F-81FD-5E6C7AFB49B3}"/>
+    <hyperlink ref="L16" r:id="rId15" xr:uid="{DF26DD02-85E0-4584-8D24-5A990A1F351F}"/>
+    <hyperlink ref="L17" r:id="rId16" xr:uid="{1CF18A64-FFF9-4F2B-9DB1-0DC1368F652D}"/>
+    <hyperlink ref="L18" r:id="rId17" xr:uid="{587518CE-C8A5-41FA-AC56-55F2B9CD578B}"/>
+    <hyperlink ref="L19" r:id="rId18" xr:uid="{859048BD-4562-480C-B782-5F876EDF150B}"/>
+    <hyperlink ref="L20" r:id="rId19" xr:uid="{0BD91D9E-F0C7-4E23-BD6D-3510644C43D6}"/>
+    <hyperlink ref="L21" r:id="rId20" xr:uid="{C5076C41-5623-45F5-A2F2-609F4EB3C983}"/>
+    <hyperlink ref="L22" r:id="rId21" xr:uid="{DDB90FA0-8053-4E4C-AB81-06D9B67EE1A2}"/>
+    <hyperlink ref="L23" r:id="rId22" xr:uid="{998EADB0-68A8-44F4-9278-2878B41CEAD1}"/>
+    <hyperlink ref="L24" r:id="rId23" xr:uid="{0C9C97CD-91A6-4A03-8214-576F6BC68284}"/>
+    <hyperlink ref="L25" r:id="rId24" xr:uid="{0CA04A0E-073B-46F9-B3BD-ED8AAEA1DCA3}"/>
+    <hyperlink ref="L26" r:id="rId25" xr:uid="{EB9AB640-2568-4895-B2FA-61A9D6F4FCB1}"/>
+    <hyperlink ref="L27" r:id="rId26" xr:uid="{9FA0840A-44EF-4F85-AB59-4A77ABE5A880}"/>
+    <hyperlink ref="L28" r:id="rId27" xr:uid="{4E68A68C-49D7-4D8E-A72B-77DC5F594803}"/>
+    <hyperlink ref="L29" r:id="rId28" xr:uid="{BAB3BFAA-62CF-49B3-8A36-7715A24D731C}"/>
+    <hyperlink ref="L30" r:id="rId29" xr:uid="{D4BFAB36-5FDF-4156-85BE-4CE9F193050A}"/>
+    <hyperlink ref="L31" r:id="rId30" xr:uid="{DD429416-16F4-4277-9FB6-5E4E2819159E}"/>
+    <hyperlink ref="L32" r:id="rId31" xr:uid="{C627DE19-BD34-4718-8B96-F67E3B4F91E6}"/>
+    <hyperlink ref="L33" r:id="rId32" xr:uid="{95265EED-FEC5-43CC-A822-64097A453EFB}"/>
+    <hyperlink ref="L34" r:id="rId33" xr:uid="{7E595AE3-7C87-4E4B-ABAC-6D1CAFBAFB42}"/>
+    <hyperlink ref="L35" r:id="rId34" xr:uid="{E4137B39-BD2A-4173-8725-2584B1DAE35A}"/>
+    <hyperlink ref="L36" r:id="rId35" xr:uid="{8C79197E-F47A-42B0-AFDA-E7DDF52F3501}"/>
+    <hyperlink ref="L37" r:id="rId36" xr:uid="{37CDE7EF-5F51-425A-AA7F-10108597B421}"/>
+    <hyperlink ref="L38" r:id="rId37" xr:uid="{4A0E5DFD-8642-4932-BBD8-866A71647D89}"/>
+    <hyperlink ref="L39" r:id="rId38" xr:uid="{2B58BCB2-C710-4F26-AA36-328289ECCA0B}"/>
+    <hyperlink ref="L40" r:id="rId39" xr:uid="{437D0C8C-EA7A-4D77-82C7-A330397DE89F}"/>
+    <hyperlink ref="L41" r:id="rId40" xr:uid="{926D04FE-6298-4FCD-9F92-0FB9433D7F43}"/>
+    <hyperlink ref="L42" r:id="rId41" xr:uid="{E384A095-7B12-4083-BBF8-C85609F2CEAE}"/>
+    <hyperlink ref="L43" r:id="rId42" xr:uid="{3ECB3568-F82E-485D-9FC4-1202B56C12D9}"/>
+    <hyperlink ref="L44" r:id="rId43" xr:uid="{0B17781E-5750-42C0-A278-EBEFB8361537}"/>
+    <hyperlink ref="L45" r:id="rId44" xr:uid="{093B94A9-4778-494E-AA8B-37D7CFB3469E}"/>
+    <hyperlink ref="L46" r:id="rId45" xr:uid="{A93AC240-A89D-4AED-AFB5-1FAC096A6097}"/>
+    <hyperlink ref="L47" r:id="rId46" xr:uid="{FCD80744-531B-4526-995E-B1A241D53D51}"/>
+    <hyperlink ref="L48" r:id="rId47" xr:uid="{5CF8B241-7DBB-4677-928A-099C8CEBB02A}"/>
+    <hyperlink ref="L49" r:id="rId48" xr:uid="{5387F6F8-B905-4B9C-BEC0-DEBE36053015}"/>
+    <hyperlink ref="L50" r:id="rId49" xr:uid="{2422E403-7C45-4716-A796-EE1328DFDC35}"/>
+    <hyperlink ref="L51" r:id="rId50" xr:uid="{836EF01D-ABDD-452E-B250-401D2C531F0C}"/>
+    <hyperlink ref="L52" r:id="rId51" xr:uid="{137AC9D1-A443-4F46-B22F-7EEE3581CCE7}"/>
+    <hyperlink ref="L53" r:id="rId52" xr:uid="{033ED722-812C-41AB-BF86-DD10B8C610E9}"/>
+    <hyperlink ref="L54" r:id="rId53" xr:uid="{17D02DA9-B15B-40AD-9C8D-99C536E7E647}"/>
+    <hyperlink ref="L55" r:id="rId54" xr:uid="{06DB301C-0945-4A8D-9517-6A0EB6A237CB}"/>
+    <hyperlink ref="L56" r:id="rId55" xr:uid="{98F833D5-6258-47B4-BB61-E865EC3A5C95}"/>
+    <hyperlink ref="L57" r:id="rId56" xr:uid="{51781501-A7EF-409F-B92E-CDE1C9408A90}"/>
+    <hyperlink ref="L58" r:id="rId57" xr:uid="{5D1E9207-C176-4608-B44A-E3E1B1BC75F8}"/>
+    <hyperlink ref="L59" r:id="rId58" xr:uid="{30F3FA80-AA79-4484-A7FF-7C1BC55A67F6}"/>
+    <hyperlink ref="L60" r:id="rId59" xr:uid="{5E11E900-9917-402C-8DB8-39BCB5B76B33}"/>
+    <hyperlink ref="L61" r:id="rId60" xr:uid="{858543F0-C883-4189-8035-61A8A006DF12}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/minimarket.xlsx
+++ b/data/minimarket.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SEMESTER 6\PRAK. SIGTER\PROJECT AKHIR\STUDENT SURVIVAL MAP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1D237E-5A1B-4802-AECB-DE23800143E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F32E6B2-E462-4D04-AE40-C5590BC5E491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F35F33EF-EB1F-4670-92AD-4BBD8F6B088B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="351">
   <si>
     <t>Latitude</t>
   </si>
@@ -429,1008 +429,24 @@
     <t>Indomaret Jl Kaliurang KM 8,3</t>
   </si>
   <si>
-    <t>-7,733752545117078</t>
-  </si>
-  <si>
-    <t>110,39419756395505</t>
-  </si>
-  <si>
-    <t>Jl, Kaliurang Km 8,3 Prujukan Rt 2/3 Sinduharjo, Tambakan, Sinduharjo, Sleman, Sleman Regency, Special Region of Yogyakarta 55581</t>
-  </si>
-  <si>
-    <t>07,00-22,00</t>
-  </si>
-  <si>
-    <t>3,3/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/HvGAw3yRT4Z41LoZ7</t>
-  </si>
-  <si>
-    <t>-7,749447245716337</t>
-  </si>
-  <si>
-    <t>110,38578306135572</t>
-  </si>
-  <si>
-    <t>Jl, Kaliurang, Kentungan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>3,8/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/hrcCoQa6NbGUDMs58</t>
-  </si>
-  <si>
-    <t>-7,756250064506058</t>
-  </si>
-  <si>
-    <t>110,37932712120767</t>
-  </si>
-  <si>
-    <t>Jl, Kaliurang, Km 5, 2, Catur Tunggal, Kec, Depok, Jl, Kaliurang No,27, Karang Wuni, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55284</t>
-  </si>
-  <si>
-    <t>3,9/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/yuGPo2Cdzm1cwWWFA</t>
-  </si>
-  <si>
-    <t>-7,752217570012537</t>
-  </si>
-  <si>
-    <t>110,38218871514682</t>
-  </si>
-  <si>
     <t>Jalan Pandega Marta No, 1 Sarimulyo Manggung, Manggung, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
   </si>
   <si>
-    <t>3,4/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/y7eFw3yPzy8XiyVH8</t>
-  </si>
-  <si>
-    <t>-7,765916891413229</t>
-  </si>
-  <si>
-    <t>110,39147146767357</t>
-  </si>
-  <si>
-    <t>Jl, Affandi No,31a, Karang Gayam, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>3,1/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/FcK4Bx17jAYCpJhX8</t>
-  </si>
-  <si>
-    <t>-7,758056400724876</t>
-  </si>
-  <si>
-    <t>110,39494223275801</t>
-  </si>
-  <si>
-    <t>Jl, Affandi No,23, Soropadan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/gk9yBhy1XfxyNVp5A</t>
-  </si>
-  <si>
-    <t>-7,752947002982559</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 110,39672719765858</t>
-  </si>
-  <si>
-    <t>Jl, Anggajaya 1 No,282, Sanggrahan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>3,2/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/U18wT9wYGWXs2n1dA</t>
-  </si>
-  <si>
-    <t>-7,749895190158755</t>
-  </si>
-  <si>
-    <t>110,39808053648082</t>
-  </si>
-  <si>
-    <t>Jl, Sukoharjo No,133 A, Sanggrahan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4,1/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/ACN1JDZCWuDx7x3c9</t>
-  </si>
-  <si>
-    <t>-7,7425767277541</t>
-  </si>
-  <si>
-    <t>110,39742175575905</t>
-  </si>
-  <si>
-    <t>Jl, Rajawali Raya No,32, Sanggrahan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4,3/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/vtbQovKZLG9tKWRM9</t>
-  </si>
-  <si>
-    <t>-7,749210435076886</t>
-  </si>
-  <si>
-    <t>110,40617648604177</t>
-  </si>
-  <si>
-    <t>Jl, Cemp, No,60, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4,5/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/Nj7awyKrLigPrPDt5</t>
-  </si>
-  <si>
-    <t>-7,748732158171262</t>
-  </si>
-  <si>
-    <t>110,41114301296018</t>
-  </si>
-  <si>
-    <t>Jl, Nusa Indah No,249, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/UWnDTdNhGfGvs4cf6</t>
-  </si>
-  <si>
-    <t>-7,752859025575523</t>
-  </si>
-  <si>
-    <t>110,40985387164312</t>
-  </si>
-  <si>
-    <t>Jl, Nusa Indah II No,50, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>2,7/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/wtP4be5hRqgrhRSLA</t>
-  </si>
-  <si>
-    <t>-7,765337640697154</t>
-  </si>
-  <si>
-    <t>110,39597081132904</t>
-  </si>
-  <si>
-    <t>JL, Empu Tantular, No, 106, Pringwulung, Condongcatur, Depok, Jl, Tantular No,103, Kaliwaru, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>3,5/5/0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/BFdQ2TDQ9pBMcoAX8</t>
-  </si>
-  <si>
     <t>Indomaret Tantular No, 409 (FY5C)</t>
   </si>
   <si>
-    <t>-7,769195812965372</t>
-  </si>
-  <si>
-    <t>110,3954706508378</t>
-  </si>
-  <si>
-    <t>Jl, Tantular Selatan, Pringwulung, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4,2/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/x2AwyBvdkzFEaSBq6</t>
-  </si>
-  <si>
-    <t>-7,766357839864531</t>
-  </si>
-  <si>
-    <t>110,40251671938006</t>
-  </si>
-  <si>
-    <t>Jl, Wahid Hasyim No,5, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/RnsoQmriB1m6i3AZ8</t>
-  </si>
-  <si>
-    <t>-7,769020449248469</t>
-  </si>
-  <si>
-    <t>110,4051622426191</t>
-  </si>
-  <si>
-    <t>Jl, Perumnas No,8, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/7pUGd4KNk2rEpYPh9</t>
-  </si>
-  <si>
-    <t>-7,764893740448012</t>
-  </si>
-  <si>
-    <t>110,40570764856093</t>
-  </si>
-  <si>
-    <t>Indomaret, Jl, Perumnas, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>3,6/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/i2NX2in6kMciJJ2f8</t>
-  </si>
-  <si>
-    <t>-7,7638932991633425</t>
-  </si>
-  <si>
-    <t>110,40900868735301</t>
-  </si>
-  <si>
-    <t>Jl, Pintu Selatan UPN, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/yiqGLnZVyKNjwWkj6?g_st=ac</t>
-  </si>
-  <si>
-    <t>-7,764463124084063</t>
-  </si>
-  <si>
-    <t>110,41105130801496</t>
-  </si>
-  <si>
-    <t>Ruko Pulohdadi, Jl, Seturan Raya Blok A2, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/YaX6UcnU3gT1rtmEA</t>
-  </si>
-  <si>
-    <t>-7,769901074159813</t>
-  </si>
-  <si>
-    <t>110,4098548994134</t>
-  </si>
-  <si>
-    <t>Jl, Seturan Raya, RT,4/RW,2, Kledokan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/rf4pXZ5op64fGaEM8</t>
-  </si>
-  <si>
-    <t>-7,744073071243356</t>
-  </si>
-  <si>
-    <t>110,41459663470026</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/fufaosvrsao483j99</t>
-  </si>
-  <si>
-    <t>-7,769789454884158</t>
-  </si>
-  <si>
-    <t>110,402001372579</t>
-  </si>
-  <si>
-    <t>Jl, Wahid Hasyim No,130Dabag, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/x4QJfLUQkhHWqZ137</t>
-  </si>
-  <si>
-    <t>-7,781287170789081</t>
-  </si>
-  <si>
-    <t>110,41401363389748</t>
-  </si>
-  <si>
-    <t>Jl, Babarsari No,11, Janti, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/E5VGMWFMkCHfZriL7</t>
-  </si>
-  <si>
-    <t>-7,76074441972423</t>
-  </si>
-  <si>
-    <t>110,42005087958772</t>
-  </si>
-  <si>
-    <t>Jl, P, Puger 1 No,2, Pugeran, Maguwoharjo, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>2,5/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/6ptXJdnoMD4LfxAm6</t>
-  </si>
-  <si>
-    <t>-7,771760619476064</t>
-  </si>
-  <si>
-    <t>110,40402001483787</t>
-  </si>
-  <si>
-    <t>Jl, Perumnas, Nologaten, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/kQbgHLjC9CHXDVUd8</t>
-  </si>
-  <si>
-    <t>-7,767021127082602</t>
-  </si>
-  <si>
-    <t>110,39044549226743</t>
-  </si>
-  <si>
-    <t>Jl, Affandi, Karang Gayam, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/D3hU9pNhRSwwefzd8</t>
-  </si>
-  <si>
-    <t>-7,756085604225498</t>
-  </si>
-  <si>
-    <t>110,3943908636679</t>
-  </si>
-  <si>
-    <t>Jl, Anggajaya III No,66, Gejayan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>4,4/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/SaS1WCo3QxG3jwW48</t>
-  </si>
-  <si>
-    <t>-7,7757624268869865</t>
-  </si>
-  <si>
-    <t>110,3946526972518</t>
-  </si>
-  <si>
-    <t>Jl, Petung No,7, Papringan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/qQN4SrSZBWcQTHjU8</t>
-  </si>
-  <si>
-    <t>-7,77254523832928</t>
-  </si>
-  <si>
-    <t>110,41586671232616</t>
-  </si>
-  <si>
-    <t>Jl, Babarsari, Tambak Bayan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/jZqh5aGaYjRwjM1Q9</t>
-  </si>
-  <si>
-    <t>-7,7750608431802695</t>
-  </si>
-  <si>
-    <t>110,41612060615564</t>
-  </si>
-  <si>
-    <t>Jl, Babarsari No,23DTambak Bayan, Tambak Bayan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/FKLhFzTtUv9Svu8X8</t>
-  </si>
-  <si>
-    <t>-7,780008155389338</t>
-  </si>
-  <si>
-    <t>110,41434334934921</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/SXgbsSj6UDL5eM7v7</t>
-  </si>
-  <si>
-    <t>-7,778918074660311</t>
-  </si>
-  <si>
-    <t>110,40850379127096</t>
-  </si>
-  <si>
-    <t>Jl, Kapas No,7, Ngentak, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4,0/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/v5r9juBWxgPk1Bog6</t>
-  </si>
-  <si>
-    <t>-7,782104456519171</t>
-  </si>
-  <si>
-    <t>110,41045031063037</t>
-  </si>
-  <si>
-    <t>Jl, Raya Janti No,3, Gowok, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/wWMHH899sSHvLsLJ7</t>
-  </si>
-  <si>
-    <t>-7,730661259789763</t>
-  </si>
-  <si>
-    <t>110,39141445284271</t>
-  </si>
-  <si>
-    <t>Jl, Damai Dk, Prujakan, RT,01/RW,32, Tambakan, Sinduharjo, Kec, Ngaglik, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55581</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/Hkk5NCU4DLaffHSk8</t>
-  </si>
-  <si>
     <t>Alfamart Kaliurang KM 8,1</t>
   </si>
   <si>
-    <t>-7,733212770145344</t>
-  </si>
-  <si>
-    <t>110,39450435764837</t>
-  </si>
-  <si>
-    <t>Jl, Kaliurang 8,1 No, 72, RT,04/RW,33, Tambakan, Sinduharjo, Kec, Ngaglik, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55581</t>
-  </si>
-  <si>
-    <t>3,7/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/ZP2CpU3Z8afNahNt5</t>
-  </si>
-  <si>
-    <t>-7,752603744250776</t>
-  </si>
-  <si>
-    <t>110,38128643153526</t>
-  </si>
-  <si>
-    <t>Jl, Kaliurang Km 5,6 Rt 01 Rw 01, Dk Manggung Kel, Manggung, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>08,00-23,00</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/hFHpxtCSXm4rSsPWA</t>
-  </si>
-  <si>
-    <t>-7,739846624846841</t>
-  </si>
-  <si>
-    <t>110,40240078104064</t>
-  </si>
-  <si>
-    <t>Jl, Raya Manukan Kel No,Rt, 05, RW,Iv, Manukan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/LLdHixFNGbzeXS5M9</t>
-  </si>
-  <si>
-    <t>-7,741377499571684</t>
-  </si>
-  <si>
-    <t>110,41098384994527</t>
-  </si>
-  <si>
-    <t>Jl, Candi Gebang, Jetis, Wedomartani, Kec, Ngemplak, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55282</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/gWeNBEXEgqUYBySc8</t>
-  </si>
-  <si>
-    <t>-7,750902817325119</t>
-  </si>
-  <si>
-    <t>110,3984525693445</t>
-  </si>
-  <si>
-    <t>Jl, Anggajaya 2 Kel No,75B, RT,04/RW,09, Sanggrahan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>3,0/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/VfSbdzbDWi5UdNs68</t>
-  </si>
-  <si>
-    <t>-7,756502140675588</t>
-  </si>
-  <si>
-    <t>110,40329998540003</t>
-  </si>
-  <si>
-    <t>Jl, Ring Road Utara No,160, Perumnas Condong Catur, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/2HTUZCfFgRj1mc689</t>
-  </si>
-  <si>
-    <t>-7,758410435461992</t>
-  </si>
-  <si>
-    <t>110,40632643116737</t>
-  </si>
-  <si>
-    <t>Jl, Ring Road Utara No,Kel, Perumnas Condong Catur, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/biQStQVcheFZL4fN8</t>
-  </si>
-  <si>
-    <t>-7,760641876439936</t>
-  </si>
-  <si>
-    <t>110,41567434281566</t>
-  </si>
-  <si>
     <t>Jalan Ringroad Utara, Mancasan Kidul, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
   </si>
   <si>
-    <t>07,00-23,00</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/EpAysQ3WXUkqcna2A</t>
-  </si>
-  <si>
-    <t>-7,7729243349685735</t>
-  </si>
-  <si>
-    <t>110,41312950657385</t>
-  </si>
-  <si>
-    <t>Jl, Babarsari Ct 19, Kel, Tambak Bayan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>10,00-21,00</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/wJ3bHdk31Wbs57Jf7</t>
-  </si>
-  <si>
-    <t>-7,76691020590576</t>
-  </si>
-  <si>
-    <t>110,40986108656197</t>
-  </si>
-  <si>
-    <t>Jl, Seturan Raya No,Kel Blok C No,5, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>2,3/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/pLVtxDoDFYRnXBfS7</t>
-  </si>
-  <si>
-    <t>-7,763377003772743</t>
-  </si>
-  <si>
-    <t>110,40540371062711</t>
-  </si>
-  <si>
-    <t>Jl, Perumnas No,106, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/69ffCYJN4SpQF2DW8</t>
-  </si>
-  <si>
-    <t>-7,765364433687017</t>
-  </si>
-  <si>
-    <t>110,40243212676862</t>
-  </si>
-  <si>
-    <t>Jl, Wahid Hasyim No,Kel, RW,No: 6, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/brniKuRnRZYaVX8F6</t>
-  </si>
-  <si>
-    <t>-7,761536782621959</t>
-  </si>
-  <si>
-    <t>110,39559748366851</t>
-  </si>
-  <si>
     <t>Gg, Jemb, Merah Kel No,103 A, RT,04/RW,06, Soropadan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
   </si>
   <si>
-    <t>09,00-22,00</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/bJxupU96DGrmDFjY7</t>
-  </si>
-  <si>
-    <t>-7,770126662899377</t>
-  </si>
-  <si>
-    <t>110,38942776021663</t>
-  </si>
-  <si>
-    <t>Jl, Affandi Kel No,21 A, Santren, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>06,00-22,00</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/mDaN88tVqkM2FXoNA</t>
-  </si>
-  <si>
-    <t>-7,776009658807369</t>
-  </si>
-  <si>
-    <t>110,3854961371992</t>
-  </si>
-  <si>
-    <t>Jl, Colombo 13/30, Desa Kel No,Rt, 04, RT,04/RW,02, Samirono, Caturtunggal, Depok, Sleman Regency, Special Region of Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/nvtwnSp9Uzx7WN8fA</t>
-  </si>
-  <si>
-    <t>-7,774319145981829</t>
-  </si>
-  <si>
-    <t>110,39359100168197</t>
-  </si>
-  <si>
-    <t>Jl, Pringgodani Kel No,8, RT,19/RW,14, Mrican, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>2,2/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/XkByBoZZxTmunCKW6</t>
-  </si>
-  <si>
-    <t>-7,770417559044908</t>
-  </si>
-  <si>
-    <t>110,40143654905349</t>
-  </si>
-  <si>
-    <t>Jl, Nologaten No,187, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/apZbFsSCBr6EYLRT9</t>
-  </si>
-  <si>
-    <t>-7,771095549600947</t>
-  </si>
-  <si>
-    <t>110,40178587703575</t>
-  </si>
-  <si>
-    <t>Dkh,Dabag, Jl, Wahid Hasyim Kel No,11, RT,008/RW,027, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/VrgpLuxUPrsUphA38</t>
-  </si>
-  <si>
-    <t>-7,77159183805787</t>
-  </si>
-  <si>
-    <t>110,40423466690144</t>
-  </si>
-  <si>
-    <t>Jl, Perumnas No, 85, Komplek Graha Strategic Blok A3 / A4 Kel, Dabag, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>09,00-21,00</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/XafqcjhRZgeAV1c77</t>
-  </si>
-  <si>
-    <t>-7,763065828579438</t>
-  </si>
-  <si>
-    <t>110,40756256677764</t>
-  </si>
-  <si>
-    <t>Jl, Pintu Selatan UPN No,3, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/sXSR64xef5eu8CCL8</t>
-  </si>
-  <si>
-    <t>-7,760820680118197</t>
-  </si>
-  <si>
-    <t>110,40799963210634</t>
-  </si>
-  <si>
     <t>Universitas Pembangunan Nasional "Veteran, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
   </si>
   <si>
-    <t>08,00-20,00</t>
-  </si>
-  <si>
-    <t>5,0/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/K8a86JiuLDtJy7Z98</t>
-  </si>
-  <si>
-    <t>-7,76318000437515</t>
-  </si>
-  <si>
-    <t>110,40996607313167</t>
-  </si>
-  <si>
-    <t>Jl, Pintu Selatan UPN Jl, Seturan Raya, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/kU2uvJp8YCZwLjSG6</t>
-  </si>
-  <si>
-    <t>-7,770692904079514</t>
-  </si>
-  <si>
-    <t>110,40972750368472</t>
-  </si>
-  <si>
-    <t>Depok Sports Center, Jl, Seturan Raya Kav,IV, Kledokan, Caturtunggal, Depok, Sleman Regency, Special Region of Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>10,00-22,00</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/2qZxGGcCcJtkY1g39</t>
-  </si>
-  <si>
-    <t>-7,758533872322579</t>
-  </si>
-  <si>
-    <t>110,41282053517918</t>
-  </si>
-  <si>
-    <t>Jl, Cendrawasih No,90b, Ngringin, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>06,00-21,00</t>
-  </si>
-  <si>
-    <t>4,6/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/Whhj3uPkLXoK1M1Y7</t>
-  </si>
-  <si>
-    <t>-7,7496373777161125</t>
-  </si>
-  <si>
-    <t>110,41077505786859</t>
-  </si>
-  <si>
-    <t>Jl, Candi Gebang, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>07,30-21,30</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/FLzj6sN18SWF7E4C6</t>
-  </si>
-  <si>
-    <t>-7,782078923814419</t>
-  </si>
-  <si>
-    <t>110,41443305384664</t>
-  </si>
-  <si>
-    <t>Jl, Raya Solo - Yogyakarta Jl, Babarsari No,KM, 7, Janti, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>08,30-21,30</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/8eNFKmsacyiLPxVA9</t>
-  </si>
-  <si>
-    <t>images\M001,jpg</t>
-  </si>
-  <si>
-    <t>images\M002,jpg</t>
-  </si>
-  <si>
-    <t>images\M003,jpg</t>
-  </si>
-  <si>
-    <t>images\M004,jpg</t>
-  </si>
-  <si>
-    <t>images\M005,jpg</t>
-  </si>
-  <si>
-    <t>images\M006,jpg</t>
-  </si>
-  <si>
-    <t>images\M007,jpg</t>
-  </si>
-  <si>
-    <t>images\M008,jpg</t>
-  </si>
-  <si>
-    <t>images\M009,jpg</t>
-  </si>
-  <si>
-    <t>images\M010,jpg</t>
-  </si>
-  <si>
-    <t>images\M011,jpg</t>
-  </si>
-  <si>
-    <t>images\M012,jpg</t>
-  </si>
-  <si>
-    <t>images\M013,jpg</t>
-  </si>
-  <si>
-    <t>images\M014,jpg</t>
-  </si>
-  <si>
-    <t>images\M015,jpg</t>
-  </si>
-  <si>
-    <t>images\M016,jpg</t>
-  </si>
-  <si>
-    <t>images\M017,jpg</t>
-  </si>
-  <si>
-    <t>images\M018,png</t>
-  </si>
-  <si>
-    <t>images\M019,jpg</t>
-  </si>
-  <si>
-    <t>images\M020,jpg</t>
-  </si>
-  <si>
-    <t>images\M021,jpg</t>
-  </si>
-  <si>
-    <t>images\M022,jpg</t>
-  </si>
-  <si>
-    <t>images\M023,jpg</t>
-  </si>
-  <si>
-    <t>images\M024,jpg</t>
-  </si>
-  <si>
-    <t>images\M025,jpg</t>
-  </si>
-  <si>
-    <t>images\M026,jpg</t>
-  </si>
-  <si>
-    <t>images\M027,jpg</t>
-  </si>
-  <si>
-    <t>images\M028,jpg</t>
-  </si>
-  <si>
-    <t>images\M029,jpg</t>
-  </si>
-  <si>
-    <t>images\M030,jpg</t>
-  </si>
-  <si>
-    <t>images\M031,jpg</t>
-  </si>
-  <si>
-    <t>images\M032,jpg</t>
-  </si>
-  <si>
-    <t>images\M033,jpg</t>
-  </si>
-  <si>
-    <t>images\M034,jpg</t>
-  </si>
-  <si>
-    <t>images\M035,jpg</t>
-  </si>
-  <si>
-    <t>images\M036,jpg</t>
-  </si>
-  <si>
-    <t>images\M037,jpg</t>
-  </si>
-  <si>
-    <t>images\M038,jpg</t>
-  </si>
-  <si>
-    <t>images\M039,jpg</t>
-  </si>
-  <si>
-    <t>images\M040,jpg</t>
-  </si>
-  <si>
-    <t>images\M041,jpg</t>
-  </si>
-  <si>
-    <t>images\M042,jpg</t>
-  </si>
-  <si>
-    <t>images\M043,jpg</t>
-  </si>
-  <si>
-    <t>images\M044,jpg</t>
-  </si>
-  <si>
-    <t>images\M045,jpg</t>
-  </si>
-  <si>
-    <t>images\M046,jpg</t>
-  </si>
-  <si>
-    <t>images\M047,jpg</t>
-  </si>
-  <si>
-    <t>images\M048,jpg</t>
-  </si>
-  <si>
-    <t>images\M049,jpg</t>
-  </si>
-  <si>
-    <t>images\M050,jpg</t>
-  </si>
-  <si>
-    <t>images\M051,jpg</t>
-  </si>
-  <si>
-    <t>images\M052,jpg</t>
-  </si>
-  <si>
-    <t>images\M053,jpg</t>
-  </si>
-  <si>
-    <t>images\M054,jpg</t>
-  </si>
-  <si>
-    <t>images\M055,jpg</t>
-  </si>
-  <si>
-    <t>images\M056,jpg</t>
-  </si>
-  <si>
-    <t>images\M057,jpg</t>
-  </si>
-  <si>
-    <t>images\M058,jpg</t>
-  </si>
-  <si>
-    <t>images\M059,jpg</t>
-  </si>
-  <si>
-    <t>images\M060,jpg</t>
-  </si>
-  <si>
     <t>Layanan</t>
   </si>
   <si>
@@ -1447,6 +463,630 @@
   </si>
   <si>
     <t>kebutuhan harian, pembayaran tagihan</t>
+  </si>
+  <si>
+    <t>Jl. Kaliurang Km 8,3 Prujukan Rt 2/3 Sinduharjo, Tambakan, Sinduharjo, Sleman, Sleman Regency, Special Region of Yogyakarta 55581</t>
+  </si>
+  <si>
+    <t>Jl. Kaliurang, Kentungan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Kaliurang, Km 5, 2, Catur Tunggal, Kec, Depok, Jl. Kaliurang No,27, Karang Wuni, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55284</t>
+  </si>
+  <si>
+    <t>Jl. Affandi No,31a, Karang Gayam, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Affandi No,23, Soropadan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>Jl. Anggajaya 1 No,282, Sanggrahan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>Jl. Sukoharjo No,133 A, Sanggrahan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Rajawali Raya No,32, Sanggrahan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Cemp, No,60, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Nusa Indah No,249, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Nusa Indah II No,50, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Empu Tantular, No, 106, Pringwulung, Condongcatur, Depok, Jl. Tantular No,103, Kaliwaru, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Tantular Selatan, Pringwulung, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Wahid Hasyim No,5, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Perumnas No,8, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Indomaret, Jl. Perumnas, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Pintu Selatan UPN, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Ruko Pulohdadi, Jl. Seturan Raya Blok A2, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Seturan Raya, RT,4/RW,2, Kledokan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Wahid Hasyim No,130Dabag, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Babarsari No,11, Janti, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. P, Puger 1 No,2, Pugeran, Maguwoharjo, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Perumnas, Nologaten, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Affandi, Karang Gayam, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Anggajaya III No,66, Gejayan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>Jl. Petung No,7, Papringan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Babarsari, Tambak Bayan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Babarsari No,23DTambak Bayan, Tambak Bayan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Kapas No,7, Ngentak, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Raya Janti No,3, Gowok, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Damai Dk, Prujakan, RT,01/RW,32, Tambakan, Sinduharjo, Kec, Ngaglik, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55581</t>
+  </si>
+  <si>
+    <t>Jl. Kaliurang 8,1 No, 72, RT,04/RW,33, Tambakan, Sinduharjo, Kec, Ngaglik, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55581</t>
+  </si>
+  <si>
+    <t>Jl. Kaliurang Km 5,6 Rt 01 Rw 01, Dk Manggung Kel, Manggung, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Raya Manukan Kel No,Rt, 05, RW,Iv, Manukan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>Jl. Candi Gebang, Jetis, Wedomartani, Kec, Ngemplak, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55282</t>
+  </si>
+  <si>
+    <t>Jl. Anggajaya 2 Kel No,75B, RT,04/RW,09, Sanggrahan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>Jl. Ring Road Utara No,160, Perumnas Condong Catur, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>Jl. Ring Road Utara No,Kel, Perumnas Condong Catur, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>Jl. Babarsari Ct 19, Kel, Tambak Bayan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Seturan Raya No,Kel Blok C No,5, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Perumnas No,106, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Wahid Hasyim No,Kel, RW,No: 6, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>Jl. Affandi Kel No,21 A, Santren, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Colombo 13/30, Desa Kel No,Rt, 04, RT,04/RW,02, Samirono, Caturtunggal, Depok, Sleman Regency, Special Region of Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Pringgodani Kel No,8, RT,19/RW,14, Mrican, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Nologaten No,187, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Dkh,Dabag, Jl. Wahid Hasyim Kel No,11, RT,008/RW,027, Dabag, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>Jl. Perumnas No, 85, Komplek Graha Strategic Blok A3 / A4 Kel, Dabag, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Pintu Selatan UPN No,3, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Pintu Selatan UPN Jl. Seturan Raya, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Depok Sports Center, Jl. Seturan Raya Kav,IV, Kledokan, Caturtunggal, Depok, Sleman Regency, Special Region of Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Cendrawasih No,90b, Ngringin, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Candi Gebang, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Raya Solo - Yogyakarta Jl. Babarsari No,KM, 7, Janti, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>07.00-22.00</t>
+  </si>
+  <si>
+    <t>08.00-23.00</t>
+  </si>
+  <si>
+    <t>07.00-23.00</t>
+  </si>
+  <si>
+    <t>10.00-21.00</t>
+  </si>
+  <si>
+    <t>09.00-22.00</t>
+  </si>
+  <si>
+    <t>06.00-22.00</t>
+  </si>
+  <si>
+    <t>09.00-21.00</t>
+  </si>
+  <si>
+    <t>08.00-20.00</t>
+  </si>
+  <si>
+    <t>10.00-22.00</t>
+  </si>
+  <si>
+    <t>06.00-21.00</t>
+  </si>
+  <si>
+    <t>07.30-21.30</t>
+  </si>
+  <si>
+    <t>08.30-21.30</t>
+  </si>
+  <si>
+    <t>3.3/5.0</t>
+  </si>
+  <si>
+    <t>3.8/5.0</t>
+  </si>
+  <si>
+    <t>3.9/5.0</t>
+  </si>
+  <si>
+    <t>3.4/5.0</t>
+  </si>
+  <si>
+    <t>3.1/5.0</t>
+  </si>
+  <si>
+    <t>3.2/5.0</t>
+  </si>
+  <si>
+    <t>4.1/5.0</t>
+  </si>
+  <si>
+    <t>4.3/5.0</t>
+  </si>
+  <si>
+    <t>4.5/5.0</t>
+  </si>
+  <si>
+    <t>2.7/5.0</t>
+  </si>
+  <si>
+    <t>3.5/5/0</t>
+  </si>
+  <si>
+    <t>4.2/5.0</t>
+  </si>
+  <si>
+    <t>3.6/5.0</t>
+  </si>
+  <si>
+    <t>2.5/5.0</t>
+  </si>
+  <si>
+    <t>4.4/5.0</t>
+  </si>
+  <si>
+    <t>4.0/5.0</t>
+  </si>
+  <si>
+    <t>3.7/5.0</t>
+  </si>
+  <si>
+    <t>3.0/5.0</t>
+  </si>
+  <si>
+    <t>2.3/5.0</t>
+  </si>
+  <si>
+    <t>2.2/5.0</t>
+  </si>
+  <si>
+    <t>5.0/5.0</t>
+  </si>
+  <si>
+    <t>4.6/5.0</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/HvGAw3yRT4Z41LoZ7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/hrcCoQa6NbGUDMs58</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/yuGPo2Cdzm1cwWWFA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/y7eFw3yPzy8XiyVH8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/FcK4Bx17jAYCpJhX8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/gk9yBhy1XfxyNVp5A</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/U18wT9wYGWXs2n1dA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ACN1JDZCWuDx7x3c9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/vtbQovKZLG9tKWRM9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Nj7awyKrLigPrPDt5</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/UWnDTdNhGfGvs4cf6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/wtP4be5hRqgrhRSLA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/BFdQ2TDQ9pBMcoAX8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/x2AwyBvdkzFEaSBq6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/RnsoQmriB1m6i3AZ8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/7pUGd4KNk2rEpYPh9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/i2NX2in6kMciJJ2f8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/yiqGLnZVyKNjwWkj6?g_st=ac</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/YaX6UcnU3gT1rtmEA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/rf4pXZ5op64fGaEM8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/fufaosvrsao483j99</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/x4QJfLUQkhHWqZ137</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/E5VGMWFMkCHfZriL7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/6ptXJdnoMD4LfxAm6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/kQbgHLjC9CHXDVUd8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/D3hU9pNhRSwwefzd8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/SaS1WCo3QxG3jwW48</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/qQN4SrSZBWcQTHjU8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/jZqh5aGaYjRwjM1Q9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/FKLhFzTtUv9Svu8X8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/SXgbsSj6UDL5eM7v7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/v5r9juBWxgPk1Bog6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/wWMHH899sSHvLsLJ7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Hkk5NCU4DLaffHSk8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ZP2CpU3Z8afNahNt5</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/hFHpxtCSXm4rSsPWA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/LLdHixFNGbzeXS5M9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/gWeNBEXEgqUYBySc8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/VfSbdzbDWi5UdNs68</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/2HTUZCfFgRj1mc689</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/biQStQVcheFZL4fN8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/EpAysQ3WXUkqcna2A</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/wJ3bHdk31Wbs57Jf7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/pLVtxDoDFYRnXBfS7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/69ffCYJN4SpQF2DW8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/brniKuRnRZYaVX8F6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/bJxupU96DGrmDFjY7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/mDaN88tVqkM2FXoNA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/nvtwnSp9Uzx7WN8fA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/XkByBoZZxTmunCKW6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/apZbFsSCBr6EYLRT9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/VrgpLuxUPrsUphA38</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/XafqcjhRZgeAV1c77</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/sXSR64xef5eu8CCL8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/K8a86JiuLDtJy7Z98</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/kU2uvJp8YCZwLjSG6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/2qZxGGcCcJtkY1g39</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Whhj3uPkLXoK1M1Y7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/FLzj6sN18SWF7E4C6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/8eNFKmsacyiLPxVA9</t>
+  </si>
+  <si>
+    <t>images\M001.jpg</t>
+  </si>
+  <si>
+    <t>images\M002.jpg</t>
+  </si>
+  <si>
+    <t>images\M003.jpg</t>
+  </si>
+  <si>
+    <t>images\M004.jpg</t>
+  </si>
+  <si>
+    <t>images\M005.jpg</t>
+  </si>
+  <si>
+    <t>images\M006.jpg</t>
+  </si>
+  <si>
+    <t>images\M007.jpg</t>
+  </si>
+  <si>
+    <t>images\M008.jpg</t>
+  </si>
+  <si>
+    <t>images\M009.jpg</t>
+  </si>
+  <si>
+    <t>images\M010.jpg</t>
+  </si>
+  <si>
+    <t>images\M011.jpg</t>
+  </si>
+  <si>
+    <t>images\M012.jpg</t>
+  </si>
+  <si>
+    <t>images\M013.jpg</t>
+  </si>
+  <si>
+    <t>images\M014.jpg</t>
+  </si>
+  <si>
+    <t>images\M015.jpg</t>
+  </si>
+  <si>
+    <t>images\M016.jpg</t>
+  </si>
+  <si>
+    <t>images\M017.jpg</t>
+  </si>
+  <si>
+    <t>images\M018.png</t>
+  </si>
+  <si>
+    <t>images\M019.jpg</t>
+  </si>
+  <si>
+    <t>images\M020.jpg</t>
+  </si>
+  <si>
+    <t>images\M021.jpg</t>
+  </si>
+  <si>
+    <t>images\M022.jpg</t>
+  </si>
+  <si>
+    <t>images\M023.jpg</t>
+  </si>
+  <si>
+    <t>images\M024.jpg</t>
+  </si>
+  <si>
+    <t>images\M025.jpg</t>
+  </si>
+  <si>
+    <t>images\M026.jpg</t>
+  </si>
+  <si>
+    <t>images\M027.jpg</t>
+  </si>
+  <si>
+    <t>images\M028.jpg</t>
+  </si>
+  <si>
+    <t>images\M029.jpg</t>
+  </si>
+  <si>
+    <t>images\M030.jpg</t>
+  </si>
+  <si>
+    <t>images\M031.jpg</t>
+  </si>
+  <si>
+    <t>images\M032.jpg</t>
+  </si>
+  <si>
+    <t>images\M033.jpg</t>
+  </si>
+  <si>
+    <t>images\M034.jpg</t>
+  </si>
+  <si>
+    <t>images\M035.jpg</t>
+  </si>
+  <si>
+    <t>images\M036.jpg</t>
+  </si>
+  <si>
+    <t>images\M037.jpg</t>
+  </si>
+  <si>
+    <t>images\M038.jpg</t>
+  </si>
+  <si>
+    <t>images\M039.jpg</t>
+  </si>
+  <si>
+    <t>images\M040.jpg</t>
+  </si>
+  <si>
+    <t>images\M041.jpg</t>
+  </si>
+  <si>
+    <t>images\M042.jpg</t>
+  </si>
+  <si>
+    <t>images\M043.jpg</t>
+  </si>
+  <si>
+    <t>images\M044.jpg</t>
+  </si>
+  <si>
+    <t>images\M045.jpg</t>
+  </si>
+  <si>
+    <t>images\M046.jpg</t>
+  </si>
+  <si>
+    <t>images\M047.jpg</t>
+  </si>
+  <si>
+    <t>images\M048.jpg</t>
+  </si>
+  <si>
+    <t>images\M049.jpg</t>
+  </si>
+  <si>
+    <t>images\M050.jpg</t>
+  </si>
+  <si>
+    <t>images\M051.jpg</t>
+  </si>
+  <si>
+    <t>images\M052.jpg</t>
+  </si>
+  <si>
+    <t>images\M053.jpg</t>
+  </si>
+  <si>
+    <t>images\M054.jpg</t>
+  </si>
+  <si>
+    <t>images\M055.jpg</t>
+  </si>
+  <si>
+    <t>images\M056.jpg</t>
+  </si>
+  <si>
+    <t>images\M057.jpg</t>
+  </si>
+  <si>
+    <t>images\M058.jpg</t>
+  </si>
+  <si>
+    <t>images\M059.jpg</t>
+  </si>
+  <si>
+    <t>images\M060.jpg</t>
   </si>
 </sst>
 </file>
@@ -1933,7 +1573,7 @@
     <col min="10" max="10" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="51.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.5546875" customWidth="1"/>
     <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1945,7 +1585,7 @@
         <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>465</v>
+        <v>137</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>0</v>
@@ -1954,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>466</v>
+        <v>138</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>2</v>
@@ -1966,7 +1606,7 @@
         <v>4</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>467</v>
+        <v>139</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>5</v>
@@ -1989,22 +1629,22 @@
         <v>130</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>132</v>
+        <v>140</v>
+      </c>
+      <c r="D2" s="11">
+        <v>-7.7337525451170697</v>
+      </c>
+      <c r="E2" s="11">
+        <v>110.394197563955</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I2" s="12" t="s">
         <v>10</v>
@@ -2013,13 +1653,13 @@
         <v>10</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>135</v>
+        <v>209</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>136</v>
+        <v>231</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>405</v>
+        <v>291</v>
       </c>
       <c r="N2" s="14" t="s">
         <v>11</v>
@@ -2033,22 +1673,22 @@
         <v>19</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
+      </c>
+      <c r="D3" s="11">
+        <v>-7.7494472457163299</v>
+      </c>
+      <c r="E3" s="11">
+        <v>110.385783061355</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I3" s="12" t="s">
         <v>10</v>
@@ -2057,13 +1697,13 @@
         <v>10</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>141</v>
+        <v>232</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>406</v>
+        <v>292</v>
       </c>
       <c r="N3" s="14" t="s">
         <v>11</v>
@@ -2077,22 +1717,22 @@
         <v>21</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
+      </c>
+      <c r="D4" s="11">
+        <v>-7.7562500645060499</v>
+      </c>
+      <c r="E4" s="11">
+        <v>110.379327121207</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>10</v>
@@ -2101,13 +1741,13 @@
         <v>10</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>145</v>
+        <v>211</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>146</v>
+        <v>233</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>407</v>
+        <v>293</v>
       </c>
       <c r="N4" s="14" t="s">
         <v>11</v>
@@ -2121,22 +1761,22 @@
         <v>23</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>148</v>
+        <v>140</v>
+      </c>
+      <c r="D5" s="11">
+        <v>-7.7522175700125304</v>
+      </c>
+      <c r="E5" s="11">
+        <v>110.382188715146</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>10</v>
@@ -2145,13 +1785,13 @@
         <v>10</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>150</v>
+        <v>212</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>151</v>
+        <v>234</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>408</v>
+        <v>294</v>
       </c>
       <c r="N5" s="14" t="s">
         <v>12</v>
@@ -2165,22 +1805,22 @@
         <v>25</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>153</v>
+        <v>140</v>
+      </c>
+      <c r="D6" s="11">
+        <v>-7.7659168914132204</v>
+      </c>
+      <c r="E6" s="11">
+        <v>110.391471467673</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>10</v>
@@ -2189,13 +1829,13 @@
         <v>10</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>156</v>
+        <v>235</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>409</v>
+        <v>295</v>
       </c>
       <c r="N6" s="14" t="s">
         <v>12</v>
@@ -2209,22 +1849,22 @@
         <v>27</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>158</v>
+        <v>140</v>
+      </c>
+      <c r="D7" s="11">
+        <v>-7.75805640072487</v>
+      </c>
+      <c r="E7" s="11">
+        <v>110.394942232758</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>10</v>
@@ -2233,13 +1873,13 @@
         <v>10</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>150</v>
+        <v>212</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>160</v>
+        <v>236</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>410</v>
+        <v>296</v>
       </c>
       <c r="N7" s="14" t="s">
         <v>11</v>
@@ -2253,22 +1893,22 @@
         <v>29</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>162</v>
+        <v>140</v>
+      </c>
+      <c r="D8" s="11">
+        <v>-7.75294700298255</v>
+      </c>
+      <c r="E8" s="11">
+        <v>110.396727197658</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>10</v>
@@ -2277,13 +1917,13 @@
         <v>10</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>411</v>
+        <v>297</v>
       </c>
       <c r="N8" s="14" t="s">
         <v>11</v>
@@ -2297,22 +1937,22 @@
         <v>31</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>167</v>
+        <v>140</v>
+      </c>
+      <c r="D9" s="11">
+        <v>-7.7498951901587496</v>
+      </c>
+      <c r="E9" s="11">
+        <v>110.39808053647999</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I9" s="12" t="s">
         <v>10</v>
@@ -2321,13 +1961,13 @@
         <v>10</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>169</v>
+        <v>215</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>170</v>
+        <v>238</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>412</v>
+        <v>298</v>
       </c>
       <c r="N9" s="14" t="s">
         <v>11</v>
@@ -2341,22 +1981,22 @@
         <v>33</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>172</v>
+        <v>140</v>
+      </c>
+      <c r="D10" s="11">
+        <v>-7.7425767277541002</v>
+      </c>
+      <c r="E10" s="11">
+        <v>110.397421755759</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I10" s="12" t="s">
         <v>10</v>
@@ -2365,13 +2005,13 @@
         <v>10</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>175</v>
+        <v>239</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>413</v>
+        <v>299</v>
       </c>
       <c r="N10" s="14" t="s">
         <v>11</v>
@@ -2385,22 +2025,22 @@
         <v>35</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>177</v>
+        <v>140</v>
+      </c>
+      <c r="D11" s="11">
+        <v>-7.74921043507688</v>
+      </c>
+      <c r="E11" s="11">
+        <v>110.40617648604101</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I11" s="12" t="s">
         <v>10</v>
@@ -2409,13 +2049,13 @@
         <v>10</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>414</v>
+        <v>300</v>
       </c>
       <c r="N11" s="14" t="s">
         <v>11</v>
@@ -2429,22 +2069,22 @@
         <v>37</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>182</v>
+        <v>140</v>
+      </c>
+      <c r="D12" s="11">
+        <v>-7.7487321581712596</v>
+      </c>
+      <c r="E12" s="11">
+        <v>110.41114301296</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>10</v>
@@ -2453,13 +2093,13 @@
         <v>10</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>145</v>
+        <v>211</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>184</v>
+        <v>241</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>415</v>
+        <v>301</v>
       </c>
       <c r="N12" s="14" t="s">
         <v>11</v>
@@ -2473,22 +2113,22 @@
         <v>39</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>186</v>
+        <v>140</v>
+      </c>
+      <c r="D13" s="11">
+        <v>-7.7528590255755203</v>
+      </c>
+      <c r="E13" s="11">
+        <v>110.40985387164299</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>10</v>
@@ -2497,13 +2137,13 @@
         <v>10</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>416</v>
+        <v>302</v>
       </c>
       <c r="N13" s="14" t="s">
         <v>11</v>
@@ -2517,22 +2157,22 @@
         <v>41</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>191</v>
+        <v>140</v>
+      </c>
+      <c r="D14" s="11">
+        <v>-7.7653376406971502</v>
+      </c>
+      <c r="E14" s="11">
+        <v>110.39597081132899</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>10</v>
@@ -2541,13 +2181,13 @@
         <v>10</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>194</v>
+        <v>243</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>417</v>
+        <v>303</v>
       </c>
       <c r="N14" s="14" t="s">
         <v>12</v>
@@ -2558,26 +2198,26 @@
         <v>42</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>195</v>
+        <v>132</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="E15" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="11">
+        <v>-7.7691958129653704</v>
+      </c>
+      <c r="E15" s="11">
+        <v>110.395470650837</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>134</v>
-      </c>
       <c r="I15" s="12" t="s">
         <v>10</v>
       </c>
@@ -2585,13 +2225,13 @@
         <v>10</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>418</v>
+        <v>304</v>
       </c>
       <c r="N15" s="14" t="s">
         <v>11</v>
@@ -2605,22 +2245,22 @@
         <v>44</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>202</v>
+        <v>140</v>
+      </c>
+      <c r="D16" s="11">
+        <v>-7.7663578398645301</v>
+      </c>
+      <c r="E16" s="11">
+        <v>110.40251671938</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>10</v>
@@ -2629,13 +2269,13 @@
         <v>10</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>419</v>
+        <v>305</v>
       </c>
       <c r="N16" s="14" t="s">
         <v>11</v>
@@ -2649,22 +2289,22 @@
         <v>46</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>206</v>
+        <v>140</v>
+      </c>
+      <c r="D17" s="11">
+        <v>-7.76902044924846</v>
+      </c>
+      <c r="E17" s="11">
+        <v>110.405162242619</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I17" s="12" t="s">
         <v>10</v>
@@ -2673,13 +2313,13 @@
         <v>10</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>420</v>
+        <v>306</v>
       </c>
       <c r="N17" s="14" t="s">
         <v>11</v>
@@ -2693,22 +2333,22 @@
         <v>48</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>210</v>
+        <v>140</v>
+      </c>
+      <c r="D18" s="11">
+        <v>-7.7648937404480103</v>
+      </c>
+      <c r="E18" s="11">
+        <v>110.40570764856</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>211</v>
+        <v>158</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>10</v>
@@ -2717,13 +2357,13 @@
         <v>10</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>421</v>
+        <v>307</v>
       </c>
       <c r="N18" s="14" t="s">
         <v>11</v>
@@ -2737,22 +2377,22 @@
         <v>50</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>215</v>
+        <v>140</v>
+      </c>
+      <c r="D19" s="16">
+        <v>-7.7638932991633398</v>
+      </c>
+      <c r="E19" s="16">
+        <v>110.40900868735299</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>216</v>
+        <v>159</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I19" s="12" t="s">
         <v>10</v>
@@ -2764,10 +2404,10 @@
         <v>10</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>422</v>
+        <v>308</v>
       </c>
       <c r="N19" s="14" t="s">
         <v>11</v>
@@ -2781,22 +2421,22 @@
         <v>52</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>219</v>
+        <v>140</v>
+      </c>
+      <c r="D20" s="11">
+        <v>-7.7644631240840596</v>
+      </c>
+      <c r="E20" s="11">
+        <v>110.411051308014</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I20" s="12" t="s">
         <v>10</v>
@@ -2805,13 +2445,13 @@
         <v>10</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>145</v>
+        <v>211</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>423</v>
+        <v>309</v>
       </c>
       <c r="N20" s="14" t="s">
         <v>11</v>
@@ -2825,22 +2465,22 @@
         <v>54</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>223</v>
+        <v>140</v>
+      </c>
+      <c r="D21" s="11">
+        <v>-7.7699010741598098</v>
+      </c>
+      <c r="E21" s="11">
+        <v>110.40985489941301</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>224</v>
+        <v>161</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="I21" s="12" t="s">
         <v>10</v>
@@ -2849,13 +2489,13 @@
         <v>10</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>424</v>
+        <v>310</v>
       </c>
       <c r="N21" s="14" t="s">
         <v>12</v>
@@ -2869,13 +2509,13 @@
         <v>56</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>227</v>
+        <v>140</v>
+      </c>
+      <c r="D22" s="11">
+        <v>-7.7440730712433501</v>
+      </c>
+      <c r="E22" s="11">
+        <v>110.4145966347</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>13</v>
@@ -2884,7 +2524,7 @@
         <v>9</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I22" s="12" t="s">
         <v>10</v>
@@ -2893,13 +2533,13 @@
         <v>10</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>425</v>
+        <v>311</v>
       </c>
       <c r="N22" s="14" t="s">
         <v>11</v>
@@ -2913,22 +2553,22 @@
         <v>58</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>230</v>
+        <v>140</v>
+      </c>
+      <c r="D23" s="11">
+        <v>-7.7697894548841502</v>
+      </c>
+      <c r="E23" s="11">
+        <v>110.40200137257899</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>231</v>
+        <v>162</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="I23" s="12" t="s">
         <v>10</v>
@@ -2937,13 +2577,13 @@
         <v>10</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>145</v>
+        <v>211</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>426</v>
+        <v>312</v>
       </c>
       <c r="N23" s="14" t="s">
         <v>12</v>
@@ -2957,22 +2597,22 @@
         <v>60</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>234</v>
+        <v>140</v>
+      </c>
+      <c r="D24" s="11">
+        <v>-7.7812871707890796</v>
+      </c>
+      <c r="E24" s="11">
+        <v>110.414013633897</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>235</v>
+        <v>163</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="I24" s="12" t="s">
         <v>10</v>
@@ -2981,13 +2621,13 @@
         <v>10</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>135</v>
+        <v>209</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>427</v>
+        <v>313</v>
       </c>
       <c r="N24" s="14" t="s">
         <v>12</v>
@@ -3001,22 +2641,22 @@
         <v>62</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>238</v>
+        <v>140</v>
+      </c>
+      <c r="D25" s="11">
+        <v>-7.7607444197242303</v>
+      </c>
+      <c r="E25" s="11">
+        <v>110.420050879587</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>239</v>
+        <v>164</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I25" s="12" t="s">
         <v>10</v>
@@ -3025,13 +2665,13 @@
         <v>10</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>428</v>
+        <v>314</v>
       </c>
       <c r="N25" s="14" t="s">
         <v>11</v>
@@ -3045,22 +2685,22 @@
         <v>64</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>243</v>
+        <v>140</v>
+      </c>
+      <c r="D26" s="11">
+        <v>-7.7717606194760602</v>
+      </c>
+      <c r="E26" s="11">
+        <v>110.404020014837</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>244</v>
+        <v>165</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I26" s="12" t="s">
         <v>10</v>
@@ -3069,13 +2709,13 @@
         <v>10</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>429</v>
+        <v>315</v>
       </c>
       <c r="N26" s="14" t="s">
         <v>11</v>
@@ -3089,22 +2729,22 @@
         <v>66</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>247</v>
+        <v>140</v>
+      </c>
+      <c r="D27" s="11">
+        <v>-7.7670211270826002</v>
+      </c>
+      <c r="E27" s="11">
+        <v>110.39044549226701</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>248</v>
+        <v>166</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="I27" s="12" t="s">
         <v>10</v>
@@ -3113,13 +2753,13 @@
         <v>10</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="L27" s="13" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>430</v>
+        <v>316</v>
       </c>
       <c r="N27" s="14" t="s">
         <v>12</v>
@@ -3133,22 +2773,22 @@
         <v>68</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>251</v>
+        <v>140</v>
+      </c>
+      <c r="D28" s="11">
+        <v>-7.7560856042254898</v>
+      </c>
+      <c r="E28" s="11">
+        <v>110.394390863667</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>252</v>
+        <v>167</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="I28" s="12" t="s">
         <v>10</v>
@@ -3157,13 +2797,13 @@
         <v>10</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="L28" s="13" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>431</v>
+        <v>317</v>
       </c>
       <c r="N28" s="14" t="s">
         <v>12</v>
@@ -3177,22 +2817,22 @@
         <v>70</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>256</v>
+        <v>140</v>
+      </c>
+      <c r="D29" s="11">
+        <v>-7.7757624268869803</v>
+      </c>
+      <c r="E29" s="11">
+        <v>110.394652697251</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>257</v>
+        <v>168</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="I29" s="12" t="s">
         <v>10</v>
@@ -3201,13 +2841,13 @@
         <v>10</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>169</v>
+        <v>215</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>258</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>432</v>
+        <v>318</v>
       </c>
       <c r="N29" s="14" t="s">
         <v>12</v>
@@ -3221,37 +2861,37 @@
         <v>72</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D30" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" s="11">
+        <v>-7.7725452383292799</v>
+      </c>
+      <c r="E30" s="11">
+        <v>110.41586671232599</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="L30" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="E30" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="I30" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J30" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="L30" s="13" t="s">
-        <v>262</v>
-      </c>
       <c r="M30" s="10" t="s">
-        <v>433</v>
+        <v>319</v>
       </c>
       <c r="N30" s="14" t="s">
         <v>12</v>
@@ -3265,22 +2905,22 @@
         <v>74</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>264</v>
+        <v>140</v>
+      </c>
+      <c r="D31" s="11">
+        <v>-7.7750608431802597</v>
+      </c>
+      <c r="E31" s="11">
+        <v>110.416120606155</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>265</v>
+        <v>170</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I31" s="12" t="s">
         <v>10</v>
@@ -3292,10 +2932,10 @@
         <v>10</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>434</v>
+        <v>320</v>
       </c>
       <c r="N31" s="14" t="s">
         <v>11</v>
@@ -3309,22 +2949,22 @@
         <v>60</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>268</v>
+        <v>140</v>
+      </c>
+      <c r="D32" s="11">
+        <v>-7.7800081553893303</v>
+      </c>
+      <c r="E32" s="11">
+        <v>110.414343349349</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>235</v>
+        <v>163</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="I32" s="12" t="s">
         <v>10</v>
@@ -3333,13 +2973,13 @@
         <v>10</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>135</v>
+        <v>209</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>435</v>
+        <v>321</v>
       </c>
       <c r="N32" s="14" t="s">
         <v>12</v>
@@ -3353,22 +2993,22 @@
         <v>77</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>271</v>
+        <v>140</v>
+      </c>
+      <c r="D33" s="11">
+        <v>-7.7789180746603099</v>
+      </c>
+      <c r="E33" s="11">
+        <v>110.40850379126999</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="I33" s="12" t="s">
         <v>10</v>
@@ -3377,13 +3017,13 @@
         <v>10</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>436</v>
+        <v>322</v>
       </c>
       <c r="N33" s="14" t="s">
         <v>12</v>
@@ -3397,22 +3037,22 @@
         <v>79</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>276</v>
+        <v>140</v>
+      </c>
+      <c r="D34" s="11">
+        <v>-7.7821044565191704</v>
+      </c>
+      <c r="E34" s="11">
+        <v>110.41045031063</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>277</v>
+        <v>172</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I34" s="12" t="s">
         <v>10</v>
@@ -3421,13 +3061,13 @@
         <v>10</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="L34" s="13" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>437</v>
+        <v>323</v>
       </c>
       <c r="N34" s="14" t="s">
         <v>11</v>
@@ -3441,22 +3081,22 @@
         <v>81</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>280</v>
+        <v>140</v>
+      </c>
+      <c r="D35" s="11">
+        <v>-7.7306612597897599</v>
+      </c>
+      <c r="E35" s="11">
+        <v>110.391414452842</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>281</v>
+        <v>173</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I35" s="12" t="s">
         <v>10</v>
@@ -3465,13 +3105,13 @@
         <v>10</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="L35" s="13" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>438</v>
+        <v>324</v>
       </c>
       <c r="N35" s="14" t="s">
         <v>11</v>
@@ -3482,25 +3122,25 @@
         <v>82</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>283</v>
+        <v>133</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>285</v>
+        <v>140</v>
+      </c>
+      <c r="D36" s="11">
+        <v>-7.7332127701453404</v>
+      </c>
+      <c r="E36" s="11">
+        <v>110.394504357648</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>286</v>
+        <v>174</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="I36" s="12" t="s">
         <v>10</v>
@@ -3509,13 +3149,13 @@
         <v>10</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>287</v>
+        <v>225</v>
       </c>
       <c r="L36" s="13" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="M36" s="10" t="s">
-        <v>439</v>
+        <v>325</v>
       </c>
       <c r="N36" s="14" t="s">
         <v>12</v>
@@ -3529,22 +3169,22 @@
         <v>84</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>290</v>
+        <v>140</v>
+      </c>
+      <c r="D37" s="11">
+        <v>-7.75260374425077</v>
+      </c>
+      <c r="E37" s="11">
+        <v>110.381286431535</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>291</v>
+        <v>175</v>
       </c>
       <c r="G37" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>292</v>
+        <v>198</v>
       </c>
       <c r="I37" s="12" t="s">
         <v>10</v>
@@ -3553,13 +3193,13 @@
         <v>10</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>150</v>
+        <v>212</v>
       </c>
       <c r="L37" s="13" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="M37" s="10" t="s">
-        <v>440</v>
+        <v>326</v>
       </c>
       <c r="N37" s="14" t="s">
         <v>11</v>
@@ -3573,22 +3213,22 @@
         <v>86</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>295</v>
+        <v>140</v>
+      </c>
+      <c r="D38" s="11">
+        <v>-7.7398466248468401</v>
+      </c>
+      <c r="E38" s="11">
+        <v>110.40240078104</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>296</v>
+        <v>176</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I38" s="12" t="s">
         <v>10</v>
@@ -3597,13 +3237,13 @@
         <v>10</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="L38" s="13" t="s">
-        <v>297</v>
+        <v>267</v>
       </c>
       <c r="M38" s="10" t="s">
-        <v>441</v>
+        <v>327</v>
       </c>
       <c r="N38" s="14" t="s">
         <v>11</v>
@@ -3617,16 +3257,16 @@
         <v>88</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>299</v>
+        <v>140</v>
+      </c>
+      <c r="D39" s="11">
+        <v>-7.74137749957168</v>
+      </c>
+      <c r="E39" s="11">
+        <v>110.410983849945</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>300</v>
+        <v>177</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>10</v>
@@ -3641,13 +3281,13 @@
         <v>10</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>145</v>
+        <v>211</v>
       </c>
       <c r="L39" s="13" t="s">
-        <v>301</v>
+        <v>268</v>
       </c>
       <c r="M39" s="10" t="s">
-        <v>442</v>
+        <v>328</v>
       </c>
       <c r="N39" s="14" t="s">
         <v>11</v>
@@ -3661,22 +3301,22 @@
         <v>90</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>303</v>
+        <v>140</v>
+      </c>
+      <c r="D40" s="11">
+        <v>-7.7509028173251098</v>
+      </c>
+      <c r="E40" s="11">
+        <v>110.398452569344</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>304</v>
+        <v>178</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I40" s="12" t="s">
         <v>10</v>
@@ -3685,13 +3325,13 @@
         <v>10</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>305</v>
+        <v>226</v>
       </c>
       <c r="L40" s="13" t="s">
-        <v>306</v>
+        <v>269</v>
       </c>
       <c r="M40" s="10" t="s">
-        <v>443</v>
+        <v>329</v>
       </c>
       <c r="N40" s="14" t="s">
         <v>11</v>
@@ -3705,16 +3345,16 @@
         <v>84</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>308</v>
+        <v>140</v>
+      </c>
+      <c r="D41" s="11">
+        <v>-7.7565021406755799</v>
+      </c>
+      <c r="E41" s="11">
+        <v>110.4032999854</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>309</v>
+        <v>179</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>10</v>
@@ -3729,13 +3369,13 @@
         <v>10</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="L41" s="13" t="s">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="M41" s="10" t="s">
-        <v>444</v>
+        <v>330</v>
       </c>
       <c r="N41" s="14" t="s">
         <v>11</v>
@@ -3749,22 +3389,22 @@
         <v>93</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>312</v>
+        <v>140</v>
+      </c>
+      <c r="D42" s="11">
+        <v>-7.7584104354619896</v>
+      </c>
+      <c r="E42" s="11">
+        <v>110.406326431167</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>313</v>
+        <v>180</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="I42" s="12" t="s">
         <v>10</v>
@@ -3773,13 +3413,13 @@
         <v>10</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="L42" s="13" t="s">
-        <v>314</v>
+        <v>271</v>
       </c>
       <c r="M42" s="10" t="s">
-        <v>445</v>
+        <v>331</v>
       </c>
       <c r="N42" s="14" t="s">
         <v>12</v>
@@ -3793,22 +3433,22 @@
         <v>95</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>315</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>316</v>
+        <v>140</v>
+      </c>
+      <c r="D43" s="11">
+        <v>-7.7606418764399301</v>
+      </c>
+      <c r="E43" s="11">
+        <v>110.415674342815</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>317</v>
+        <v>134</v>
       </c>
       <c r="G43" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>318</v>
+        <v>199</v>
       </c>
       <c r="I43" s="12" t="s">
         <v>10</v>
@@ -3817,13 +3457,13 @@
         <v>10</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>287</v>
+        <v>225</v>
       </c>
       <c r="L43" s="13" t="s">
-        <v>319</v>
+        <v>272</v>
       </c>
       <c r="M43" s="10" t="s">
-        <v>446</v>
+        <v>332</v>
       </c>
       <c r="N43" s="14" t="s">
         <v>11</v>
@@ -3837,22 +3477,22 @@
         <v>97</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>321</v>
+        <v>140</v>
+      </c>
+      <c r="D44" s="11">
+        <v>-7.7729243349685699</v>
+      </c>
+      <c r="E44" s="11">
+        <v>110.413129506573</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>322</v>
+        <v>181</v>
       </c>
       <c r="G44" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>323</v>
+        <v>200</v>
       </c>
       <c r="I44" s="12" t="s">
         <v>10</v>
@@ -3861,13 +3501,13 @@
         <v>10</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="L44" s="13" t="s">
-        <v>324</v>
+        <v>273</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>447</v>
+        <v>333</v>
       </c>
       <c r="N44" s="14" t="s">
         <v>11</v>
@@ -3881,22 +3521,22 @@
         <v>84</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>326</v>
+        <v>140</v>
+      </c>
+      <c r="D45" s="11">
+        <v>-7.7669102059057602</v>
+      </c>
+      <c r="E45" s="11">
+        <v>110.40986108656099</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>327</v>
+        <v>182</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I45" s="12" t="s">
         <v>10</v>
@@ -3905,13 +3545,13 @@
         <v>10</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>328</v>
+        <v>227</v>
       </c>
       <c r="L45" s="13" t="s">
-        <v>329</v>
+        <v>274</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>448</v>
+        <v>334</v>
       </c>
       <c r="N45" s="14" t="s">
         <v>11</v>
@@ -3925,22 +3565,22 @@
         <v>100</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>331</v>
+        <v>140</v>
+      </c>
+      <c r="D46" s="11">
+        <v>-7.7633770037727396</v>
+      </c>
+      <c r="E46" s="11">
+        <v>110.405403710627</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>332</v>
+        <v>183</v>
       </c>
       <c r="G46" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="I46" s="12" t="s">
         <v>10</v>
@@ -3949,13 +3589,13 @@
         <v>10</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="L46" s="13" t="s">
-        <v>333</v>
+        <v>275</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>449</v>
+        <v>335</v>
       </c>
       <c r="N46" s="14" t="s">
         <v>12</v>
@@ -3969,37 +3609,37 @@
         <v>102</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>335</v>
+        <v>140</v>
+      </c>
+      <c r="D47" s="11">
+        <v>-7.7653644336870098</v>
+      </c>
+      <c r="E47" s="11">
+        <v>110.40243212676801</v>
       </c>
       <c r="F47" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I47" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="L47" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="M47" s="10" t="s">
         <v>336</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="I47" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J47" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="K47" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="L47" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="M47" s="10" t="s">
-        <v>450</v>
       </c>
       <c r="N47" s="14" t="s">
         <v>11</v>
@@ -4013,22 +3653,22 @@
         <v>104</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>339</v>
+        <v>140</v>
+      </c>
+      <c r="D48" s="11">
+        <v>-7.7615367826219499</v>
+      </c>
+      <c r="E48" s="11">
+        <v>110.395597483668</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>340</v>
+        <v>135</v>
       </c>
       <c r="G48" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>341</v>
+        <v>201</v>
       </c>
       <c r="I48" s="12" t="s">
         <v>10</v>
@@ -4037,13 +3677,13 @@
         <v>10</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="L48" s="13" t="s">
-        <v>342</v>
+        <v>277</v>
       </c>
       <c r="M48" s="10" t="s">
-        <v>451</v>
+        <v>337</v>
       </c>
       <c r="N48" s="14" t="s">
         <v>11</v>
@@ -4057,22 +3697,22 @@
         <v>106</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>344</v>
+        <v>140</v>
+      </c>
+      <c r="D49" s="11">
+        <v>-7.7701266628993704</v>
+      </c>
+      <c r="E49" s="11">
+        <v>110.38942776021599</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>345</v>
+        <v>185</v>
       </c>
       <c r="G49" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>346</v>
+        <v>202</v>
       </c>
       <c r="I49" s="12" t="s">
         <v>10</v>
@@ -4081,13 +3721,13 @@
         <v>10</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>135</v>
+        <v>209</v>
       </c>
       <c r="L49" s="13" t="s">
-        <v>347</v>
+        <v>278</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>452</v>
+        <v>338</v>
       </c>
       <c r="N49" s="14" t="s">
         <v>11</v>
@@ -4101,22 +3741,22 @@
         <v>84</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>349</v>
+        <v>140</v>
+      </c>
+      <c r="D50" s="11">
+        <v>-7.7760096588073599</v>
+      </c>
+      <c r="E50" s="11">
+        <v>110.385496137199</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>350</v>
+        <v>186</v>
       </c>
       <c r="G50" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I50" s="12" t="s">
         <v>10</v>
@@ -4125,13 +3765,13 @@
         <v>10</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>150</v>
+        <v>212</v>
       </c>
       <c r="L50" s="13" t="s">
-        <v>351</v>
+        <v>279</v>
       </c>
       <c r="M50" s="10" t="s">
-        <v>453</v>
+        <v>339</v>
       </c>
       <c r="N50" s="14" t="s">
         <v>11</v>
@@ -4145,22 +3785,22 @@
         <v>109</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>353</v>
+        <v>140</v>
+      </c>
+      <c r="D51" s="11">
+        <v>-7.7743191459818197</v>
+      </c>
+      <c r="E51" s="11">
+        <v>110.393591001681</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>354</v>
+        <v>187</v>
       </c>
       <c r="G51" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I51" s="12" t="s">
         <v>10</v>
@@ -4169,13 +3809,13 @@
         <v>10</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>355</v>
+        <v>228</v>
       </c>
       <c r="L51" s="13" t="s">
-        <v>356</v>
+        <v>280</v>
       </c>
       <c r="M51" s="10" t="s">
-        <v>454</v>
+        <v>340</v>
       </c>
       <c r="N51" s="14" t="s">
         <v>11</v>
@@ -4189,22 +3829,22 @@
         <v>111</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D52" s="18" t="s">
-        <v>357</v>
-      </c>
-      <c r="E52" s="18" t="s">
-        <v>358</v>
+        <v>140</v>
+      </c>
+      <c r="D52" s="18">
+        <v>-7.7704175590449003</v>
+      </c>
+      <c r="E52" s="18">
+        <v>110.401436549053</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>359</v>
+        <v>188</v>
       </c>
       <c r="G52" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="I52" s="12" t="s">
         <v>10</v>
@@ -4213,13 +3853,13 @@
         <v>10</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="L52" s="19" t="s">
-        <v>360</v>
+        <v>281</v>
       </c>
       <c r="M52" s="10" t="s">
-        <v>455</v>
+        <v>341</v>
       </c>
       <c r="N52" s="14" t="s">
         <v>12</v>
@@ -4233,22 +3873,22 @@
         <v>113</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D53" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>362</v>
+        <v>140</v>
+      </c>
+      <c r="D53" s="18">
+        <v>-7.7710955496009397</v>
+      </c>
+      <c r="E53" s="18">
+        <v>110.401785877035</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>363</v>
+        <v>189</v>
       </c>
       <c r="G53" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I53" s="12" t="s">
         <v>10</v>
@@ -4257,13 +3897,13 @@
         <v>10</v>
       </c>
       <c r="K53" s="14" t="s">
-        <v>305</v>
+        <v>226</v>
       </c>
       <c r="L53" s="19" t="s">
-        <v>364</v>
+        <v>282</v>
       </c>
       <c r="M53" s="10" t="s">
-        <v>456</v>
+        <v>342</v>
       </c>
       <c r="N53" s="14" t="s">
         <v>11</v>
@@ -4277,22 +3917,22 @@
         <v>115</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>366</v>
+        <v>140</v>
+      </c>
+      <c r="D54" s="18">
+        <v>-7.7715918380578701</v>
+      </c>
+      <c r="E54" s="18">
+        <v>110.404234666901</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>367</v>
+        <v>190</v>
       </c>
       <c r="G54" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>368</v>
+        <v>203</v>
       </c>
       <c r="I54" s="12" t="s">
         <v>10</v>
@@ -4301,13 +3941,13 @@
         <v>10</v>
       </c>
       <c r="K54" s="14" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="L54" s="19" t="s">
-        <v>369</v>
+        <v>283</v>
       </c>
       <c r="M54" s="10" t="s">
-        <v>457</v>
+        <v>343</v>
       </c>
       <c r="N54" s="14" t="s">
         <v>11</v>
@@ -4321,16 +3961,16 @@
         <v>117</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="D55" s="18" t="s">
-        <v>370</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>371</v>
+        <v>142</v>
+      </c>
+      <c r="D55" s="18">
+        <v>-7.7630658285794301</v>
+      </c>
+      <c r="E55" s="18">
+        <v>110.407562566777</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>372</v>
+        <v>191</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>10</v>
@@ -4345,13 +3985,13 @@
         <v>10</v>
       </c>
       <c r="K55" s="10" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="L55" s="19" t="s">
-        <v>373</v>
+        <v>284</v>
       </c>
       <c r="M55" s="10" t="s">
-        <v>458</v>
+        <v>344</v>
       </c>
       <c r="N55" s="14" t="s">
         <v>11</v>
@@ -4365,22 +4005,22 @@
         <v>119</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="D56" s="18" t="s">
-        <v>374</v>
-      </c>
-      <c r="E56" s="18" t="s">
-        <v>375</v>
+        <v>142</v>
+      </c>
+      <c r="D56" s="18">
+        <v>-7.76082068011819</v>
+      </c>
+      <c r="E56" s="18">
+        <v>110.407999632106</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>376</v>
+        <v>136</v>
       </c>
       <c r="G56" s="14" t="s">
         <v>14</v>
       </c>
       <c r="H56" s="14" t="s">
-        <v>377</v>
+        <v>204</v>
       </c>
       <c r="I56" s="12" t="s">
         <v>10</v>
@@ -4389,13 +4029,13 @@
         <v>10</v>
       </c>
       <c r="K56" s="14" t="s">
-        <v>378</v>
+        <v>229</v>
       </c>
       <c r="L56" s="19" t="s">
-        <v>379</v>
+        <v>285</v>
       </c>
       <c r="M56" s="10" t="s">
-        <v>459</v>
+        <v>345</v>
       </c>
       <c r="N56" s="14" t="s">
         <v>11</v>
@@ -4409,22 +4049,22 @@
         <v>121</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="D57" s="18" t="s">
-        <v>380</v>
-      </c>
-      <c r="E57" s="18" t="s">
-        <v>381</v>
+        <v>142</v>
+      </c>
+      <c r="D57" s="18">
+        <v>-7.7631800043751502</v>
+      </c>
+      <c r="E57" s="18">
+        <v>110.409966073131</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>382</v>
+        <v>192</v>
       </c>
       <c r="G57" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="I57" s="12" t="s">
         <v>10</v>
@@ -4433,13 +4073,13 @@
         <v>10</v>
       </c>
       <c r="K57" s="14" t="s">
-        <v>305</v>
+        <v>226</v>
       </c>
       <c r="L57" s="19" t="s">
-        <v>383</v>
+        <v>286</v>
       </c>
       <c r="M57" s="10" t="s">
-        <v>460</v>
+        <v>346</v>
       </c>
       <c r="N57" s="14" t="s">
         <v>12</v>
@@ -4453,22 +4093,22 @@
         <v>123</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="D58" s="18" t="s">
-        <v>384</v>
-      </c>
-      <c r="E58" s="18" t="s">
-        <v>385</v>
+        <v>142</v>
+      </c>
+      <c r="D58" s="18">
+        <v>-7.7706929040795103</v>
+      </c>
+      <c r="E58" s="18">
+        <v>110.409727503684</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>386</v>
+        <v>193</v>
       </c>
       <c r="G58" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H58" s="14" t="s">
-        <v>387</v>
+        <v>205</v>
       </c>
       <c r="I58" s="12" t="s">
         <v>10</v>
@@ -4477,13 +4117,13 @@
         <v>10</v>
       </c>
       <c r="K58" s="14" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="L58" s="19" t="s">
-        <v>388</v>
+        <v>287</v>
       </c>
       <c r="M58" s="10" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="N58" s="14" t="s">
         <v>11</v>
@@ -4497,22 +4137,22 @@
         <v>125</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>389</v>
-      </c>
-      <c r="E59" s="18" t="s">
-        <v>390</v>
+        <v>142</v>
+      </c>
+      <c r="D59" s="18">
+        <v>-7.7585338723225696</v>
+      </c>
+      <c r="E59" s="18">
+        <v>110.41282053517899</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>391</v>
+        <v>194</v>
       </c>
       <c r="G59" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H59" s="14" t="s">
-        <v>392</v>
+        <v>206</v>
       </c>
       <c r="I59" s="12" t="s">
         <v>10</v>
@@ -4521,13 +4161,13 @@
         <v>10</v>
       </c>
       <c r="K59" s="14" t="s">
-        <v>393</v>
+        <v>230</v>
       </c>
       <c r="L59" s="19" t="s">
-        <v>394</v>
+        <v>288</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>462</v>
+        <v>348</v>
       </c>
       <c r="N59" s="14" t="s">
         <v>11</v>
@@ -4541,22 +4181,22 @@
         <v>127</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>395</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>396</v>
+        <v>142</v>
+      </c>
+      <c r="D60" s="18">
+        <v>-7.7496373777161098</v>
+      </c>
+      <c r="E60" s="18">
+        <v>110.41077505786799</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>397</v>
+        <v>195</v>
       </c>
       <c r="G60" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H60" s="14" t="s">
-        <v>398</v>
+        <v>207</v>
       </c>
       <c r="I60" s="12" t="s">
         <v>10</v>
@@ -4565,13 +4205,13 @@
         <v>10</v>
       </c>
       <c r="K60" s="14" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="L60" s="19" t="s">
-        <v>399</v>
+        <v>289</v>
       </c>
       <c r="M60" s="10" t="s">
-        <v>463</v>
+        <v>349</v>
       </c>
       <c r="N60" s="14" t="s">
         <v>11</v>
@@ -4585,22 +4225,22 @@
         <v>129</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>400</v>
-      </c>
-      <c r="E61" s="18" t="s">
-        <v>401</v>
+        <v>142</v>
+      </c>
+      <c r="D61" s="18">
+        <v>-7.7820789238144101</v>
+      </c>
+      <c r="E61" s="18">
+        <v>110.414433053846</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>402</v>
+        <v>196</v>
       </c>
       <c r="G61" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H61" s="14" t="s">
-        <v>403</v>
+        <v>208</v>
       </c>
       <c r="I61" s="12" t="s">
         <v>10</v>
@@ -4609,13 +4249,13 @@
         <v>10</v>
       </c>
       <c r="K61" s="14" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="L61" s="19" t="s">
-        <v>404</v>
+        <v>290</v>
       </c>
       <c r="M61" s="10" t="s">
-        <v>464</v>
+        <v>350</v>
       </c>
       <c r="N61" s="14" t="s">
         <v>11</v>
@@ -4634,66 +4274,66 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="L2" r:id="rId1" xr:uid="{5267468C-7468-4CEA-B194-8253A23D86EB}"/>
-    <hyperlink ref="L3" r:id="rId2" xr:uid="{AE4828DB-01F9-4D16-99A9-D249BB7CD965}"/>
-    <hyperlink ref="L4" r:id="rId3" xr:uid="{A012B563-CCAB-4EF1-B8F4-4E2F970CC37A}"/>
-    <hyperlink ref="L5" r:id="rId4" xr:uid="{FADB8A6F-2D74-4AD7-831E-5A0D3F9761A1}"/>
-    <hyperlink ref="L6" r:id="rId5" xr:uid="{D1E4914A-B889-4293-A1C0-4466B3DD9FC6}"/>
-    <hyperlink ref="L7" r:id="rId6" xr:uid="{4BCA6FCC-6ACE-400A-AC58-F86D8B8487EF}"/>
-    <hyperlink ref="L8" r:id="rId7" xr:uid="{35275D1F-E69D-479B-A1EE-C431302ADAA9}"/>
-    <hyperlink ref="L9" r:id="rId8" xr:uid="{5C4C4F7C-D86C-4F12-AA86-1F9071C7E670}"/>
-    <hyperlink ref="L10" r:id="rId9" xr:uid="{F797255C-90E0-4EA7-91E8-0C962653454D}"/>
-    <hyperlink ref="L11" r:id="rId10" xr:uid="{7D477009-7B94-45EB-A9C6-54553CEBC50F}"/>
-    <hyperlink ref="L12" r:id="rId11" xr:uid="{CA27134D-422E-4CE9-BEE1-07F3EF506206}"/>
-    <hyperlink ref="L13" r:id="rId12" xr:uid="{C9EDF69B-6BE5-4EF6-AD03-4CD79219E036}"/>
-    <hyperlink ref="L14" r:id="rId13" xr:uid="{A6F7FA4C-49ED-4FE7-80C5-A2A779343E1C}"/>
-    <hyperlink ref="L15" r:id="rId14" xr:uid="{1A0174E0-D31E-471A-BBDB-48F59C5343A4}"/>
-    <hyperlink ref="L16" r:id="rId15" xr:uid="{7F96AD68-703B-4CF4-A425-4DB03227FD24}"/>
-    <hyperlink ref="L17" r:id="rId16" xr:uid="{4798BDDB-D99F-40A4-9A78-D8934469539F}"/>
-    <hyperlink ref="L18" r:id="rId17" xr:uid="{9F84449B-5F0E-43EC-B3AA-E82E1A6654AF}"/>
-    <hyperlink ref="L19" r:id="rId18" xr:uid="{272CEEEB-55EB-457E-96EB-1A19DA92C196}"/>
-    <hyperlink ref="L20" r:id="rId19" xr:uid="{57AF8A39-8026-4732-890D-6669E0F18DA1}"/>
-    <hyperlink ref="L21" r:id="rId20" xr:uid="{BA49357A-79E8-4041-891D-3DC07A9119ED}"/>
-    <hyperlink ref="L22" r:id="rId21" xr:uid="{16ACD3CD-A3AA-44C2-A4BE-47E7A47B2088}"/>
-    <hyperlink ref="L23" r:id="rId22" xr:uid="{9B1E49E6-2BE5-4B70-8426-B63F2CD98862}"/>
-    <hyperlink ref="L24" r:id="rId23" xr:uid="{F674B1FE-B185-4ABB-ADFE-1DDD33C8D8E5}"/>
-    <hyperlink ref="L25" r:id="rId24" xr:uid="{13044E6A-1B95-45EB-B555-3863FF8483CD}"/>
-    <hyperlink ref="L26" r:id="rId25" xr:uid="{D8299CD3-FF56-457D-83DD-A390398EFC97}"/>
-    <hyperlink ref="L27" r:id="rId26" xr:uid="{B8F47810-22EC-4874-B43B-89BD344421A1}"/>
-    <hyperlink ref="L28" r:id="rId27" xr:uid="{555AD20D-8FCC-468B-8C15-7EEC5961E9FB}"/>
-    <hyperlink ref="L29" r:id="rId28" xr:uid="{8287139D-8C2A-4612-AC36-280951097225}"/>
-    <hyperlink ref="L30" r:id="rId29" xr:uid="{BA5396D3-7163-4EDB-B184-76494CB2C22D}"/>
-    <hyperlink ref="L31" r:id="rId30" xr:uid="{0E923CF6-34FB-47CF-BAAC-719AAB79F554}"/>
-    <hyperlink ref="L32" r:id="rId31" xr:uid="{47593C02-73A7-4EB6-8998-9440491A17D4}"/>
-    <hyperlink ref="L33" r:id="rId32" xr:uid="{EDBA646B-52E9-4AC0-AF38-853C71344029}"/>
-    <hyperlink ref="L34" r:id="rId33" xr:uid="{24A82FC5-507A-4874-A85E-B2747897C3DB}"/>
-    <hyperlink ref="L35" r:id="rId34" xr:uid="{8236309C-1E1C-426C-A8E6-D0B045361307}"/>
-    <hyperlink ref="L36" r:id="rId35" xr:uid="{B11BECAE-5AF1-42F8-9F80-4BE1EA597461}"/>
-    <hyperlink ref="L37" r:id="rId36" xr:uid="{1099F6DD-F039-47EC-BA0E-27F3A4806C3C}"/>
-    <hyperlink ref="L38" r:id="rId37" xr:uid="{8453EB8F-AF20-4BE8-8431-DAE6CDC2B400}"/>
-    <hyperlink ref="L39" r:id="rId38" xr:uid="{4B96C1B6-73F6-4206-B5B7-C22F57867270}"/>
-    <hyperlink ref="L40" r:id="rId39" xr:uid="{2B4D3CAA-15C1-4D5B-93DE-1884CBB573C6}"/>
-    <hyperlink ref="L41" r:id="rId40" xr:uid="{032C58F3-A8BC-411B-97A1-AC94D914E018}"/>
-    <hyperlink ref="L42" r:id="rId41" xr:uid="{B2EC1574-B4DE-4439-A2B4-010637857E3B}"/>
-    <hyperlink ref="L43" r:id="rId42" xr:uid="{F7F77453-21CC-48BB-A6B9-D7278D82E5B7}"/>
-    <hyperlink ref="L44" r:id="rId43" xr:uid="{2F29C550-6B2B-4362-BF5B-6449170F79F6}"/>
-    <hyperlink ref="L45" r:id="rId44" xr:uid="{A15A821E-BF2A-476F-BDED-AA79B9336568}"/>
-    <hyperlink ref="L46" r:id="rId45" xr:uid="{200BF4A1-4D26-45AC-980D-C46051A7C5CB}"/>
-    <hyperlink ref="L47" r:id="rId46" xr:uid="{E75A5E8A-E6F3-4C6A-A5B3-64D1ACD45353}"/>
-    <hyperlink ref="L48" r:id="rId47" xr:uid="{74D0E4AD-8EFB-41CB-8C5E-CC504DF1DD08}"/>
-    <hyperlink ref="L49" r:id="rId48" xr:uid="{71D08FF8-5EAE-460C-99A6-F3D95CBA62AD}"/>
-    <hyperlink ref="L50" r:id="rId49" xr:uid="{54DF84E0-1CDE-4476-AF69-3BC45EBF67D6}"/>
-    <hyperlink ref="L51" r:id="rId50" xr:uid="{ABD2C2B0-5877-4B9C-BA32-780092013A14}"/>
-    <hyperlink ref="L52" r:id="rId51" xr:uid="{4716626E-ABAA-4611-8D0E-3955E1B7CDA0}"/>
-    <hyperlink ref="L53" r:id="rId52" xr:uid="{A7685B54-6818-4D50-91FF-64723D09B5C5}"/>
-    <hyperlink ref="L54" r:id="rId53" xr:uid="{9403FDFE-01A1-4960-8D5B-C208E5862B7E}"/>
-    <hyperlink ref="L55" r:id="rId54" xr:uid="{0FD8E974-4C61-43EB-B661-26BF4BBDCFD9}"/>
-    <hyperlink ref="L56" r:id="rId55" xr:uid="{AD2153FD-7204-44EE-9883-D9E8AB25C4C7}"/>
-    <hyperlink ref="L57" r:id="rId56" xr:uid="{9DE015F3-2093-4264-85AD-14199E7AE820}"/>
-    <hyperlink ref="L58" r:id="rId57" xr:uid="{146AB10F-B53F-44CF-8742-119D90BF586E}"/>
-    <hyperlink ref="L59" r:id="rId58" xr:uid="{6C06F7D9-06A0-491D-96B9-C4D83D1C1226}"/>
-    <hyperlink ref="L60" r:id="rId59" xr:uid="{D277597D-D1CD-4BE1-A20B-44E4C3393C7A}"/>
-    <hyperlink ref="L61" r:id="rId60" xr:uid="{40A020AD-275D-4EE3-AA43-7EAD61E40479}"/>
+    <hyperlink ref="L2" r:id="rId1" display="https://maps,app,goo,gl/HvGAw3yRT4Z41LoZ7" xr:uid="{5267468C-7468-4CEA-B194-8253A23D86EB}"/>
+    <hyperlink ref="L3" r:id="rId2" display="https://maps,app,goo,gl/hrcCoQa6NbGUDMs58" xr:uid="{AE4828DB-01F9-4D16-99A9-D249BB7CD965}"/>
+    <hyperlink ref="L4" r:id="rId3" display="https://maps,app,goo,gl/yuGPo2Cdzm1cwWWFA" xr:uid="{A012B563-CCAB-4EF1-B8F4-4E2F970CC37A}"/>
+    <hyperlink ref="L5" r:id="rId4" display="https://maps,app,goo,gl/y7eFw3yPzy8XiyVH8" xr:uid="{FADB8A6F-2D74-4AD7-831E-5A0D3F9761A1}"/>
+    <hyperlink ref="L6" r:id="rId5" display="https://maps,app,goo,gl/FcK4Bx17jAYCpJhX8" xr:uid="{D1E4914A-B889-4293-A1C0-4466B3DD9FC6}"/>
+    <hyperlink ref="L7" r:id="rId6" display="https://maps,app,goo,gl/gk9yBhy1XfxyNVp5A" xr:uid="{4BCA6FCC-6ACE-400A-AC58-F86D8B8487EF}"/>
+    <hyperlink ref="L8" r:id="rId7" display="https://maps,app,goo,gl/U18wT9wYGWXs2n1dA" xr:uid="{35275D1F-E69D-479B-A1EE-C431302ADAA9}"/>
+    <hyperlink ref="L9" r:id="rId8" display="https://maps,app,goo,gl/ACN1JDZCWuDx7x3c9" xr:uid="{5C4C4F7C-D86C-4F12-AA86-1F9071C7E670}"/>
+    <hyperlink ref="L10" r:id="rId9" display="https://maps,app,goo,gl/vtbQovKZLG9tKWRM9" xr:uid="{F797255C-90E0-4EA7-91E8-0C962653454D}"/>
+    <hyperlink ref="L11" r:id="rId10" display="https://maps,app,goo,gl/Nj7awyKrLigPrPDt5" xr:uid="{7D477009-7B94-45EB-A9C6-54553CEBC50F}"/>
+    <hyperlink ref="L12" r:id="rId11" display="https://maps,app,goo,gl/UWnDTdNhGfGvs4cf6" xr:uid="{CA27134D-422E-4CE9-BEE1-07F3EF506206}"/>
+    <hyperlink ref="L13" r:id="rId12" display="https://maps,app,goo,gl/wtP4be5hRqgrhRSLA" xr:uid="{C9EDF69B-6BE5-4EF6-AD03-4CD79219E036}"/>
+    <hyperlink ref="L14" r:id="rId13" display="https://maps,app,goo,gl/BFdQ2TDQ9pBMcoAX8" xr:uid="{A6F7FA4C-49ED-4FE7-80C5-A2A779343E1C}"/>
+    <hyperlink ref="L15" r:id="rId14" display="https://maps,app,goo,gl/x2AwyBvdkzFEaSBq6" xr:uid="{1A0174E0-D31E-471A-BBDB-48F59C5343A4}"/>
+    <hyperlink ref="L16" r:id="rId15" display="https://maps,app,goo,gl/RnsoQmriB1m6i3AZ8" xr:uid="{7F96AD68-703B-4CF4-A425-4DB03227FD24}"/>
+    <hyperlink ref="L17" r:id="rId16" display="https://maps,app,goo,gl/7pUGd4KNk2rEpYPh9" xr:uid="{4798BDDB-D99F-40A4-9A78-D8934469539F}"/>
+    <hyperlink ref="L18" r:id="rId17" display="https://maps,app,goo,gl/i2NX2in6kMciJJ2f8" xr:uid="{9F84449B-5F0E-43EC-B3AA-E82E1A6654AF}"/>
+    <hyperlink ref="L19" r:id="rId18" display="https://maps,app,goo,gl/yiqGLnZVyKNjwWkj6?g_st=ac" xr:uid="{272CEEEB-55EB-457E-96EB-1A19DA92C196}"/>
+    <hyperlink ref="L20" r:id="rId19" display="https://maps,app,goo,gl/YaX6UcnU3gT1rtmEA" xr:uid="{57AF8A39-8026-4732-890D-6669E0F18DA1}"/>
+    <hyperlink ref="L21" r:id="rId20" display="https://maps,app,goo,gl/rf4pXZ5op64fGaEM8" xr:uid="{BA49357A-79E8-4041-891D-3DC07A9119ED}"/>
+    <hyperlink ref="L22" r:id="rId21" display="https://maps,app,goo,gl/fufaosvrsao483j99" xr:uid="{16ACD3CD-A3AA-44C2-A4BE-47E7A47B2088}"/>
+    <hyperlink ref="L23" r:id="rId22" display="https://maps,app,goo,gl/x4QJfLUQkhHWqZ137" xr:uid="{9B1E49E6-2BE5-4B70-8426-B63F2CD98862}"/>
+    <hyperlink ref="L24" r:id="rId23" display="https://maps,app,goo,gl/E5VGMWFMkCHfZriL7" xr:uid="{F674B1FE-B185-4ABB-ADFE-1DDD33C8D8E5}"/>
+    <hyperlink ref="L25" r:id="rId24" display="https://maps,app,goo,gl/6ptXJdnoMD4LfxAm6" xr:uid="{13044E6A-1B95-45EB-B555-3863FF8483CD}"/>
+    <hyperlink ref="L26" r:id="rId25" display="https://maps,app,goo,gl/kQbgHLjC9CHXDVUd8" xr:uid="{D8299CD3-FF56-457D-83DD-A390398EFC97}"/>
+    <hyperlink ref="L27" r:id="rId26" display="https://maps,app,goo,gl/D3hU9pNhRSwwefzd8" xr:uid="{B8F47810-22EC-4874-B43B-89BD344421A1}"/>
+    <hyperlink ref="L28" r:id="rId27" display="https://maps,app,goo,gl/SaS1WCo3QxG3jwW48" xr:uid="{555AD20D-8FCC-468B-8C15-7EEC5961E9FB}"/>
+    <hyperlink ref="L29" r:id="rId28" display="https://maps,app,goo,gl/qQN4SrSZBWcQTHjU8" xr:uid="{8287139D-8C2A-4612-AC36-280951097225}"/>
+    <hyperlink ref="L30" r:id="rId29" display="https://maps,app,goo,gl/jZqh5aGaYjRwjM1Q9" xr:uid="{BA5396D3-7163-4EDB-B184-76494CB2C22D}"/>
+    <hyperlink ref="L31" r:id="rId30" display="https://maps,app,goo,gl/FKLhFzTtUv9Svu8X8" xr:uid="{0E923CF6-34FB-47CF-BAAC-719AAB79F554}"/>
+    <hyperlink ref="L32" r:id="rId31" display="https://maps,app,goo,gl/SXgbsSj6UDL5eM7v7" xr:uid="{47593C02-73A7-4EB6-8998-9440491A17D4}"/>
+    <hyperlink ref="L33" r:id="rId32" display="https://maps,app,goo,gl/v5r9juBWxgPk1Bog6" xr:uid="{EDBA646B-52E9-4AC0-AF38-853C71344029}"/>
+    <hyperlink ref="L34" r:id="rId33" display="https://maps,app,goo,gl/wWMHH899sSHvLsLJ7" xr:uid="{24A82FC5-507A-4874-A85E-B2747897C3DB}"/>
+    <hyperlink ref="L35" r:id="rId34" display="https://maps,app,goo,gl/Hkk5NCU4DLaffHSk8" xr:uid="{8236309C-1E1C-426C-A8E6-D0B045361307}"/>
+    <hyperlink ref="L36" r:id="rId35" display="https://maps,app,goo,gl/ZP2CpU3Z8afNahNt5" xr:uid="{B11BECAE-5AF1-42F8-9F80-4BE1EA597461}"/>
+    <hyperlink ref="L37" r:id="rId36" display="https://maps,app,goo,gl/hFHpxtCSXm4rSsPWA" xr:uid="{1099F6DD-F039-47EC-BA0E-27F3A4806C3C}"/>
+    <hyperlink ref="L38" r:id="rId37" display="https://maps,app,goo,gl/LLdHixFNGbzeXS5M9" xr:uid="{8453EB8F-AF20-4BE8-8431-DAE6CDC2B400}"/>
+    <hyperlink ref="L39" r:id="rId38" display="https://maps,app,goo,gl/gWeNBEXEgqUYBySc8" xr:uid="{4B96C1B6-73F6-4206-B5B7-C22F57867270}"/>
+    <hyperlink ref="L40" r:id="rId39" display="https://maps,app,goo,gl/VfSbdzbDWi5UdNs68" xr:uid="{2B4D3CAA-15C1-4D5B-93DE-1884CBB573C6}"/>
+    <hyperlink ref="L41" r:id="rId40" display="https://maps,app,goo,gl/2HTUZCfFgRj1mc689" xr:uid="{032C58F3-A8BC-411B-97A1-AC94D914E018}"/>
+    <hyperlink ref="L42" r:id="rId41" display="https://maps,app,goo,gl/biQStQVcheFZL4fN8" xr:uid="{B2EC1574-B4DE-4439-A2B4-010637857E3B}"/>
+    <hyperlink ref="L43" r:id="rId42" display="https://maps,app,goo,gl/EpAysQ3WXUkqcna2A" xr:uid="{F7F77453-21CC-48BB-A6B9-D7278D82E5B7}"/>
+    <hyperlink ref="L44" r:id="rId43" display="https://maps,app,goo,gl/wJ3bHdk31Wbs57Jf7" xr:uid="{2F29C550-6B2B-4362-BF5B-6449170F79F6}"/>
+    <hyperlink ref="L45" r:id="rId44" display="https://maps,app,goo,gl/pLVtxDoDFYRnXBfS7" xr:uid="{A15A821E-BF2A-476F-BDED-AA79B9336568}"/>
+    <hyperlink ref="L46" r:id="rId45" display="https://maps,app,goo,gl/69ffCYJN4SpQF2DW8" xr:uid="{200BF4A1-4D26-45AC-980D-C46051A7C5CB}"/>
+    <hyperlink ref="L47" r:id="rId46" display="https://maps,app,goo,gl/brniKuRnRZYaVX8F6" xr:uid="{E75A5E8A-E6F3-4C6A-A5B3-64D1ACD45353}"/>
+    <hyperlink ref="L48" r:id="rId47" display="https://maps,app,goo,gl/bJxupU96DGrmDFjY7" xr:uid="{74D0E4AD-8EFB-41CB-8C5E-CC504DF1DD08}"/>
+    <hyperlink ref="L49" r:id="rId48" display="https://maps,app,goo,gl/mDaN88tVqkM2FXoNA" xr:uid="{71D08FF8-5EAE-460C-99A6-F3D95CBA62AD}"/>
+    <hyperlink ref="L50" r:id="rId49" display="https://maps,app,goo,gl/nvtwnSp9Uzx7WN8fA" xr:uid="{54DF84E0-1CDE-4476-AF69-3BC45EBF67D6}"/>
+    <hyperlink ref="L51" r:id="rId50" display="https://maps,app,goo,gl/XkByBoZZxTmunCKW6" xr:uid="{ABD2C2B0-5877-4B9C-BA32-780092013A14}"/>
+    <hyperlink ref="L52" r:id="rId51" display="https://maps,app,goo,gl/apZbFsSCBr6EYLRT9" xr:uid="{4716626E-ABAA-4611-8D0E-3955E1B7CDA0}"/>
+    <hyperlink ref="L53" r:id="rId52" display="https://maps,app,goo,gl/VrgpLuxUPrsUphA38" xr:uid="{A7685B54-6818-4D50-91FF-64723D09B5C5}"/>
+    <hyperlink ref="L54" r:id="rId53" display="https://maps,app,goo,gl/XafqcjhRZgeAV1c77" xr:uid="{9403FDFE-01A1-4960-8D5B-C208E5862B7E}"/>
+    <hyperlink ref="L55" r:id="rId54" display="https://maps,app,goo,gl/sXSR64xef5eu8CCL8" xr:uid="{0FD8E974-4C61-43EB-B661-26BF4BBDCFD9}"/>
+    <hyperlink ref="L56" r:id="rId55" display="https://maps,app,goo,gl/K8a86JiuLDtJy7Z98" xr:uid="{AD2153FD-7204-44EE-9883-D9E8AB25C4C7}"/>
+    <hyperlink ref="L57" r:id="rId56" display="https://maps,app,goo,gl/kU2uvJp8YCZwLjSG6" xr:uid="{9DE015F3-2093-4264-85AD-14199E7AE820}"/>
+    <hyperlink ref="L58" r:id="rId57" display="https://maps,app,goo,gl/2qZxGGcCcJtkY1g39" xr:uid="{146AB10F-B53F-44CF-8742-119D90BF586E}"/>
+    <hyperlink ref="L59" r:id="rId58" display="https://maps,app,goo,gl/Whhj3uPkLXoK1M1Y7" xr:uid="{6C06F7D9-06A0-491D-96B9-C4D83D1C1226}"/>
+    <hyperlink ref="L60" r:id="rId59" display="https://maps,app,goo,gl/FLzj6sN18SWF7E4C6" xr:uid="{D277597D-D1CD-4BE1-A20B-44E4C3393C7A}"/>
+    <hyperlink ref="L61" r:id="rId60" display="https://maps,app,goo,gl/8eNFKmsacyiLPxVA9" xr:uid="{40A020AD-275D-4EE3-AA43-7EAD61E40479}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
